--- a/Results/Ammonia/ammonia human toxicity non-carcinogenic results.xlsx
+++ b/Results/Ammonia/ammonia human toxicity non-carcinogenic results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.885664256065011e-08</v>
+        <v>1.885664256064888e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.346776542341748e-08</v>
+        <v>1.346776542341749e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.072215489419955e-08</v>
+        <v>2.072215489419917e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.377588483266537e-08</v>
+        <v>1.377588483266511e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.267104578056845e-08</v>
+        <v>1.267104578056828e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.783530532283579e-08</v>
+        <v>1.783530532283531e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>3.031208717097679e-08</v>
+        <v>3.031208717097685e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.490465436189733e-08</v>
+        <v>1.490465436189716e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.639511487928019e-08</v>
+        <v>1.639511487928039e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.521512318609949e-08</v>
+        <v>1.521512318609966e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.428351642036153e-08</v>
+        <v>3.428351642036156e-08</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.062620311243821e-08</v>
+        <v>2.06262031124391e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.463655127155318e-08</v>
+        <v>1.463655127155319e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.277192873573759e-08</v>
+        <v>2.277192873573753e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.495219696051099e-08</v>
+        <v>1.495219696051093e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.384735790841405e-08</v>
+        <v>1.38473579084141e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.945145371958218e-08</v>
+        <v>1.945145371958195e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.382082805233619e-08</v>
+        <v>3.382082805233629e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.607991453824049e-08</v>
+        <v>1.607991453824048e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.778104093822754e-08</v>
+        <v>1.778104093822727e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.651470052788764e-08</v>
+        <v>1.651470052788694e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.836971210138208e-08</v>
+        <v>3.836971210138211e-08</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.999610417659964e-08</v>
+        <v>1.135574895314915e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.698600745586412e-08</v>
+        <v>8.891357279195099e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>2.110507221043218e-08</v>
+        <v>1.246471698698207e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.71341859537259e-08</v>
+        <v>8.917438337779829e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.713418595372592e-08</v>
+        <v>8.917438337779845e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.933037007652993e-08</v>
+        <v>1.073829498242929e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.680359572283146e-08</v>
+        <v>1.816324049938144e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.734580734683375e-08</v>
+        <v>8.954302206969341e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.847783789586701e-08</v>
+        <v>9.837482672416965e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.813610547061744e-08</v>
+        <v>9.495750247167161e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>2.916412339835751e-08</v>
+        <v>2.052376817490749e-08</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.303877048976083e-07</v>
+        <v>1.011846701932901e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.967330895844781e-07</v>
+        <v>5.812684346704347e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.566573498100875e-07</v>
+        <v>1.243219172384107e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>2.967330915785335e-07</v>
+        <v>5.812684546109985e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.967330915785335e-07</v>
+        <v>5.812684546109985e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.871366366551678e-07</v>
+        <v>9.307219745413473e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.404893458787783e-06</v>
+        <v>2.607070550845649e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.967326285982e-07</v>
+        <v>5.812638248076589e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.995640399401292e-07</v>
+        <v>7.690865386877494e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.468338203041789e-07</v>
+        <v>6.734654774440121e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.738010653046783e-06</v>
+        <v>6.115256013422915e-08</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.443023894956458e-08</v>
+        <v>1.4322683217472e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.390094922431021e-08</v>
+        <v>1.186838701431033e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.846682930633152e-08</v>
+        <v>1.552041941341128e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.264731848469409e-08</v>
+        <v>1.164774964843579e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.421892567998207e-08</v>
+        <v>1.192435251330763e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.376450484949468e-08</v>
+        <v>1.679870266963215e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.208131283697522e-08</v>
+        <v>2.437211867782731e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.177994211979839e-08</v>
+        <v>1.192123647129207e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.636908135246321e-08</v>
+        <v>1.298634150371553e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.488849827787614e-08</v>
+        <v>1.244417136526833e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.646285032587706e-08</v>
+        <v>2.356834409765356e-08</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.154478089541438e-08</v>
+        <v>1.866831601603701e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.889494505192668e-08</v>
+        <v>1.626733025613463e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>6.265102378246787e-08</v>
+        <v>1.977680442403902e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.888819596020713e-08</v>
+        <v>1.626614405910079e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.888819596020713e-08</v>
+        <v>1.626614405910079e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>6.087904679534519e-08</v>
+        <v>1.80508620453169e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.835227244164681e-08</v>
+        <v>2.5475807562269e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.889448406564893e-08</v>
+        <v>1.626686926985689e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.00265146146823e-08</v>
+        <v>1.715004973530455e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.968478218943243e-08</v>
+        <v>1.68083173100547e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.071280011717274e-08</v>
+        <v>2.783633523779503e-08</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.714383795365901e-07</v>
+        <v>3.800958927208113e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.674723623068831e-07</v>
+        <v>5.2976955494092e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.916740828406555e-07</v>
+        <v>6.008486259986679e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.404852205642177e-07</v>
+        <v>4.822722021622221e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.719137484248911e-07</v>
+        <v>3.615864118509563e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.694400513343986e-07</v>
+        <v>5.47575986452911e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.769132769807007e-07</v>
+        <v>6.218254416224336e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.674554886047024e-07</v>
+        <v>5.297360586983091e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.686069101404942e-07</v>
+        <v>5.386019914892967e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.677455831088151e-07</v>
+        <v>3.582701816881118e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.823401605643696e-07</v>
+        <v>8.268275037931078e-08</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.472936943397701e-07</v>
+        <v>3.376012470046716e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.809118595428788e-07</v>
+        <v>3.774230709017782e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.846706665122357e-07</v>
+        <v>4.125226142811128e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.227643227121074e-07</v>
+        <v>4.510834221115077e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.809118248794156e-07</v>
+        <v>3.774230263251069e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.828959612862976e-07</v>
+        <v>3.952583887936003e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.903691869325992e-07</v>
+        <v>4.69507843963122e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.809113985566013e-07</v>
+        <v>3.774184610390007e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.820434291056347e-07</v>
+        <v>3.862502656934773e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.360338087460432e-07</v>
+        <v>3.458486167846438e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.927297146081248e-07</v>
+        <v>4.931131207183823e-08</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.234528055462375e-08</v>
+        <v>1.234528055462373e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.159186987567249e-08</v>
+        <v>1.159186987567245e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3233388449007e-08</v>
+        <v>1.323338844900698e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.189494926859319e-08</v>
+        <v>1.189494926859318e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.080457498192073e-08</v>
+        <v>1.08045749819207e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.305318049983317e-08</v>
+        <v>1.305318049983316e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.314507626635256e-08</v>
+        <v>1.314507626635254e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.300525262081226e-08</v>
+        <v>1.300525262081224e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.394957594960652e-08</v>
+        <v>1.394957594960647e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.185057432791167e-08</v>
+        <v>1.185057432791163e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.289959104902773e-08</v>
+        <v>1.289959104902772e-08</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.313920667947443e-08</v>
+        <v>1.313920667947442e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.247641786306477e-08</v>
+        <v>1.247641786306473e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.416071472901128e-08</v>
+        <v>1.416071472901126e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.278845786901739e-08</v>
+        <v>1.278845786901735e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.16980835823449e-08</v>
+        <v>1.169808358234485e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.395343825749723e-08</v>
+        <v>1.395343825749716e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.407573220805124e-08</v>
+        <v>1.407573220805123e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.389958291516604e-08</v>
+        <v>1.3899582915166e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.49693608081072e-08</v>
+        <v>1.496936080810712e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.265544451205607e-08</v>
+        <v>1.265544451205606e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.377696251163517e-08</v>
+        <v>1.377696251163514e-08</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.504997148997494e-08</v>
+        <v>7.317988241935719e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.500040591055286e-08</v>
+        <v>7.634006777370891e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.557791400086205e-08</v>
+        <v>7.845930752822823e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.511465154538624e-08</v>
+        <v>7.654115403540847e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.511465154538627e-08</v>
+        <v>7.65411540354086e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.541887376946369e-08</v>
+        <v>7.729667856612586e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.552597403501229e-08</v>
+        <v>7.793990786973092e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.518465803455857e-08</v>
+        <v>7.666382279393063e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.594382672433852e-08</v>
+        <v>8.211843476299283e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.509328353962117e-08</v>
+        <v>7.361300291581951e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.538051129307237e-08</v>
+        <v>7.648528045033138e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.368385909094632e-07</v>
+        <v>2.875278514361892e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.752713635398898e-07</v>
+        <v>3.58416951672879e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.860405167276325e-07</v>
+        <v>3.784734867016852e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.752713652323025e-07</v>
+        <v>3.584169685970084e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.752713652323022e-07</v>
+        <v>3.584169685970084e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.77533278303061e-07</v>
+        <v>3.626180289992131e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.977596647791425e-07</v>
+        <v>3.986712018414837e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.752712993752944e-07</v>
+        <v>3.584163100269188e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.248310590366396e-07</v>
+        <v>4.497599616405379e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.428982763455651e-07</v>
+        <v>2.98549789035437e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.744779925653858e-07</v>
+        <v>3.758812100535913e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.266353632329973e-08</v>
+        <v>1.217797562626653e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.898099276064136e-08</v>
+        <v>1.009459004965352e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.944854454235845e-08</v>
+        <v>1.27529537132744e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.79119385547103e-08</v>
+        <v>9.906437904977435e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.904127335129343e-08</v>
+        <v>1.010520082809905e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>4.303243860278849e-08</v>
+        <v>1.016203546916243e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.370813963519263e-08</v>
+        <v>1.275405190572822e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.900492863529649e-08</v>
+        <v>1.009874989194289e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.369353947236152e-08</v>
+        <v>1.309579289348713e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.887829211421666e-08</v>
+        <v>9.787461787564291e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>2.921893758809901e-08</v>
+        <v>1.008409105976049e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.078786933610713e-08</v>
+        <v>1.360785822877263e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.092262004528667e-08</v>
+        <v>1.395631643082592e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.131344968556553e-08</v>
+        <v>1.413538499925055e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.092390126556472e-08</v>
+        <v>1.395654332014189e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.092390126556479e-08</v>
+        <v>1.395654332014189e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.11567716155958e-08</v>
+        <v>1.40195378434495e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.126387188114442e-08</v>
+        <v>1.408386077381001e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.092255588069077e-08</v>
+        <v>1.395625226622997e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.168172457047064e-08</v>
+        <v>1.450171346313619e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.083118138575334e-08</v>
+        <v>1.365117027841886e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.11184091392044e-08</v>
+        <v>1.393839803187005e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.456991202022e-07</v>
+        <v>3.031223829069051e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.309614341095952e-07</v>
+        <v>4.56431475344458e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.489810712360229e-07</v>
+        <v>4.892488620362043e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.076826687625084e-07</v>
+        <v>4.154608625010712e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.485337928628463e-07</v>
+        <v>3.113588414817534e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.311746229737171e-07</v>
+        <v>4.570267951080038e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.312817232392655e-07</v>
+        <v>4.576700244116085e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.309404072388123e-07</v>
+        <v>4.563939393358087e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.317163018269279e-07</v>
+        <v>4.618779888857822e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.441615334527395e-07</v>
+        <v>3.007731215320168e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.200372212214513e-07</v>
+        <v>6.126810870188436e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.02482594247169e-07</v>
+        <v>2.270612976381961e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.277085366069392e-07</v>
+        <v>2.747063767244799e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.281017377200111e-07</v>
+        <v>2.765012362008193e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>1.566632271479054e-07</v>
+        <v>3.256666457459287e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.277085201279059e-07</v>
+        <v>2.747063616668632e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.279426881772483e-07</v>
+        <v>2.753385908507157e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.280497884427971e-07</v>
+        <v>2.759818201543209e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.277084724423434e-07</v>
+        <v>2.747057350785202e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.284676411321232e-07</v>
+        <v>2.801603470475828e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.130791668806655e-07</v>
+        <v>2.460681566615905e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.279043257008572e-07</v>
+        <v>2.745271927349211e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1310,10 +1310,10 @@
         <v>1.315999459690331e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.238433740991819e-08</v>
+        <v>1.238433740991821e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.703198635925438e-08</v>
+        <v>1.703198635925439e-08</v>
       </c>
       <c r="E2" t="n">
         <v>1.179368004376355e-08</v>
@@ -1322,22 +1322,22 @@
         <v>1.179368004376355e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.506508855794537e-08</v>
+        <v>1.506508855794534e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.092498744543485e-08</v>
+        <v>2.092498744543486e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.367682386043902e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.49305754513667e-08</v>
+        <v>1.493057545136671e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.390406464433816e-08</v>
+        <v>1.390406464433818e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.637998050731255e-08</v>
+        <v>1.637998050731256e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1350,7 +1350,7 @@
         <v>1.41018512144301e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.35416401086687e-08</v>
+        <v>1.354164010866873e-08</v>
       </c>
       <c r="D3" t="n">
         <v>1.855544382181106e-08</v>
@@ -1365,7 +1365,7 @@
         <v>1.629310390865359e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.305190511471105e-08</v>
+        <v>2.305190511471104e-08</v>
       </c>
       <c r="I3" t="n">
         <v>1.469655256470756e-08</v>
@@ -1374,10 +1374,10 @@
         <v>1.628819143829569e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.491736904714863e-08</v>
+        <v>1.491736904714864e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.780566900776751e-08</v>
+        <v>1.78056690077675e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.567203274072853e-08</v>
+        <v>7.920892713623225e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.56923880622653e-08</v>
+        <v>8.646404202595248e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.797376777323761e-08</v>
+        <v>1.022262774613229e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.552502287425412e-08</v>
+        <v>8.149532026353708e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.552502287425413e-08</v>
+        <v>8.149532026353706e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.674833780728437e-08</v>
+        <v>9.043500455938977e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>2.02872397427566e-08</v>
+        <v>1.253609971565133e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.569433977942818e-08</v>
+        <v>8.179123849633306e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.731743596499272e-08</v>
+        <v>9.566295937887467e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.595479345503626e-08</v>
+        <v>8.203653427930975e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.758697277194575e-08</v>
+        <v>9.83583274484035e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.285554603075495e-07</v>
+        <v>2.778837585772965e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.827029586489232e-07</v>
+        <v>5.564026437120587e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.144741003269027e-07</v>
+        <v>8.000668589744527e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.227120664754632e-07</v>
+        <v>4.461445150257769e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.227120664754632e-07</v>
+        <v>4.461445150257769e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.075125266588667e-07</v>
+        <v>6.021799741652365e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.17104899629758e-07</v>
+        <v>1.351760071912262e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.227118141066896e-07</v>
+        <v>4.461419913380418e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.668057171292228e-07</v>
+        <v>7.107623308949399e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.194180195327884e-07</v>
+        <v>4.401318102357781e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.283344281441703e-07</v>
+        <v>8.212738449863255e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.599189303026506e-08</v>
+        <v>1.057851626116099e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.140865822804451e-08</v>
+        <v>1.141246773678415e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.336759303197668e-08</v>
+        <v>1.293196849133986e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.948957756453969e-08</v>
+        <v>1.060729363852638e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.081541705258486e-08</v>
+        <v>1.084064138715791e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>4.706819809682093e-08</v>
+        <v>1.437979583798214e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.222234720681436e-08</v>
+        <v>1.815667859886979e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.601420006896457e-08</v>
+        <v>1.351541923167646e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.804776173544028e-08</v>
+        <v>1.497483324417948e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.097286603875819e-08</v>
+        <v>1.084683418834359e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.275732674929953e-08</v>
+        <v>1.250581503038705e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.375404736898981e-08</v>
+        <v>1.462332725187936e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.447301319099593e-08</v>
+        <v>1.547179418826776e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.605341906476071e-08</v>
+        <v>1.692464633712478e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.37781462543671e-08</v>
+        <v>1.488208170477261e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.37781462543671e-08</v>
+        <v>1.488208170477261e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.483035243554571e-08</v>
+        <v>1.574593499419514e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.836925437101793e-08</v>
+        <v>1.923853425390748e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.377635440768939e-08</v>
+        <v>1.488155838788946e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.539945059325408e-08</v>
+        <v>1.626873047614361e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.403680808329759e-08</v>
+        <v>1.490608796618712e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.566898740020697e-08</v>
+        <v>1.653826728309651e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.549664942831014e-07</v>
+        <v>3.243671781223931e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.465344626278498e-07</v>
+        <v>4.92746091060397e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.669284003682983e-07</v>
+        <v>5.403864284544138e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.209947609228162e-07</v>
+        <v>4.431220572694948e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.578704470770511e-07</v>
+        <v>3.320232655029479e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.46869468808257e-07</v>
+        <v>4.95448192926495e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.504083707437796e-07</v>
+        <v>5.303741855237077e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.458154707804002e-07</v>
+        <v>4.868044268634385e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.474564170221258e-07</v>
+        <v>5.007075638446518e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.535621029804511e-07</v>
+        <v>3.242253977317138e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.425841548376848e-07</v>
+        <v>6.703533647846905e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.212569402285579e-07</v>
+        <v>2.650383633078758e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.521859810081475e-07</v>
+        <v>3.266927643090009e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.53768757931991e-07</v>
+        <v>3.412254588456865e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>1.86351336061229e-07</v>
+        <v>3.821496298434867e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.51489549434352e-07</v>
+        <v>3.20792885712651e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.525433202526974e-07</v>
+        <v>3.294341723682744e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.560822221881695e-07</v>
+        <v>3.643601649653979e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.514893222248409e-07</v>
+        <v>3.207904063052178e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.531124184104057e-07</v>
+        <v>3.346621271877595e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.137098970504147e-07</v>
+        <v>2.902289564737242e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.533819552173586e-07</v>
+        <v>3.373574952572879e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.246407726630161e-08</v>
+        <v>1.246407726630162e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.158643556388618e-08</v>
+        <v>1.158643556388617e-08</v>
       </c>
       <c r="D2" t="n">
         <v>1.568966487521941e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.115423964260677e-08</v>
+        <v>1.115423964260676e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.115423964260677e-08</v>
+        <v>1.115423964260676e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.396257077776869e-08</v>
+        <v>1.396257077776867e-08</v>
       </c>
       <c r="H2" t="n">
         <v>1.703665882208002e-08</v>
@@ -1727,7 +1727,7 @@
         <v>1.306560873392667e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.342266082719069e-08</v>
+        <v>1.342266082719068e-08</v>
       </c>
       <c r="K2" t="n">
         <v>1.287984496719376e-08</v>
@@ -1746,31 +1746,31 @@
         <v>1.330466647602042e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.263296532499075e-08</v>
+        <v>1.263296532499072e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.701476040473611e-08</v>
+        <v>1.701476040473613e-08</v>
       </c>
       <c r="E3" t="n">
         <v>1.208561374505136e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.208561374505137e-08</v>
+        <v>1.208561374505136e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.502824442620328e-08</v>
+        <v>1.502824442620327e-08</v>
       </c>
       <c r="H3" t="n">
         <v>1.858205323116226e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.399753774228034e-08</v>
+        <v>1.399753774228033e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.455871854336872e-08</v>
+        <v>1.455871854336871e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.374969849450686e-08</v>
+        <v>1.374969849450687e-08</v>
       </c>
       <c r="L3" t="n">
         <v>1.444839487664238e-08</v>
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.508580644031533e-08</v>
+        <v>7.458354043608166e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.509766252018451e-08</v>
+        <v>8.153765766935432e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.700328159407572e-08</v>
+        <v>9.375829197368615e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.510506209259068e-08</v>
+        <v>7.757797149230321e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.510506209259069e-08</v>
+        <v>7.757797149230321e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.592163449264467e-08</v>
+        <v>8.339471479183478e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.780390206106727e-08</v>
+        <v>1.017644966436013e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.516643086264188e-08</v>
+        <v>7.768446015684787e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.625514829759082e-08</v>
+        <v>8.62769590088373e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.520162247735325e-08</v>
+        <v>7.57417008064608e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.567795896344322e-08</v>
+        <v>8.050506566736143e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.286173374002504e-08</v>
+        <v>1.938691718372094e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.257639321532978e-07</v>
+        <v>4.523102902145629e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.196967619076393e-07</v>
+        <v>6.264988144388477e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.775550504312489e-07</v>
+        <v>3.63489949419097e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.775550504312489e-07</v>
+        <v>3.63489949419097e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.296128127425143e-07</v>
+        <v>4.594911864736816e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.392908642961943e-07</v>
+        <v>8.43581546157813e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.775548659203073e-07</v>
+        <v>3.634881043096814e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.617538072862765e-07</v>
+        <v>5.183545964876661e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.545844745697618e-07</v>
+        <v>3.210555191598416e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.21783341781721e-07</v>
+        <v>4.432505374619558e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.332281924014826e-08</v>
+        <v>1.242806826944991e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.966876060180539e-08</v>
+        <v>1.071827901540464e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.119471676595549e-08</v>
+        <v>1.44448682369673e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.794430274821957e-08</v>
+        <v>1.001750349237655e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.915438528097272e-08</v>
+        <v>1.023047801698708e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.98789608165224e-08</v>
+        <v>1.079596089887526e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.773810701555276e-08</v>
+        <v>1.544486970780212e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.912375718651976e-08</v>
+        <v>1.022493543537657e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.108577845837684e-08</v>
+        <v>1.123788679503847e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.907548310297236e-08</v>
+        <v>1.001596953752393e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.965859066496695e-08</v>
+        <v>1.051109773287135e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.141369032158999e-08</v>
+        <v>1.385206157206756e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.209926122345154e-08</v>
+        <v>1.466604710342295e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.332893187820618e-08</v>
+        <v>1.576914361273274e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.152056730101705e-08</v>
+        <v>1.416692603118485e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.152056730101705e-08</v>
+        <v>1.416692603118485e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.224951837391933e-08</v>
+        <v>1.473317900764287e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.413178594234193e-08</v>
+        <v>1.657015719281953e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.149431474391659e-08</v>
+        <v>1.416215354414418e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.258303217886558e-08</v>
+        <v>1.50214034293431e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.152950635862801e-08</v>
+        <v>1.396787760910547e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.200584284471798e-08</v>
+        <v>1.444421409519555e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.473188400369819e-07</v>
+        <v>3.073136783051429e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.343678926262762e-07</v>
+        <v>4.674532605654769e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.534538281098638e-07</v>
+        <v>5.099112515865045e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.101503793066082e-07</v>
+        <v>4.208577279288773e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.50152703561314e-07</v>
+        <v>3.152618191893416e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.344734245424659e-07</v>
+        <v>4.680458631952483e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.363556921110191e-07</v>
+        <v>4.864156450472441e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.337182209124632e-07</v>
+        <v>4.623356085602614e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.348239024684297e-07</v>
+        <v>4.709579642650794e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.45831240855566e-07</v>
+        <v>3.05649827906334e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.24396907997464e-07</v>
+        <v>6.238504130230648e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.082177053397034e-07</v>
+        <v>2.384956816108298e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.356601959074757e-07</v>
+        <v>2.93727715281213e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3689210899449e-07</v>
+        <v>3.047626270550662e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>1.659323339102566e-07</v>
+        <v>3.430339684529941e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.350554131616754e-07</v>
+        <v>2.886905882299567e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.358104530579435e-07</v>
+        <v>2.943990343234119e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.37692720626366e-07</v>
+        <v>3.127688161751788e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.350552494279409e-07</v>
+        <v>2.886887796884249e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.361439668628898e-07</v>
+        <v>2.972812785404141e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.19587380421708e-07</v>
+        <v>2.594606337930249e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.355667775287422e-07</v>
+        <v>2.915093851989388e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2099,34 +2099,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.205295168183212e-08</v>
+        <v>1.205295168183222e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.084956101107515e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.460820613215816e-08</v>
+        <v>1.460820613215824e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.051822373895018e-08</v>
+        <v>1.051822373895025e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.051822373895018e-08</v>
+        <v>1.051822373895025e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.318047809855082e-08</v>
+        <v>1.318047809855086e-08</v>
       </c>
       <c r="H2" t="n">
         <v>1.487851782095149e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.244986286676451e-08</v>
+        <v>1.244986286676456e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.196921079939227e-08</v>
+        <v>1.196921079939231e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.241873125942762e-08</v>
+        <v>1.241873125942757e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.259129516527715e-08</v>
@@ -2139,34 +2139,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.283508370952467e-08</v>
+        <v>1.283508370952465e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.17916008638652e-08</v>
+        <v>1.179160086386522e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.577415564676438e-08</v>
+        <v>1.577415564676434e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.136041018417781e-08</v>
+        <v>1.136041018417783e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.136041018417781e-08</v>
+        <v>1.136041018417783e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.413197265514477e-08</v>
+        <v>1.41319726551447e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.610255547867232e-08</v>
+        <v>1.610255547867231e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.329280336369076e-08</v>
+        <v>1.32928033636906e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.289054682943969e-08</v>
+        <v>1.289054682943974e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.322609232480775e-08</v>
+        <v>1.322609232480784e-08</v>
       </c>
       <c r="L3" t="n">
         <v>1.34545324505705e-08</v>
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.488615181186929e-08</v>
+        <v>7.217266339068222e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.469140864507006e-08</v>
+        <v>7.727820107064171e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.640514230727229e-08</v>
+        <v>8.736256834471255e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.480880749346044e-08</v>
+        <v>7.39949422149456e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.480880749346043e-08</v>
+        <v>7.39949422149456e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.550183567390553e-08</v>
+        <v>7.877926441009754e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.656603787194395e-08</v>
+        <v>8.897152399142871e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.484766257226855e-08</v>
+        <v>7.406199643395649e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.543706354389957e-08</v>
+        <v>7.768178071098519e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.498599788392762e-08</v>
+        <v>7.317112411126578e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.520733524749214e-08</v>
+        <v>7.538449774691063e-09</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.091246300387672e-08</v>
+        <v>1.531789706496741e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.868664083689719e-07</v>
+        <v>3.803061989427201e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.617975692804838e-07</v>
+        <v>5.192532374773193e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.447714478422175e-07</v>
+        <v>3.027291879893356e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.447714478422175e-07</v>
+        <v>3.027291879893356e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.86824942391497e-07</v>
+        <v>3.803079305991866e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.071555665710177e-07</v>
+        <v>6.004090917305197e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.447712863471596e-07</v>
+        <v>3.027275730387052e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.795247777665144e-07</v>
+        <v>3.664761561779244e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.317420670350865e-07</v>
+        <v>2.786618047038332e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.684490772624613e-07</v>
+        <v>3.45089962231829e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.284292133761093e-08</v>
+        <v>9.633869828261943e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>2.905100445703397e-08</v>
+        <v>1.025510895627183e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0326670397902e-08</v>
+        <v>1.118644576514425e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.741372035454775e-08</v>
+        <v>9.617958873024972e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.860812300951708e-08</v>
+        <v>9.828173739160457e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>2.923253739145292e-08</v>
+        <v>1.279831785087866e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.641041864149561e-08</v>
+        <v>1.414976338612214e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.857836428981594e-08</v>
+        <v>1.232659105326452e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.001439971122297e-08</v>
+        <v>1.276594720838154e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.865581140746668e-08</v>
+        <v>9.722999578232878e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>2.895189830656035e-08</v>
+        <v>9.95749285997923e-09</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.131708925718125e-08</v>
+        <v>1.362911129469988e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.182276826310997e-08</v>
+        <v>1.426293936442795e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.283385105050125e-08</v>
+        <v>1.514770953853839e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.131226990537907e-08</v>
+        <v>1.382410357117984e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.131226990537907e-08</v>
+        <v>1.382410357117984e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.193277311921744e-08</v>
+        <v>1.428977139664144e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.299697531725592e-08</v>
+        <v>1.530899735477452e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.127860001758055e-08</v>
+        <v>1.38180445990273e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.186800098921152e-08</v>
+        <v>1.418002302673016e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.141693532923957e-08</v>
+        <v>1.372895736675823e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.163827269280415e-08</v>
+        <v>1.39502947303227e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.472777576402729e-07</v>
+        <v>3.051818883860875e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.343048158870916e-07</v>
+        <v>4.637977957215478e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.531962748886272e-07</v>
+        <v>5.041149594296811e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.101060665364589e-07</v>
+        <v>4.17718116268123e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.500016987638956e-07</v>
+        <v>3.119344295616118e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.343629519637044e-07</v>
+        <v>4.639748269929207e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.354271541619509e-07</v>
+        <v>4.741670865746188e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.337087788620674e-07</v>
+        <v>4.592575590167796e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.343151735818305e-07</v>
+        <v>4.629072522903596e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.45771388160715e-07</v>
+        <v>3.033534097511451e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.243930856889234e-07</v>
+        <v>6.195514155752051e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.02795260963999e-07</v>
+        <v>2.268926946600639e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.286352322469362e-07</v>
+        <v>2.77819329523273e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.296485532038415e-07</v>
+        <v>2.866709704427009e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>1.573264461313579e-07</v>
+        <v>3.24825984858491e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.280912062665703e-07</v>
+        <v>2.733719629752737e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.287452371030438e-07</v>
+        <v>2.780876498454076e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.298094393010822e-07</v>
+        <v>2.882799094267386e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.280910640014067e-07</v>
+        <v>2.733703818692666e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.28680464973038e-07</v>
+        <v>2.769901661462947e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.129550776426102e-07</v>
+        <v>2.163348083399995e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.284507366766304e-07</v>
+        <v>2.746928831822202e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.202667322870276e-08</v>
+        <v>1.202667322870273e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.656937077301573e-09</v>
+        <v>9.656937077301575e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.49716216911806e-08</v>
+        <v>1.497162169118058e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.064893833960795e-08</v>
+        <v>1.064893833960792e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.064893833960795e-08</v>
+        <v>1.064893833960792e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.395661517796725e-08</v>
+        <v>1.395661517796723e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.904687015669996e-08</v>
+        <v>1.904687015669994e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.261394980017978e-08</v>
+        <v>1.261394980017975e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.461923626230487e-08</v>
+        <v>1.461923626230486e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.320662082738277e-08</v>
+        <v>1.320662082738271e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.623387456784187e-08</v>
+        <v>1.623387456784186e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.279249453232955e-08</v>
+        <v>1.279249453232953e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.041767053602954e-08</v>
+        <v>1.041767053602953e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.617979530841526e-08</v>
+        <v>1.617979530841523e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.150339208912132e-08</v>
+        <v>1.15033920891213e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.150339208912132e-08</v>
+        <v>1.15033920891213e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.50123275602541e-08</v>
+        <v>1.501232756025407e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.088573351807179e-08</v>
+        <v>2.088573351807176e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.346911982948917e-08</v>
+        <v>1.346911982948916e-08</v>
       </c>
       <c r="J3" t="n">
         <v>1.593404080607928e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.411965791040652e-08</v>
+        <v>1.411965791040648e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.763175125986965e-08</v>
+        <v>1.763175125986963e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.456944711768937e-08</v>
+        <v>7.142627710455047e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.364212228823258e-08</v>
+        <v>6.9827879588972e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.632009419058063e-08</v>
+        <v>8.893274783346291e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.460529917201126e-08</v>
+        <v>7.43797254519317e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.460529917201122e-08</v>
+        <v>7.43797254519317e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.566083357536118e-08</v>
+        <v>8.280061144313032e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.874207793859773e-08</v>
+        <v>1.131525853136338e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.463549744047587e-08</v>
+        <v>7.443085647917436e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.674209519223481e-08</v>
+        <v>9.315275785000471e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.515206614183951e-08</v>
+        <v>7.725246734605169e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.707097521446427e-08</v>
+        <v>9.644155807229916e-09</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.124066339928685e-08</v>
+        <v>1.535676173150703e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.287194317098629e-07</v>
+        <v>2.723639430735786e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.957781781509784e-07</v>
+        <v>5.807789729386433e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.60898079448585e-07</v>
+        <v>3.318550173435451e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.60898079448585e-07</v>
+        <v>3.318550173435451e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.41786657452747e-07</v>
+        <v>4.807820593108227e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>5.946558300358931e-07</v>
+        <v>1.126760783512532e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.608978345547786e-07</v>
+        <v>3.318525684054813e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.519488848950366e-07</v>
+        <v>6.831167045301527e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.830848957998323e-07</v>
+        <v>3.728142459425861e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.187249327992853e-07</v>
+        <v>8.033525195911128e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.414948208237045e-08</v>
+        <v>9.725680311102123e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>2.883419260719755e-08</v>
+        <v>9.656592320546709e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>3.117625402659749e-08</v>
+        <v>1.150795890031739e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.804972822884289e-08</v>
+        <v>9.804192046373963e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.934306346829519e-08</v>
+        <v>1.003181904728412e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.033726888583628e-08</v>
+        <v>1.086311374496011e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.987249176340526e-08</v>
+        <v>1.679421133484121e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.421553240515681e-08</v>
+        <v>1.002613824856451e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.671774178142979e-08</v>
+        <v>1.459098955611175e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.979508375305606e-08</v>
+        <v>1.030241782021461e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.183615995317784e-08</v>
+        <v>1.224282830716234e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.255933537763764e-08</v>
+        <v>1.382884800797595e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.240458881717183e-08</v>
+        <v>1.380498203102373e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.430762771749311e-08</v>
+        <v>1.557908064785513e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.266585352440448e-08</v>
+        <v>1.4136630074917e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.266585352440448e-08</v>
+        <v>1.4136630074917e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.365072183530947e-08</v>
+        <v>1.496628144183394e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.673196619854598e-08</v>
+        <v>1.800147882888426e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.262538570042407e-08</v>
+        <v>1.412930594543835e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.473198345218304e-08</v>
+        <v>1.600149608252135e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.314195440178777e-08</v>
+        <v>1.441146703212607e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.506086347441249e-08</v>
+        <v>1.633037610475082e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.536062452963582e-07</v>
+        <v>3.161310405730492e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.441704764823646e-07</v>
+        <v>4.755577807721538e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.648155024692172e-07</v>
+        <v>5.262846640340245e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.195899903446114e-07</v>
+        <v>4.351527799608213e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.565717134560882e-07</v>
+        <v>3.242406132380095e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.453573571904506e-07</v>
+        <v>4.870664908151298e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.484386015537289e-07</v>
+        <v>5.174184646857071e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.443320210555646e-07</v>
+        <v>4.786967358511743e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.46456436054263e-07</v>
+        <v>4.974499955764472e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.525048133744709e-07</v>
+        <v>3.189933011655844e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.414691629035662e-07</v>
+        <v>6.673823653114163e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.183436906964255e-07</v>
+        <v>2.540689448134575e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.478968655402535e-07</v>
+        <v>3.061162264321757e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.49802267275746e-07</v>
+        <v>3.238613711903685e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>1.824001967423488e-07</v>
+        <v>3.696987435755086e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.481178838853144e-07</v>
+        <v>3.0936187327407e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.491429985583912e-07</v>
+        <v>3.17729220540278e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.522242429216278e-07</v>
+        <v>3.480811944107811e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.481176624235059e-07</v>
+        <v>3.093594655763221e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.502242601752649e-07</v>
+        <v>3.280813669471524e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.112266531317517e-07</v>
+        <v>2.463437395320582e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.505531401974944e-07</v>
+        <v>3.313701671694464e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.216534207452416e-08</v>
+        <v>1.216534207452423e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.822465541363821e-09</v>
+        <v>9.822465541363843e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.289742891312563e-08</v>
+        <v>1.289742891312574e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.066852678930309e-08</v>
+        <v>1.066852678930308e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.066852678930309e-08</v>
+        <v>1.066852678930308e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.262751925355437e-08</v>
+        <v>1.262751925355438e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.301850535817241e-08</v>
+        <v>1.301850535817242e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.26896891090426e-08</v>
+        <v>1.268968910904266e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.242170198088302e-08</v>
+        <v>1.242170198088307e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.238591093560438e-08</v>
+        <v>1.238591093560439e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.292132056642474e-08</v>
+        <v>1.292132056642476e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.294591569447805e-08</v>
+        <v>1.294591569447802e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.061100949386498e-08</v>
+        <v>1.061100949386499e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.378796721020149e-08</v>
+        <v>1.378796721020152e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.152832041352319e-08</v>
+        <v>1.15283204135232e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.152832041352319e-08</v>
+        <v>1.15283204135232e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.347751519007701e-08</v>
+        <v>1.347751519007705e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.394520509622911e-08</v>
+        <v>1.394520509622914e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.355114627490712e-08</v>
+        <v>1.355114627490719e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.341191633569084e-08</v>
+        <v>1.341191633569086e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.318274216168194e-08</v>
+        <v>1.318274216168206e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.381563923602618e-08</v>
+        <v>1.381563923602619e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.458290721218857e-08</v>
+        <v>7.171808513276143e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.380606339415091e-08</v>
+        <v>7.082678143505125e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.501810181658634e-08</v>
+        <v>7.607003117673926e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.469438610790785e-08</v>
+        <v>7.449769225506346e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.46943861079079e-08</v>
+        <v>7.449769225506346e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.480481464666027e-08</v>
+        <v>7.43725389482545e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.509058161478987e-08</v>
+        <v>7.67948291587745e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.463135668118717e-08</v>
+        <v>7.438633112311258e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.541257833075352e-08</v>
+        <v>8.001479631841112e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.464724807737058e-08</v>
+        <v>7.236149378458179e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.503323155977529e-08</v>
+        <v>7.622132860862875e-09</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.34850271785703e-08</v>
+        <v>1.577858158072264e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.323834716753932e-07</v>
+        <v>2.795230188791956e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.646380921044981e-07</v>
+        <v>3.394012126565769e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.542880050190318e-07</v>
+        <v>3.201824602073725e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.542880050190318e-07</v>
+        <v>3.201824602073725e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.519095817499048e-07</v>
+        <v>3.156769277424368e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.879600215965789e-07</v>
+        <v>3.810450418781121e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.542879529144779e-07</v>
+        <v>3.201819391618328e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.090725221077984e-07</v>
+        <v>4.208562955191252e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.309137840035177e-07</v>
+        <v>2.76990595905797e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.850128970238513e-07</v>
+        <v>3.753855382043498e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.818268802260425e-08</v>
+        <v>9.565369922939535e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>2.796572044836727e-08</v>
+        <v>9.574777771543536e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>4.306898368000111e-08</v>
+        <v>1.000634668700595e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.715437286464312e-08</v>
+        <v>9.642726882808996e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.827362597641666e-08</v>
+        <v>9.839715429413731e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>2.84045954570759e-08</v>
+        <v>1.228356353437462e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.422181939535511e-08</v>
+        <v>1.280658073747521e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.823113749160286e-08</v>
+        <v>1.228494275186043e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.985309546043713e-08</v>
+        <v>1.054301063289389e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.822279023786793e-08</v>
+        <v>9.625444785759071e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>2.865163074516794e-08</v>
+        <v>1.001897110450446e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.077503083799419e-08</v>
+        <v>1.354162223690247e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.06778295319039e-08</v>
+        <v>1.357210894858602e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.120799462549881e-08</v>
+        <v>1.397642421752916e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.087594701712489e-08</v>
+        <v>1.381772391102311e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.087594701712489e-08</v>
+        <v>1.381772391102311e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.099693827246591e-08</v>
+        <v>1.380706761845174e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.128270524059556e-08</v>
+        <v>1.404929663950377e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.082348030699285e-08</v>
+        <v>1.380844683593757e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.160470195655924e-08</v>
+        <v>1.437129335546744e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.083937170317624e-08</v>
+        <v>1.360596310208449e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.122535518558092e-08</v>
+        <v>1.399194658448918e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.464429532211349e-07</v>
+        <v>3.037917648509914e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.324831270214559e-07</v>
+        <v>4.556984113336417e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.507923333385382e-07</v>
+        <v>4.910326764068562e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.09082136144998e-07</v>
+        <v>4.166201304665161e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.49252261040792e-07</v>
+        <v>3.113195508536955e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.327323844343234e-07</v>
+        <v>4.57925059696222e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.330181514025748e-07</v>
+        <v>4.603473499069567e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.325589264688503e-07</v>
+        <v>4.579388518710807e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.333570628651732e-07</v>
+        <v>4.635970870205091e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.449085456437666e-07</v>
+        <v>3.016213762591705e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.228655267956068e-07</v>
+        <v>6.180061652879752e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.060049609252535e-07</v>
+        <v>2.326208987958871e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.321856134244744e-07</v>
+        <v>2.791747883594661e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.327180193596884e-07</v>
+        <v>2.83221884930125e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>1.626553897403411e-07</v>
+        <v>3.349090572370801e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.323312989147203e-07</v>
+        <v>2.815386576731802e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.325047221650365e-07</v>
+        <v>2.815243750581234e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.327904891331663e-07</v>
+        <v>2.839466652686434e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.323312641995635e-07</v>
+        <v>2.815381672329811e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.331124858491299e-07</v>
+        <v>2.871666324282801e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.171216681162163e-07</v>
+        <v>2.212775506398766e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.327331390781517e-07</v>
+        <v>2.833731647184975e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3290,31 +3290,31 @@
         <v>1.236360549604841e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.986444727906919e-09</v>
+        <v>9.986444727906915e-09</v>
       </c>
       <c r="D2" t="n">
         <v>1.305173558019141e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.063467247838516e-08</v>
+        <v>1.063467247838515e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.063467247838516e-08</v>
+        <v>1.063467247838515e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.272546131180706e-08</v>
+        <v>1.272546131180704e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.292672838597696e-08</v>
+        <v>1.292672838597695e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.275692610366723e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.193064881037019e-08</v>
+        <v>1.193064881037017e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.24456808850239e-08</v>
+        <v>1.244568088502389e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.272060923494674e-08</v>
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.317272875422184e-08</v>
+        <v>1.317272875422183e-08</v>
       </c>
       <c r="C3" t="n">
         <v>1.081351513346684e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.39642208967038e-08</v>
+        <v>1.396422089670378e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.150333848323067e-08</v>
+        <v>1.150333848323065e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.150333848323067e-08</v>
+        <v>1.150333848323065e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.35889379005507e-08</v>
+        <v>1.358893790055069e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.38379104398073e-08</v>
+        <v>1.383791043980729e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.36273496037671e-08</v>
+        <v>1.362734960376709e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.285400074902072e-08</v>
+        <v>1.285400074902071e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.326408756184448e-08</v>
+        <v>1.326408756184446e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35835643325819e-08</v>
+        <v>1.358356433258188e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.513387389480496e-08</v>
+        <v>7.308001388493263e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.438880985953859e-08</v>
+        <v>7.25862495720149e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.554293807128286e-08</v>
+        <v>7.717065564971164e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.516262076233591e-08</v>
+        <v>7.507232735070738e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.516262076233591e-08</v>
+        <v>7.507232735070741e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.529601281471271e-08</v>
+        <v>7.513786788701426e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.546918005400326e-08</v>
+        <v>7.643307547691538e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.510376311530309e-08</v>
+        <v>7.496827440769815e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.558594365677016e-08</v>
+        <v>7.760071150458457e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.517061381721779e-08</v>
+        <v>7.344741310906084e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.534709733812807e-08</v>
+        <v>7.521224831816378e-09</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.632850039886213e-08</v>
+        <v>1.631825560438432e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.391447113028314e-07</v>
+        <v>2.921566349224487e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.650120475183928e-07</v>
+        <v>3.402362868511762e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.498590158844056e-07</v>
+        <v>3.121379814809837e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.498590158844056e-07</v>
+        <v>3.121379814809837e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.491152645599605e-07</v>
+        <v>3.106597496824473e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.731308850275468e-07</v>
+        <v>3.539176747267723e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.498589596362509e-07</v>
+        <v>3.121374189994382e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.754499210400468e-07</v>
+        <v>3.589613101745704e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.311525344311629e-07</v>
+        <v>2.775755922835141e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.630108860764663e-07</v>
+        <v>3.351005150894067e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.296615223351295e-08</v>
+        <v>1.220648234956294e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.855897168870841e-08</v>
+        <v>9.752573425621628e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>2.916178559981171e-08</v>
+        <v>1.011398271700429e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.759069951575401e-08</v>
+        <v>9.694574583819952e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.87353902123651e-08</v>
+        <v>9.896040145331882e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>4.312829115342071e-08</v>
+        <v>1.241226774977083e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.518044741530162e-08</v>
+        <v>1.287249057494518e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.86951916653615e-08</v>
+        <v>9.8889188526182e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>4.385900599427619e-08</v>
+        <v>1.273613009489623e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.874139013018265e-08</v>
+        <v>9.733197929045991e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>2.895028332733979e-08</v>
+        <v>9.915385552944623e-09</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.173530778120099e-08</v>
+        <v>1.374985371759311e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.167941562686831e-08</v>
+        <v>1.382177153668843e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.214213776931393e-08</v>
+        <v>1.415852467692092e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.175981129258512e-08</v>
+        <v>1.394833823349281e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.175981129258512e-08</v>
+        <v>1.394833823349281e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.189744670110872e-08</v>
+        <v>1.3955639117801e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.207061394039927e-08</v>
+        <v>1.408515987679138e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.170519700169911e-08</v>
+        <v>1.393867976986957e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.21873775431662e-08</v>
+        <v>1.420192347955831e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.177204770361384e-08</v>
+        <v>1.378659364000593e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.194853122452406e-08</v>
+        <v>1.396307716091621e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.47689314326689e-07</v>
+        <v>3.063775877809011e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.343929865191758e-07</v>
+        <v>4.597935983948534e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.527611236048741e-07</v>
+        <v>4.946746599265441e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.107023199621135e-07</v>
+        <v>4.192221960775047e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.504409997226874e-07</v>
+        <v>3.131622730308116e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.345389758243459e-07</v>
+        <v>4.610054806931026e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.347121430638404e-07</v>
+        <v>4.623006882833646e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.343467261249362e-07</v>
+        <v>4.608358872137883e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.348459432586091e-07</v>
+        <v>4.634983087127948e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.461157890106582e-07</v>
+        <v>3.039109202007256e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.251424263833528e-07</v>
+        <v>6.204520244833215e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.024435660675446e-07</v>
+        <v>2.267450712763044e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.276057748461889e-07</v>
+        <v>2.71848106868798e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.280707414374053e-07</v>
+        <v>2.752195885009381e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>1.567327539557478e-07</v>
+        <v>3.242357604209947e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.276315952250433e-07</v>
+        <v>2.730177213324848e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.278238059204292e-07</v>
+        <v>2.731867826799239e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.279969731597197e-07</v>
+        <v>2.744819902698275e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.276315562210195e-07</v>
+        <v>2.730171892006094e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.281137367624867e-07</v>
+        <v>2.756496262974972e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.130869445187312e-07</v>
+        <v>2.447368158261941e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.278748904438445e-07</v>
+        <v>2.732611631110758e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.206331430969987e-08</v>
+        <v>1.20633143096998e-08</v>
       </c>
       <c r="C2" t="n">
         <v>9.703224222653484e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.305454099449373e-08</v>
+        <v>1.305454099449376e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.063791734365459e-08</v>
+        <v>1.063791734365443e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.063791734365459e-08</v>
+        <v>1.063791734365445e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.290047661788507e-08</v>
+        <v>1.290047661788505e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.790729600573888e-08</v>
+        <v>1.790729600573886e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.26379469608866e-08</v>
+        <v>1.263794696088657e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.155220536720352e-08</v>
+        <v>1.155220536720344e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.237542446203796e-08</v>
+        <v>1.237542446203799e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.545634206786562e-08</v>
+        <v>1.545634206786561e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.282706551359752e-08</v>
+        <v>1.282706551359728e-08</v>
       </c>
       <c r="C3" t="n">
         <v>1.046533751663934e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.396718153309962e-08</v>
+        <v>1.396718153309945e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.148842952104814e-08</v>
+        <v>1.148842952104822e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.148842952104814e-08</v>
+        <v>1.148842952104796e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.378997558566018e-08</v>
+        <v>1.378997558565994e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.956726063286606e-08</v>
+        <v>1.956726063286607e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.348995711616526e-08</v>
+        <v>1.348995711616506e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.241018702576606e-08</v>
+        <v>1.241018702576593e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.316573902298478e-08</v>
+        <v>1.316573902298477e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.672982606868507e-08</v>
+        <v>1.672982606868506e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.452660971568663e-08</v>
+        <v>7.129320759723848e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.366075736001586e-08</v>
+        <v>6.991671755148476e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.511585197795914e-08</v>
+        <v>7.718563021996231e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.463591024701815e-08</v>
+        <v>7.431489560555355e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.463591024701816e-08</v>
+        <v>7.431489560555356e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.497063009367341e-08</v>
+        <v>7.617538141660014e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.800004543426368e-08</v>
+        <v>1.060275647830077e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.459967642791914e-08</v>
+        <v>7.425032473877185e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.48995347904782e-08</v>
+        <v>7.502245834515147e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.463173647061456e-08</v>
+        <v>7.234447514651421e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.654403676851766e-08</v>
+        <v>9.146747812555081e-09</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.29356298087894e-08</v>
+        <v>1.564930824994353e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.31731463173828e-07</v>
+        <v>2.777211586577842e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.847427755837536e-07</v>
+        <v>3.757290141484726e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.617842593342767e-07</v>
+        <v>3.332959885958149e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.617842593342767e-07</v>
+        <v>3.332959885958149e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.785426297436399e-07</v>
+        <v>3.640620992405931e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>5.196756201239067e-07</v>
+        <v>9.889765714524266e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.617841623263262e-07</v>
+        <v>3.33295018516309e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.698952541902088e-07</v>
+        <v>3.478149230105231e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.381786622253403e-07</v>
+        <v>2.897870632965957e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.663397486054377e-07</v>
+        <v>7.071079276226159e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.367947035119656e-08</v>
+        <v>9.670892595441067e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>2.866848995161613e-08</v>
+        <v>9.633032676957673e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>2.959758176904107e-08</v>
+        <v>1.026734745141567e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.788390039487297e-08</v>
+        <v>9.763135813943548e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.908211896872906e-08</v>
+        <v>9.974022281799496e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>4.412349072918325e-08</v>
+        <v>1.274844158570744e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.86825194050573e-08</v>
+        <v>1.600287186789942e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.90404255727435e-08</v>
+        <v>1.255593591792457e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.443190365070178e-08</v>
+        <v>1.26999427257503e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.903004140883872e-08</v>
+        <v>9.768549170047611e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>3.105730383884224e-08</v>
+        <v>1.170108280309126e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.243643467081823e-08</v>
+        <v>1.380144991567335e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.229845330636802e-08</v>
+        <v>1.379190620485868e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.302332233211005e-08</v>
+        <v>1.439027776817554e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.255819053023909e-08</v>
+        <v>1.410581085423674e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.255819053023909e-08</v>
+        <v>1.410581085423674e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.288045504880504e-08</v>
+        <v>1.428966729760953e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.590987038939515e-08</v>
+        <v>1.72748856342502e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.250950138305075e-08</v>
+        <v>1.409716162982671e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.280935974560957e-08</v>
+        <v>1.417437499046472e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.254156142574586e-08</v>
+        <v>1.390657667060097e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.445386172364954e-08</v>
+        <v>1.581887696850461e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.533088912316847e-07</v>
+        <v>3.155500217418637e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.437368493993359e-07</v>
+        <v>4.748506373465103e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.631623529812825e-07</v>
+        <v>5.137474696202544e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.191896584509913e-07</v>
+        <v>4.343294904937698e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.562811168411e-07</v>
+        <v>3.236104578603035e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.442516318994526e-07</v>
+        <v>4.797099424081792e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.47281047240085e-07</v>
+        <v>5.095621257746582e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.438806782336986e-07</v>
+        <v>4.7778488573035e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.441983222011184e-07</v>
+        <v>4.785883220011146e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.517329577938294e-07</v>
+        <v>3.136426233678742e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.403585193096571e-07</v>
+        <v>6.613809643098225e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.169395361853665e-07</v>
+        <v>2.515399572071883e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.461333081069126e-07</v>
+        <v>3.030684056026662e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.468605386088941e-07</v>
+        <v>3.090562774339922e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>1.801926524743555e-07</v>
+        <v>3.65694760346795e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.463444305589933e-07</v>
+        <v>3.061218900985595e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.467153098493495e-07</v>
+        <v>3.080460165301752e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.497447251899397e-07</v>
+        <v>3.378981998965825e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.463443561835952e-07</v>
+        <v>3.061209598523467e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.46644214546154e-07</v>
+        <v>3.068930934587263e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.286919800061944e-07</v>
+        <v>2.743040333460538e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.482887165241941e-07</v>
+        <v>3.233381132391255e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.257900105354381e-08</v>
+        <v>1.257900105354376e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.917250620845058e-09</v>
+        <v>9.917250620845065e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.325289181287598e-08</v>
+        <v>1.325289181287596e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.070047819680555e-08</v>
+        <v>1.070047819680556e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.070047819680555e-08</v>
+        <v>1.070047819680556e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.292476129571325e-08</v>
+        <v>1.29247612957132e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.314049669977476e-08</v>
+        <v>1.314049669977477e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.305661938225058e-08</v>
+        <v>1.305661938225066e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.185961435754811e-08</v>
+        <v>1.185961435754816e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.247737688334225e-08</v>
+        <v>1.247737688334223e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.28901634892912e-08</v>
+        <v>1.289016348929122e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4119,19 +4119,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.337377894391247e-08</v>
+        <v>1.337377894391251e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.071996272093378e-08</v>
+        <v>1.071996272093379e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.414889291319481e-08</v>
+        <v>1.414889291319479e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.15674594219807e-08</v>
+        <v>1.156745942198065e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.15674594219807e-08</v>
+        <v>1.156745942198065e-08</v>
       </c>
       <c r="G3" t="n">
         <v>1.377147484642578e-08</v>
@@ -4140,13 +4140,13 @@
         <v>1.403750746510073e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.392568132597556e-08</v>
+        <v>1.392568132597552e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.277304949488747e-08</v>
+        <v>1.277304949488744e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.32879459862156e-08</v>
+        <v>1.328794598621558e-08</v>
       </c>
       <c r="L3" t="n">
         <v>1.373188708915453e-08</v>
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.465568669192417e-08</v>
+        <v>7.208640746080827e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.388277324722321e-08</v>
+        <v>7.120167618865884e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.505628619317346e-08</v>
+        <v>7.609240247330088e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.479107975101218e-08</v>
+        <v>7.467928638284443e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.479107975101218e-08</v>
+        <v>7.467928638284445e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.480841498357965e-08</v>
+        <v>7.404885731263712e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.499001748456766e-08</v>
+        <v>7.542971538724346e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.467645977177845e-08</v>
+        <v>7.447719913044914e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.512528288413613e-08</v>
+        <v>7.678236938292497e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.471818176451242e-08</v>
+        <v>7.271135818669187e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.484165982429363e-08</v>
+        <v>7.394613878450285e-09</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.595131978064477e-08</v>
+        <v>1.62366721207763e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.348361912331501e-07</v>
+        <v>2.840796906903888e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.638337222458091e-07</v>
+        <v>3.379406885070882e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.541093035449281e-07</v>
+        <v>3.198793589314912e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.541093035449281e-07</v>
+        <v>3.198793589314912e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.47806307079649e-07</v>
+        <v>3.081251461333545e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.726110614925462e-07</v>
+        <v>3.528427513380939e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.541092603301172e-07</v>
+        <v>3.198789267833879e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.767379393930987e-07</v>
+        <v>3.612206432974415e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.331281876185509e-07</v>
+        <v>2.811129673605522e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.596967296995373e-07</v>
+        <v>3.288910603834863e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.217099780053658e-08</v>
+        <v>9.592557310123458e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>2.799238623354033e-08</v>
+        <v>9.603459491001745e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>2.863668454909349e-08</v>
+        <v>9.999415856686137e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>2.715605427532685e-08</v>
+        <v>9.644164142771666e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.826664656116489e-08</v>
+        <v>9.839628384020018e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>2.835339553448918e-08</v>
+        <v>9.788802295306308e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>4.408572379924598e-08</v>
+        <v>1.266381582235995e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.822144032268828e-08</v>
+        <v>1.229041464192007e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.949928867897045e-08</v>
+        <v>1.258749986553287e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.824985561298819e-08</v>
+        <v>9.652710403096136e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>2.839713039082668e-08</v>
+        <v>9.780376685232679e-09</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.094071963745829e-08</v>
+        <v>1.359480650989078e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.084379580798379e-08</v>
+        <v>1.362530755431095e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.133908948197263e-08</v>
+        <v>1.399501359155683e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.102805060229298e-08</v>
+        <v>1.384563547355162e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.102805060229298e-08</v>
+        <v>1.384563547355162e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.109344792911367e-08</v>
+        <v>1.379105149507366e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.127505043010183e-08</v>
+        <v>1.392913730253438e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.09614927173129e-08</v>
+        <v>1.383388567685485e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.141031582966999e-08</v>
+        <v>1.406440270210246e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.100321471004673e-08</v>
+        <v>1.365730158247913e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.112669276982781e-08</v>
+        <v>1.378077964226028e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.465569261447805e-07</v>
+        <v>3.042325876399272e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.326670281537433e-07</v>
+        <v>4.562619627376447e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.509395229762078e-07</v>
+        <v>4.912468969618829e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.09221289827215e-07</v>
+        <v>4.168764542627292e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.493487397268871e-07</v>
+        <v>3.115007666571416e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.32833343744021e-07</v>
+        <v>4.57772729851765e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.330149462451298e-07</v>
+        <v>4.591535879265837e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.327013885322194e-07</v>
+        <v>4.582010716695765e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.331671374295404e-07</v>
+        <v>4.605360313034287e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.450196294712762e-07</v>
+        <v>3.020419049079439e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.22829983624358e-07</v>
+        <v>6.160055857354095e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.060131119630086e-07</v>
+        <v>2.328754750666648e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.321892225563532e-07</v>
+        <v>2.794210258444688e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.326867559607692e-07</v>
+        <v>2.831220281424582e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>1.626254749851988e-07</v>
+        <v>3.348678205851535e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.323069455226362e-07</v>
+        <v>2.81507209020184e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.32438874677483e-07</v>
+        <v>2.810784652520954e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.326204771784712e-07</v>
+        <v>2.82459323326703e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.323069194656822e-07</v>
+        <v>2.81506807069908e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.327557425780396e-07</v>
+        <v>2.838119773223835e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>9.92661987891473e-08</v>
+        <v>2.529490229132907e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.324721195181973e-07</v>
+        <v>2.80975746723962e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4484,16 +4484,16 @@
         <v>1.309132526562569e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.064904977145341e-08</v>
+        <v>1.064904977145343e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.064904977145341e-08</v>
+        <v>1.064904977145343e-08</v>
       </c>
       <c r="G2" t="n">
         <v>1.280418138424921e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.300826418668226e-08</v>
+        <v>1.300826418668227e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.285114127549325e-08</v>
@@ -4502,7 +4502,7 @@
         <v>1.197583527254516e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2505404069807e-08</v>
+        <v>1.250540406980697e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.280048479362851e-08</v>
@@ -4515,34 +4515,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.328958135130796e-08</v>
+        <v>1.328958135130797e-08</v>
       </c>
       <c r="C3" t="n">
         <v>1.088136891045876e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.401612299048039e-08</v>
+        <v>1.40161229904804e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.153823300199914e-08</v>
+        <v>1.153823300199915e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.153823300199914e-08</v>
+        <v>1.153823300199915e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.36858480452216e-08</v>
+        <v>1.368584804522163e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.39379954157204e-08</v>
+        <v>1.393799541572041e-08</v>
       </c>
       <c r="I3" t="n">
         <v>1.374248394292673e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.292812400786478e-08</v>
+        <v>1.292812400786477e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.334896493098126e-08</v>
+        <v>1.334896493098123e-08</v>
       </c>
       <c r="L3" t="n">
         <v>1.368180512007601e-08</v>
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.510447012285262e-08</v>
+        <v>7.308371112004372e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.435127462140171e-08</v>
+        <v>7.248525496792053e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.547996615288649e-08</v>
+        <v>7.683867142038242e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.518797406755699e-08</v>
+        <v>7.516335874346423e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.518797406755701e-08</v>
+        <v>7.516335874346428e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.525569910346117e-08</v>
+        <v>7.503743568378678e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.543114356541005e-08</v>
+        <v>7.63504455456181e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.506915815479238e-08</v>
+        <v>7.495378943073399e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.558876417545969e-08</v>
+        <v>7.792665164611458e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.515846432450658e-08</v>
+        <v>7.362365313658341e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.530807076433761e-08</v>
+        <v>7.511971753489355e-09</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.676222489960359e-08</v>
+        <v>1.640013590344786e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.385435268667155e-07</v>
+        <v>2.910636177352823e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.623374749594569e-07</v>
+        <v>3.353078855194046e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.50167849724309e-07</v>
+        <v>3.127279386120735e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.50167849724309e-07</v>
+        <v>3.127279386120735e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.485632776105882e-07</v>
+        <v>3.096587725850077e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.727020615456174e-07</v>
+        <v>3.531472596909309e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.501677947112753e-07</v>
+        <v>3.127273884817457e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.790012866456813e-07</v>
+        <v>3.655326896352806e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.331568228181582e-07</v>
+        <v>2.813007629600898e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.624690694392404e-07</v>
+        <v>3.341230737992864e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.284851703239363e-08</v>
+        <v>9.687029477501432e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>2.844176688250914e-08</v>
+        <v>9.728452121309261e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>2.901963265071486e-08</v>
+        <v>1.006684843274358e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.749676589513759e-08</v>
+        <v>9.682683224262011e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.862825749391379e-08</v>
+        <v>9.881825744567545e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>4.299974601300221e-08</v>
+        <v>1.238669579799912e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.500863181444263e-08</v>
+        <v>1.284068245818426e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.858426257744063e-08</v>
+        <v>1.237833117269382e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.376472278175073e-08</v>
+        <v>1.031863071493363e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.865689129993976e-08</v>
+        <v>9.738088448461476e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>2.883820833338551e-08</v>
+        <v>9.893275952738367e-09</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.177181741482163e-08</v>
+        <v>1.37618242004222e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.17050600496384e-08</v>
+        <v>1.382279169653838e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.214507993376064e-08</v>
+        <v>1.41369271325055e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.180832019488327e-08</v>
+        <v>1.396151675783194e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.180832019488327e-08</v>
+        <v>1.396151675783194e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.19230463954302e-08</v>
+        <v>1.39571966567965e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.209849085737908e-08</v>
+        <v>1.408849764297963e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.173650544676143e-08</v>
+        <v>1.394883203149124e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.225611146742871e-08</v>
+        <v>1.424611825302927e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.182581161647567e-08</v>
+        <v>1.381581840207616e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.197541805630659e-08</v>
+        <v>1.396542484190718e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.476380139375843e-07</v>
+        <v>3.063427469700336e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.343291421812489e-07</v>
+        <v>4.596462997753791e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.526543816395224e-07</v>
+        <v>4.942656404149906e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.106473549502644e-07</v>
+        <v>4.191718672329833e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.503941838754111e-07</v>
+        <v>3.131262867158606e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.344586487014362e-07</v>
+        <v>4.608346248857413e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.346340931635857e-07</v>
+        <v>4.621476347479249e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.342721077527675e-07</v>
+        <v>4.607509786326878e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.348087468060016e-07</v>
+        <v>4.637538189852236e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.460820794294712e-07</v>
+        <v>3.040492144727356e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.250444618919301e-07</v>
+        <v>6.202557629655807e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.023888492607684e-07</v>
+        <v>2.267042175703663e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.275313626660714e-07</v>
+        <v>2.716822088471698e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.279736262573675e-07</v>
+        <v>2.748275121314452e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>1.566538147677431e-07</v>
+        <v>3.241432370266672e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.27562845898798e-07</v>
+        <v>2.729431320947583e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.277493490118633e-07</v>
+        <v>2.730262584497515e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.27924793473812e-07</v>
+        <v>2.743392683115824e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.275628080631945e-07</v>
+        <v>2.729426121966985e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.280824140838616e-07</v>
+        <v>2.759154744120785e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.124531697028777e-07</v>
+        <v>2.448623336746414e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.278017206727395e-07</v>
+        <v>2.731085403008575e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4874,7 +4874,7 @@
         <v>1.771459907632718e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.237585206017734e-08</v>
+        <v>1.237585206017735e-08</v>
       </c>
       <c r="D2" t="n">
         <v>2.049773754710638e-08</v>
@@ -4889,13 +4889,13 @@
         <v>1.77813230064116e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.911132806803279e-08</v>
+        <v>2.911132806803282e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.38411130297236e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.559483223398556e-08</v>
+        <v>1.559483223398554e-08</v>
       </c>
       <c r="K2" t="n">
         <v>1.459619187563124e-08</v>
@@ -4911,25 +4911,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.931721228615588e-08</v>
+        <v>1.931721228615589e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.338869220229865e-08</v>
+        <v>1.338869220229864e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.251839805294933e-08</v>
+        <v>2.251839805294934e-08</v>
       </c>
       <c r="E3" t="n">
         <v>1.370708417612333e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.259715616177088e-08</v>
+        <v>1.259715616177087e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.939395862757342e-08</v>
+        <v>1.939395862757343e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.244352571761366e-08</v>
+        <v>3.244352571761369e-08</v>
       </c>
       <c r="I3" t="n">
         <v>1.486034229345187e-08</v>
@@ -4938,10 +4938,10 @@
         <v>1.686735366909542e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.581143524006129e-08</v>
+        <v>1.581143524006128e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.761940455089019e-08</v>
+        <v>3.76194045508902e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.889091092708295e-08</v>
+        <v>1.059963346091396e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.588077935735048e-08</v>
+        <v>8.173596603698607e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>2.054536881638031e-08</v>
+        <v>1.225409135021135e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.602474602204643e-08</v>
+        <v>8.198936453927121e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.602474602204645e-08</v>
+        <v>8.198936453927121e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.887001464263262e-08</v>
+        <v>1.062863930336887e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.566376289690204e-08</v>
+        <v>1.737248543073304e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.627449784768932e-08</v>
+        <v>8.242398093422759e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.758454452767649e-08</v>
+        <v>9.293267061507516e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.735786166948446e-08</v>
+        <v>9.066584203315466e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>2.834779179485957e-08</v>
+        <v>2.005651432869051e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.322516159577651e-07</v>
+        <v>8.335111715210258e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.200085787327407e-07</v>
+        <v>4.41000890990958e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.997594819613776e-07</v>
+        <v>1.141957747113493e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>2.200085808169383e-07</v>
+        <v>4.410009118329398e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.200085808169381e-07</v>
+        <v>4.410009118329398e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.523879565629747e-07</v>
+        <v>8.692779666791406e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2328754638019e-06</v>
+        <v>2.298417436387264e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.20007980475217e-07</v>
+        <v>4.409949084157216e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.275973687832036e-07</v>
+        <v>6.385552383482893e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.911897885923987e-07</v>
+        <v>5.726100308060181e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.148591920884313e-07</v>
+        <v>7.04825205071206e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.091816421633652e-08</v>
+        <v>1.623643000927902e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.146973017742266e-08</v>
+        <v>1.091725193316454e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.66127204398145e-08</v>
+        <v>1.508194522061272e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.030631537507896e-08</v>
+        <v>1.071249264644087e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.184480093368386e-08</v>
+        <v>1.098326610328813e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.445027801298666e-08</v>
+        <v>1.626543585173392e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.156020824326053e-08</v>
+        <v>2.314973615559761e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.830175113694294e-08</v>
+        <v>1.387919464178783e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.974611840625155e-08</v>
+        <v>1.495370403346508e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.280340964336178e-08</v>
+        <v>1.178500063198786e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.433303818825408e-08</v>
+        <v>2.286991767868324e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.781790677192567e-08</v>
+        <v>1.745078469248261e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.520209195005568e-08</v>
+        <v>1.5094147582515e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.946983090499241e-08</v>
+        <v>1.910479664068581e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.519290923243291e-08</v>
+        <v>1.509253314160145e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.519290923243291e-08</v>
+        <v>1.509253314160145e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.779701048747537e-08</v>
+        <v>1.747979053493751e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.459075874174477e-08</v>
+        <v>2.422363666230167e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.520149369253196e-08</v>
+        <v>1.509354932499139e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.651154037251929e-08</v>
+        <v>1.614441829307615e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.628485751432722e-08</v>
+        <v>1.59177354348841e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.727478763970225e-08</v>
+        <v>2.690766556025917e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.606574656326714e-07</v>
+        <v>3.555054695389845e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.504508385461118e-07</v>
+        <v>4.945792679721721e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.738675353579544e-07</v>
+        <v>5.683879241994161e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.251791687047424e-07</v>
+        <v>4.501011464661643e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.609665141071096e-07</v>
+        <v>3.370868749867102e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.530331485731783e-07</v>
+        <v>5.184135065182953e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.598268968274485e-07</v>
+        <v>5.858519677919395e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.504376317782355e-07</v>
+        <v>4.945510944188346e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.517658370468399e-07</v>
+        <v>5.05091743215477e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.574081024782709e-07</v>
+        <v>3.371542645209961e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.590268788147304e-07</v>
+        <v>7.825603332882769e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.292095729729462e-07</v>
+        <v>3.001571787577781e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.581126192697322e-07</v>
+        <v>3.320640029263495e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.623828962841108e-07</v>
+        <v>3.721749604926507e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>1.944846807467284e-07</v>
+        <v>3.960788479527843e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.581125878176592e-07</v>
+        <v>3.320639647444944e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.607075378071518e-07</v>
+        <v>3.559204324505743e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.675012860614213e-07</v>
+        <v>4.23358893724216e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.581120210122086e-07</v>
+        <v>3.320580203511135e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.594220676921957e-07</v>
+        <v>3.42566710031961e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.409332347276506e-07</v>
+        <v>3.081584974370207e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.701853149593788e-07</v>
+        <v>4.50199182703791e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5270,34 +5270,34 @@
         <v>1.672876203507606e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.321689868574275e-08</v>
+        <v>1.321689868574274e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.003169902396027e-08</v>
+        <v>2.003169902396019e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.35293762358919e-08</v>
+        <v>1.352937623589191e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.241094569865644e-08</v>
+        <v>1.241094569865643e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.769423025335446e-08</v>
+        <v>1.769423025335431e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.700572210086013e-08</v>
+        <v>2.700572210086011e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.464200456530198e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.49208708155338e-08</v>
+        <v>1.492087081553379e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.47422793366257e-08</v>
+        <v>1.474227933662571e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.214427920186085e-08</v>
+        <v>3.214427920186074e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.818524788212205e-08</v>
+        <v>1.818524788212214e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.435155120454916e-08</v>
+        <v>1.435155120454914e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1984309620675e-08</v>
+        <v>2.198430962067484e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.467278267327742e-08</v>
+        <v>1.467278267327741e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.355435213604194e-08</v>
+        <v>1.355435213604193e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.929573632928126e-08</v>
+        <v>1.929573632928119e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.002293262543767e-08</v>
+        <v>3.002293262543766e-08</v>
       </c>
       <c r="I3" t="n">
         <v>1.578421096161955e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.608802647132673e-08</v>
+        <v>1.608802647132671e-08</v>
       </c>
       <c r="K3" t="n">
         <v>1.597694827830415e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.591579478666966e-08</v>
+        <v>3.59157947866697e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.834455420968386e-08</v>
+        <v>1.002189085973559e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.648754508050591e-08</v>
+        <v>8.674087907367402e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>2.030801029226312e-08</v>
+        <v>1.198534694231475e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.661841696550129e-08</v>
+        <v>8.697122971946288e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.66184169655013e-08</v>
+        <v>8.697122971946288e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.885990756711044e-08</v>
+        <v>1.058551132571444e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.445221763246846e-08</v>
+        <v>1.612955428252009e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.680318847359758e-08</v>
+        <v>8.729248057446661e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.719950525925522e-08</v>
+        <v>8.876841909306918e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.746669485605587e-08</v>
+        <v>9.144031506107543e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>2.750627550903771e-08</v>
+        <v>1.918361215908945e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.538460042267489e-07</v>
+        <v>6.90701457427799e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.447335818843965e-07</v>
+        <v>4.88453901671798e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.282614154605537e-07</v>
+        <v>1.01385145767511e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>2.447335838418534e-07</v>
+        <v>4.88453921246368e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.447335838418534e-07</v>
+        <v>4.88453921246368e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.134684042624267e-07</v>
+        <v>8.003660636776182e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.022334888296133e-06</v>
+        <v>1.917569033676699e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.447331048373051e-07</v>
+        <v>4.884491312008832e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.638234926184297e-07</v>
+        <v>5.228266344932268e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.709507989131915e-07</v>
+        <v>5.37572335784221e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.388705506297409e-06</v>
+        <v>7.228633886626511e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.280774889493104e-08</v>
+        <v>1.527331222610959e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.100099638475015e-08</v>
+        <v>1.122845532307327e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.517126552880025e-08</v>
+        <v>1.460127984976997e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9910786780334e-08</v>
+        <v>1.103658004668028e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.128234443822433e-08</v>
+        <v>1.127797419316095e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.332310225235752e-08</v>
+        <v>1.583693269208847e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.500203221367603e-08</v>
+        <v>2.150632161967805e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.126638315884467e-08</v>
+        <v>1.398066942382067e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.254106369734194e-08</v>
+        <v>1.415230501649335e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.181253771634742e-08</v>
+        <v>1.166889983583759e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.232122490270209e-08</v>
+        <v>2.179104323824574e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.490776017103498e-08</v>
+        <v>1.645701507406401e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.336687148204012e-08</v>
+        <v>1.516484931886654e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.686884670150665e-08</v>
+        <v>1.842005411547445e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.336248466192981e-08</v>
+        <v>1.516407885147586e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.336248466192981e-08</v>
+        <v>1.516407885147586e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.542311352846152e-08</v>
+        <v>1.702063554004294e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.10154235938195e-08</v>
+        <v>2.25646784968485e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.336639443494867e-08</v>
+        <v>1.516437227177507e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.376271122060636e-08</v>
+        <v>1.531196612363532e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.402990081740703e-08</v>
+        <v>1.557915572043596e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.406948147038878e-08</v>
+        <v>2.561873637341786e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.507422094329382e-07</v>
+        <v>3.332387805276406e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.355879289308355e-07</v>
+        <v>4.723575525611247e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.569860253246638e-07</v>
+        <v>5.364067736230342e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.119639618577147e-07</v>
+        <v>4.307793868667976e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.519379394317897e-07</v>
+        <v>3.251335879696225e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.376283725429018e-07</v>
+        <v>4.908876095281996e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.432206826082618e-07</v>
+        <v>5.463280390962581e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.355716534493894e-07</v>
+        <v>4.723249768455218e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.359849445862784e-07</v>
+        <v>4.738307902221291e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.482599679441861e-07</v>
+        <v>3.216364744488417e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.364962734926082e-07</v>
+        <v>7.356585150952195e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.153619949789569e-07</v>
+        <v>2.70969603426046e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.416297253149801e-07</v>
+        <v>3.069911150928986e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.451340753296047e-07</v>
+        <v>3.395473426984346e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>1.737202521946332e-07</v>
+        <v>3.634704582244948e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.416296980449832e-07</v>
+        <v>3.069910832271506e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.436859673614014e-07</v>
+        <v>3.25548977304663e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.492782774267596e-07</v>
+        <v>3.809894068727184e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.416292482678887e-07</v>
+        <v>3.069863446219842e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.420255650535462e-07</v>
+        <v>3.084622831405872e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.07276738118026e-07</v>
+        <v>2.495059903456477e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.523323353033284e-07</v>
+        <v>4.115299856384125e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.608664520365268e-08</v>
+        <v>1.608664520365262e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.493012813299792e-08</v>
+        <v>1.493012813299794e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.908683882398784e-08</v>
+        <v>1.908683882398787e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.524277559892831e-08</v>
+        <v>1.524277559892836e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.412253653574876e-08</v>
+        <v>1.412253653574874e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.718537056139731e-08</v>
+        <v>1.718537056139727e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.462790139365836e-08</v>
+        <v>2.462790139365832e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.628649970388829e-08</v>
+        <v>1.628649970388828e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.499571787002354e-08</v>
+        <v>1.499571787002352e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.460148395156017e-08</v>
+        <v>1.460148395156016e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.029043495936404e-08</v>
+        <v>3.029043495936424e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.744505851893315e-08</v>
+        <v>1.744505851893307e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.630991298713453e-08</v>
+        <v>1.630991298713458e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.089590267055474e-08</v>
+        <v>2.089590267055475e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.663163641150289e-08</v>
+        <v>1.663163641150286e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.551139734832327e-08</v>
+        <v>1.551139734832332e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.870882028061154e-08</v>
+        <v>1.870882028061165e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.72857932725603e-08</v>
+        <v>2.728579327256022e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.767570780233448e-08</v>
+        <v>1.767570780233456e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.616423050546675e-08</v>
+        <v>1.616423050546665e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.580899832769327e-08</v>
+        <v>1.580899832769324e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.378192911609656e-08</v>
+        <v>3.378192911609643e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.835606396505741e-08</v>
+        <v>9.715481373588648e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.800244831123739e-08</v>
+        <v>9.752534440147097e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>2.013955194335903e-08</v>
+        <v>1.14989693518902e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.812728849896567e-08</v>
+        <v>9.774507715038931e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.812728849896567e-08</v>
+        <v>9.774507715038918e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.895515201923694e-08</v>
+        <v>1.035911290180268e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.343235609925088e-08</v>
+        <v>1.479177350778207e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.82034106344542e-08</v>
+        <v>9.787752652397771e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.760451580068654e-08</v>
+        <v>8.963933209217702e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.775886852152935e-08</v>
+        <v>9.118285930060484e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>2.679775418542309e-08</v>
+        <v>1.815717159395415e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.14617136918024e-07</v>
+        <v>6.185742993077395e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.250774648658443e-07</v>
+        <v>6.379773706090822e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.685178892698121e-07</v>
+        <v>9.041355629373891e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.250774665672648e-07</v>
+        <v>6.379773876232865e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.250774665672648e-07</v>
+        <v>6.379773876232865e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.804623139367169e-07</v>
+        <v>7.398437305451783e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.480690881648883e-07</v>
+        <v>1.599278375648994e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>3.250772814235581e-07</v>
+        <v>6.379755361862161e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.641967032067396e-07</v>
+        <v>5.236415795751431e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.568320247683505e-07</v>
+        <v>5.119516120150315e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.253627332139002e-06</v>
+        <v>2.340791761437902e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.28666568411669e-08</v>
+        <v>1.226934570594547e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.266682215837327e-08</v>
+        <v>1.233346422325798e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.02294659549981e-08</v>
+        <v>1.679479418924269e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.15644707495195e-08</v>
+        <v>1.213945177832181e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.278631603605673e-08</v>
+        <v>1.235449654758712e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.346574489534631e-08</v>
+        <v>1.291297723415953e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.392989013958131e-08</v>
+        <v>2.015933946979547e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.801113371140481e-08</v>
+        <v>1.503391188551427e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.754062362548025e-08</v>
+        <v>1.167472547263741e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.214956473722097e-08</v>
+        <v>1.165104845029818e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.163214605124742e-08</v>
+        <v>2.07680245481921e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.509452249113609e-08</v>
+        <v>1.618145003914192e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.494205260281877e-08</v>
+        <v>1.625390476023716e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.687562784494079e-08</v>
+        <v>1.796451867553435e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.494748168274665e-08</v>
+        <v>1.625486168026996e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.494748168274665e-08</v>
+        <v>1.625486168026996e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.56936105453155e-08</v>
+        <v>1.682508156735588e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.017081462532946e-08</v>
+        <v>2.125774217333532e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.494186916053276e-08</v>
+        <v>1.625372131795109e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.434297432676507e-08</v>
+        <v>1.5429901874771e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.449732704760785e-08</v>
+        <v>1.558425459561378e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.353621271150169e-08</v>
+        <v>2.462314025950762e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.508572787138693e-07</v>
+        <v>3.303569504301643e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.37210259878334e-07</v>
+        <v>4.833310906690314e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.5705323295777e-07</v>
+        <v>5.319577698448788e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.135553638278414e-07</v>
+        <v>4.416984878654635e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.534507592488636e-07</v>
+        <v>3.359143843796651e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.379365944554597e-07</v>
+        <v>4.889984656174076e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.424137985354779e-07</v>
+        <v>5.333250716772092e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.371848530706768e-07</v>
+        <v>4.832848631233589e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.36602954091828e-07</v>
+        <v>4.750765813960529e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.486536686409059e-07</v>
+        <v>3.215577062623972e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.361150258117166e-07</v>
+        <v>7.25970111051938e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.106688916467274e-07</v>
+        <v>2.596253895752612e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.370429404022962e-07</v>
+        <v>3.070366093464763e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.389789038925529e-07</v>
+        <v>3.241469518161426e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>1.676539537751972e-07</v>
+        <v>3.609120066105597e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.370429153243808e-07</v>
+        <v>3.070365792290529e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.377944983447929e-07</v>
+        <v>3.127483774176644e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.422717024248068e-07</v>
+        <v>3.570749834774584e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.370427569600103e-07</v>
+        <v>3.070347749236156e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.364438621262425e-07</v>
+        <v>2.987965804918153e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.212286481324222e-07</v>
+        <v>2.732896704290118e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.456371005109791e-07</v>
+        <v>3.907289643391799e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6059,34 +6059,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.272978810631349e-08</v>
+        <v>1.272978810631351e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.100369855519e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.433705516805333e-08</v>
+        <v>1.433705516805334e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.129918056279561e-08</v>
+        <v>1.129918056279557e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.023236141972942e-08</v>
+        <v>1.023236141972938e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.361922528295574e-08</v>
+        <v>1.361922528295567e-08</v>
       </c>
       <c r="H2" t="n">
         <v>1.733556426644123e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.247353224648822e-08</v>
+        <v>1.247353224648819e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.409764696968284e-08</v>
+        <v>1.409764696968274e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.25162585439782e-08</v>
+        <v>1.251625854397818e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.692531803263927e-08</v>
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.357580166304463e-08</v>
+        <v>1.357580166304458e-08</v>
       </c>
       <c r="C3" t="n">
         <v>1.180364900579631e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.542449172841426e-08</v>
+        <v>1.542449172841418e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.21071196707818e-08</v>
+        <v>1.210711967078177e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.104030052771561e-08</v>
+        <v>1.104030052771559e-08</v>
       </c>
       <c r="G3" t="n">
         <v>1.459883866253915e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.889101919925964e-08</v>
+        <v>1.889101919925963e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.328144566751056e-08</v>
+        <v>1.32814456675105e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.514649434084718e-08</v>
+        <v>1.514649434084711e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.341784148066614e-08</v>
+        <v>1.341784148066607e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.840154363279466e-08</v>
+        <v>1.840154363279467e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.521442452243435e-08</v>
+        <v>7.531888352584277e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.452875027205607e-08</v>
+        <v>7.287045482993552e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.616987668495603e-08</v>
+        <v>8.487340515105955e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.465800836216798e-08</v>
+        <v>7.309796412555734e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.465800836216798e-08</v>
+        <v>7.309796412555738e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.568869221461586e-08</v>
+        <v>8.051035221859725e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.795208491005162e-08</v>
+        <v>1.026954874020152e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.478783992841407e-08</v>
+        <v>7.332468638952787e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.601715667189438e-08</v>
+        <v>8.334620502044309e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.543434509111032e-08</v>
+        <v>7.751808921260265e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.770874162513839e-08</v>
+        <v>1.002620545528832e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.681219016077126e-07</v>
+        <v>3.44436041737693e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.593756346930676e-07</v>
+        <v>3.278009700295486e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>2.583150687134605e-07</v>
+        <v>5.110489408119506e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.59375636520526e-07</v>
+        <v>3.278009883041323e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.59375636520526e-07</v>
+        <v>3.278009883041323e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.223871001945918e-07</v>
+        <v>4.442995482921254e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.584062829113673e-07</v>
+        <v>8.778948716838321e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.593754203443874e-07</v>
+        <v>3.277988265427463e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.553127695034976e-07</v>
+        <v>5.045064813219637e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.888757149485333e-07</v>
+        <v>3.827748985076016e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.844581726559606e-07</v>
+        <v>8.789248084693922e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.025216551957126e-08</v>
+        <v>1.017853075373925e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.968340445888517e-08</v>
+        <v>9.954264605422815e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>3.134843103323311e-08</v>
+        <v>1.380161014965575e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.85416855534532e-08</v>
+        <v>9.753323584981406e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.98414195209429e-08</v>
+        <v>9.982076762020073e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>4.561071520157651e-08</v>
+        <v>1.06976776230147e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.85314237195791e-08</v>
+        <v>1.565151234151566e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.470986291537469e-08</v>
+        <v>9.97911104010776e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>4.606190197270376e-08</v>
+        <v>1.362249564633386e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.047116593436998e-08</v>
+        <v>1.039828937533372e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.284430250893061e-08</v>
+        <v>1.269006415640134e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.305501880384453e-08</v>
+        <v>1.419183291002487e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.262864855850446e-08</v>
+        <v>1.399262754507359e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.400794309913091e-08</v>
+        <v>1.514684016791554e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.26268789117454e-08</v>
+        <v>1.399231759307145e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.26268789117454e-08</v>
+        <v>1.399231759307145e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.352928649602603e-08</v>
+        <v>1.471097977930032e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.579267919146183e-08</v>
+        <v>1.692949329764214e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.26284342098243e-08</v>
+        <v>1.399241319639337e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.385775095330456e-08</v>
+        <v>1.49945650594849e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.327493937252054e-08</v>
+        <v>1.441175347870085e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.554933590654857e-08</v>
+        <v>1.668615001272891e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.549488998272305e-07</v>
+        <v>3.212515587296721e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.454345070169474e-07</v>
+        <v>4.792645844984659e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.656441011719573e-07</v>
+        <v>5.239480378690107e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.205734457211986e-07</v>
+        <v>4.355091319136889e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.574041370808162e-07</v>
+        <v>3.243311493090455e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.463157480230753e-07</v>
+        <v>4.864139682420555e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.485791407185115e-07</v>
+        <v>5.085991034254745e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.454148957368736e-07</v>
+        <v>4.792283024129862e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.46662075490435e-07</v>
+        <v>4.892812599414733e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.534804440474774e-07</v>
+        <v>3.204792220592986e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.432806980964888e-07</v>
+        <v>6.73268694837564e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.19692663494438e-07</v>
+        <v>2.592005831201868e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.490773134888042e-07</v>
+        <v>3.096759248082573e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.504591435085933e-07</v>
+        <v>3.212225134799784e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>1.834785781913999e-07</v>
+        <v>3.702221654150074e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.49077291902842e-07</v>
+        <v>3.096759018752211e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.499779514263256e-07</v>
+        <v>3.168594471505246e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.522413441217614e-07</v>
+        <v>3.390445823339425e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.490770991401239e-07</v>
+        <v>3.096737813214551e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.503064158836041e-07</v>
+        <v>3.196952999523699e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.121862065998927e-07</v>
+        <v>2.834673748652982e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.519980008368483e-07</v>
+        <v>3.3661114948481e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6455,34 +6455,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.260765916960231e-08</v>
+        <v>1.260765916960241e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.139493485087925e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.293238189084613e-08</v>
+        <v>1.293238189084629e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.169126513861708e-08</v>
+        <v>1.169126513861702e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.062084954044761e-08</v>
+        <v>1.062084954044759e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.296493511622647e-08</v>
+        <v>1.296493511622655e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.265354482396115e-08</v>
+        <v>1.265354482396114e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.283355610758244e-08</v>
+        <v>1.283355610758255e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.364622755932701e-08</v>
+        <v>1.364622755932708e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.249295459317496e-08</v>
+        <v>1.249295459317489e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.241368429175276e-08</v>
@@ -6495,34 +6495,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.343806605142458e-08</v>
+        <v>1.343806605142469e-08</v>
       </c>
       <c r="C3" t="n">
         <v>1.225124862672149e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.381156444696403e-08</v>
+        <v>1.381156444696417e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.255605045874376e-08</v>
+        <v>1.255605045874391e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.148563486057428e-08</v>
+        <v>1.148563486057433e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.384900739953173e-08</v>
+        <v>1.384900739953191e-08</v>
       </c>
       <c r="H3" t="n">
         <v>1.3507944503067e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.369892607938819e-08</v>
+        <v>1.369892607938823e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.462551337012597e-08</v>
+        <v>1.462551337012592e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.339040140601858e-08</v>
+        <v>1.339040140601856e-08</v>
       </c>
       <c r="L3" t="n">
         <v>1.32151570600644e-08</v>
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.504865701732048e-08</v>
+        <v>7.447078430433229e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.473300408019704e-08</v>
+        <v>7.503631922430806e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.524169091543102e-08</v>
+        <v>7.640112328543785e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.484660502960179e-08</v>
+        <v>7.523627100810265e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.484660502960179e-08</v>
+        <v>7.523627100810265e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.520886327493493e-08</v>
+        <v>7.650280310653563e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.507658414971703e-08</v>
+        <v>7.475005562829811e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.492356069484619e-08</v>
+        <v>7.537107702547145e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.563785809802121e-08</v>
+        <v>8.03627951113395e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.531397327180582e-08</v>
+        <v>7.712394684918585e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.493446097058329e-08</v>
+        <v>7.332882383696041e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.510003068243225e-07</v>
+        <v>3.1374568666812e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.692275165293104e-07</v>
+        <v>3.46946659661373e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.755478609577128e-07</v>
+        <v>3.585399810310547e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.692275182421655e-07</v>
+        <v>3.469466767899235e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.692275182421654e-07</v>
+        <v>3.469466767899235e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.75666347787489e-07</v>
+        <v>3.589079743183871e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.782366960646157e-07</v>
+        <v>3.619118510425034e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.692274410634367e-07</v>
+        <v>3.46945905002634e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.126000460510014e-07</v>
+        <v>4.270162440302065e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.749115326104234e-07</v>
+        <v>3.58015649763112e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.610965429614492e-07</v>
+        <v>3.305740867469738e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.894284992406934e-08</v>
+        <v>1.230533097715128e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.876564660599652e-08</v>
+        <v>9.973376993588983e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>2.914503387365664e-08</v>
+        <v>1.008712909070204e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.769897210004975e-08</v>
+        <v>9.785643692952126e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.883784978479381e-08</v>
+        <v>9.986086164380971e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>2.910305618168379e-08</v>
+        <v>1.009565824899084e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.319789910151203e-08</v>
+        <v>9.920794567977318e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>2.881775360159509e-08</v>
+        <v>9.98248564088441e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>3.035516352705364e-08</v>
+        <v>1.291204620125395e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.923379278770653e-08</v>
+        <v>1.016228290644213e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.882564389269452e-08</v>
+        <v>9.777730564739954e-09</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.048562488948858e-08</v>
+        <v>1.368398474213951e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.036060403288826e-08</v>
+        <v>1.377408948012734e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.067629904965221e-08</v>
+        <v>1.387660332637365e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.036072455534148e-08</v>
+        <v>1.377411210347154e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.036072455534146e-08</v>
+        <v>1.377411210347154e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.064583114710303e-08</v>
+        <v>1.388718662235984e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.051355202188514e-08</v>
+        <v>1.371191187453607e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.036052856701432e-08</v>
+        <v>1.377401401425339e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.107482597018929e-08</v>
+        <v>1.42731858228402e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.075094114397392e-08</v>
+        <v>1.394930099662484e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.037142884275141e-08</v>
+        <v>1.356978869540231e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.452897888864112e-07</v>
+        <v>3.036951751518556e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.299575664708186e-07</v>
+        <v>4.538315469792606e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.478340734285736e-07</v>
+        <v>4.857637142903947e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.067701593698406e-07</v>
+        <v>4.130217248165966e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.478534219530882e-07</v>
+        <v>3.09328267524987e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.302230090987884e-07</v>
+        <v>4.549276977059831e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.300907299735697e-07</v>
+        <v>4.53174950227744e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.299377065186995e-07</v>
+        <v>4.537959716249182e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.306686642608701e-07</v>
+        <v>4.588170119072599e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.439804028829869e-07</v>
+        <v>3.035768617378059e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.18501108486307e-07</v>
+        <v>6.076061205695962e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.064273562842467e-07</v>
+        <v>2.352972941426666e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.32452478642586e-07</v>
+        <v>2.822225933314519e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.327705430385579e-07</v>
+        <v>2.832519019012982e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>1.626291776185723e-07</v>
+        <v>3.353335973553257e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.324524625555946e-07</v>
+        <v>2.82222579132273e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.327377057568007e-07</v>
+        <v>2.833535647537768e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.32605426631583e-07</v>
+        <v>2.816008172755392e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.324524031767121e-07</v>
+        <v>2.822218386727124e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.33166700579887e-07</v>
+        <v>2.872135567585807e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.170766085849653e-07</v>
+        <v>2.562261840298623e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.324633034524492e-07</v>
+        <v>2.801795854842015e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6851,34 +6851,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.303070338771554e-08</v>
+        <v>1.303070338771555e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.164697103989864e-08</v>
+        <v>1.164697103989865e-08</v>
       </c>
       <c r="D2" t="n">
         <v>1.322838813834859e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.194835774778808e-08</v>
+        <v>1.194835774778809e-08</v>
       </c>
       <c r="F2" t="n">
         <v>1.086344159199364e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.302385549435149e-08</v>
+        <v>1.30238554943515e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.274976782058061e-08</v>
+        <v>1.274976782058062e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.306460196795239e-08</v>
+        <v>1.30646019679524e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.443561857029283e-08</v>
+        <v>1.443561857029285e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.240819567022471e-08</v>
+        <v>1.240819567022472e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.270388310724131e-08</v>
@@ -6894,34 +6894,34 @@
         <v>1.392755734465627e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.25404191559694e-08</v>
+        <v>1.254041915596941e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.415493575815699e-08</v>
+        <v>1.4154935758157e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.285075641644946e-08</v>
+        <v>1.285075641644948e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.176584026065503e-08</v>
+        <v>1.176584026065504e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.391968084875072e-08</v>
+        <v>1.391968084875077e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.36210367537501e-08</v>
+        <v>1.362103675375011e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.396770217562233e-08</v>
+        <v>1.396770217562235e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.552989644069763e-08</v>
+        <v>1.552989644069765e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.329458739595282e-08</v>
+        <v>1.329458739595283e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.355183707819123e-08</v>
+        <v>1.355183707819124e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.544571833224545e-08</v>
+        <v>7.724385407074104e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.502447587466256e-08</v>
+        <v>7.668326911628119e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.556323353988329e-08</v>
+        <v>7.841900614711969e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>1.513797585768729e-08</v>
+        <v>7.688304316226235e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.513797585768729e-08</v>
+        <v>7.688304316226246e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.538985400889155e-08</v>
+        <v>7.711198961486697e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.527935638288052e-08</v>
+        <v>7.558023457709094e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.520901972323317e-08</v>
+        <v>7.700763686374978e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.622704033643204e-08</v>
+        <v>8.505707411260669e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.540431315839471e-08</v>
+        <v>7.682980233223255e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.52525009342778e-08</v>
+        <v>7.531168009106399e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.72183202781568e-07</v>
+        <v>3.531018252067839e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.782484761909479e-07</v>
+        <v>3.639575081163042e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.861270713426232e-07</v>
+        <v>3.786113590533187e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.782484778993144e-07</v>
+        <v>3.639575251999767e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.782484778993144e-07</v>
+        <v>3.639575251999767e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.764886171670099e-07</v>
+        <v>3.606458112368062e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.767370063802818e-07</v>
+        <v>3.597456970327376e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.782484240763541e-07</v>
+        <v>3.639569869703815e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.519480002279968e-07</v>
+        <v>4.999259612737508e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.692448062091599e-07</v>
+        <v>3.475890686344421e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.747081980492252e-07</v>
+        <v>3.541433206894874e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.932409473741445e-08</v>
+        <v>1.016697964114839e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.904441439869501e-08</v>
+        <v>1.013583607848748e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.345969281492705e-08</v>
+        <v>1.028865356052976e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.797323525816412e-08</v>
+        <v>9.947309958469486e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.910503607258079e-08</v>
+        <v>1.014650690072747e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.926823041406028e-08</v>
+        <v>1.258841293333175e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.346348341589102e-08</v>
+        <v>1.251842978864049e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.908739612840218e-08</v>
+        <v>1.014335792044926e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.093805896710856e-08</v>
+        <v>1.339242174550923e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.928112158070387e-08</v>
+        <v>1.012529850231571e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.912521113678861e-08</v>
+        <v>9.972764991518236e-09</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.111715907349606e-08</v>
+        <v>1.400255894351525e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.088051257907777e-08</v>
+        <v>1.397898933741023e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.123231377007988e-08</v>
+        <v>1.411965870120992e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.088047327839823e-08</v>
+        <v>1.397898382818468e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.088047327839823e-08</v>
+        <v>1.397898382818468e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.106129475014224e-08</v>
+        <v>1.398937249792784e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.095079712413107e-08</v>
+        <v>1.383619699415026e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.088046046448368e-08</v>
+        <v>1.397893722281612e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.189848107768262e-08</v>
+        <v>1.478388094770182e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.107575389964487e-08</v>
+        <v>1.396115376966441e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.092394167552836e-08</v>
+        <v>1.380934154554753e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.459646825322322e-07</v>
+        <v>3.069572298179914e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.307598619858919e-07</v>
+        <v>4.563775466149985e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.487221669233339e-07</v>
+        <v>4.887787266784153e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.075070656225385e-07</v>
+        <v>4.154526393138255e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.484241752186237e-07</v>
+        <v>3.114667527663947e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.309209649599368e-07</v>
+        <v>4.564467428332426e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.308104673339265e-07</v>
+        <v>4.549149877954674e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.307401306742785e-07</v>
+        <v>4.563423900821254e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.317748586229017e-07</v>
+        <v>4.644212322411695e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.443441330860086e-07</v>
+        <v>3.037638841751677e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.195859077788708e-07</v>
+        <v>6.109384732352002e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.028152961905992e-07</v>
+        <v>2.31014310268223e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.276472975902023e-07</v>
+        <v>2.748994342615766e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.28001468834368e-07</v>
+        <v>2.763102991931188e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>1.565759738192445e-07</v>
+        <v>3.258139182257457e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.276472815116102e-07</v>
+        <v>2.748994200401948e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.278280797612663e-07</v>
+        <v>2.750032658667526e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.277175821352551e-07</v>
+        <v>2.734715108289766e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.276472454756082e-07</v>
+        <v>2.748989131156354e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.286652660888067e-07</v>
+        <v>2.829483503644926e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.133176698821724e-07</v>
+        <v>2.481201541364688e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.276907266866524e-07</v>
+        <v>2.732029563429497e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7262,19 +7262,19 @@
         <v>1.1096079387941e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.684772375174112e-08</v>
+        <v>1.684772375174111e-08</v>
       </c>
       <c r="H2" t="n">
         <v>2.850998777627049e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.336406311017388e-08</v>
+        <v>1.336406311017389e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.490682520211061e-08</v>
+        <v>1.490682520211062e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.392247243978423e-08</v>
+        <v>1.392247243978424e-08</v>
       </c>
       <c r="L2" t="n">
         <v>3.065983065831605e-08</v>
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.653303018115162e-08</v>
+        <v>1.653303018115163e-08</v>
       </c>
       <c r="C3" t="n">
         <v>1.282180018581687e-08</v>
@@ -7296,7 +7296,7 @@
         <v>2.201845177122014e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.313435672163432e-08</v>
+        <v>1.313435672163433e-08</v>
       </c>
       <c r="F3" t="n">
         <v>1.204153079207429e-08</v>
@@ -7305,19 +7305,19 @@
         <v>1.831609465336826e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.174766700088855e-08</v>
+        <v>3.174766700088854e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.430799565896999e-08</v>
+        <v>1.430799565897e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.607757027410975e-08</v>
+        <v>1.607757027410978e-08</v>
       </c>
       <c r="K3" t="n">
         <v>1.503617585849451e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.420240052226176e-08</v>
+        <v>3.420240052226174e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.724178879696176e-08</v>
+        <v>9.130396830796694e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.541684798361366e-08</v>
+        <v>7.863283674818235e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>2.007680047293257e-08</v>
+        <v>1.196540850676749e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.555757198230953e-08</v>
+        <v>7.888052768884992e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.555757198230954e-08</v>
+        <v>7.88805276888499e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.810374354458235e-08</v>
+        <v>1.004144579847816e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.509394405393453e-08</v>
+        <v>1.698255208776946e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.578497782432174e-08</v>
+        <v>7.927633397901898e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.698544426064078e-08</v>
+        <v>8.874052294475708e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.675969704447142e-08</v>
+        <v>8.648305078306334e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>2.637199962255226e-08</v>
+        <v>1.82606076563872e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.999771769360909e-07</v>
+        <v>5.889182487364593e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.976321862693667e-07</v>
+        <v>3.993318303933662e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.62931056641036e-07</v>
+        <v>1.075077570746474e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.976321882965881e-07</v>
+        <v>3.993318506655812e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.976321882965881e-07</v>
+        <v>3.993318506655812e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.958053576285431e-07</v>
+        <v>7.651692951705073e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.118083097092234e-06</v>
+        <v>2.093486419801545e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.976316509192096e-07</v>
+        <v>3.993264768917963e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.916094339455259e-07</v>
+        <v>5.720787421711368e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.558760301628974e-07</v>
+        <v>5.073277947911024e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.384259819511296e-06</v>
+        <v>2.572488626618239e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.268276420880353e-08</v>
+        <v>1.184800848855519e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.088149501159893e-08</v>
+        <v>1.058506153699536e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.604323387427812e-08</v>
+        <v>1.477550077017752e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.972524008558092e-08</v>
+        <v>1.038156234154944e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.121907459068863e-08</v>
+        <v>1.064447721302374e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>4.961334794439934e-08</v>
+        <v>1.558713614279606e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.744513277036259e-08</v>
+        <v>2.267636127100831e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.122595323616351e-08</v>
+        <v>1.34733237422198e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.866510467085899e-08</v>
+        <v>1.444967249646204e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.208078204612327e-08</v>
+        <v>1.134481602398574e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.216662213985778e-08</v>
+        <v>2.104046120437002e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.584005637027639e-08</v>
+        <v>1.592369188688991e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.438378074779339e-08</v>
+        <v>1.47214638041521e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.867253683080465e-08</v>
+        <v>1.875825806894521e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.437684210708382e-08</v>
+        <v>1.472024427382433e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.437684210708386e-08</v>
+        <v>1.472024427382433e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.670201111789695e-08</v>
+        <v>1.683474085457136e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.369221162724918e-08</v>
+        <v>2.377584714386265e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.438324539763638e-08</v>
+        <v>1.472092845399511e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.558371183395542e-08</v>
+        <v>1.566734735056891e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.535796461778604e-08</v>
+        <v>1.544160013439954e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.497026719586693e-08</v>
+        <v>2.505390271248036e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.584117147310639e-07</v>
+        <v>3.397630366056856e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.489257082605881e-07</v>
+        <v>4.896084286091384e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.722699236776773e-07</v>
+        <v>5.635139795029252e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.237744228036273e-07</v>
+        <v>4.453421831486585e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.598676613265595e-07</v>
+        <v>3.328662835584814e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.512292732676384e-07</v>
+        <v>5.107153880741024e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.582194737769935e-07</v>
+        <v>5.801264509670201e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.48910507547378e-07</v>
+        <v>4.8957726406834e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.501290459080615e-07</v>
+        <v>4.990732596207866e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.562215004268874e-07</v>
+        <v>3.319358234061042e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.555528467183137e-07</v>
+        <v>7.619643643130991e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.26167401008823e-07</v>
+        <v>2.830130447620472e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.558177971377737e-07</v>
+        <v>3.257385059205361e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.601090876914289e-07</v>
+        <v>3.661109092367767e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>1.917142003404078e-07</v>
+        <v>3.889161919191428e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.558177660446771e-07</v>
+        <v>3.257384679009921e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.581360275078771e-07</v>
+        <v>3.468712764247289e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.651262280172295e-07</v>
+        <v>4.162823393176419e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.558172617876166e-07</v>
+        <v>3.257331524189661e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.570177282239357e-07</v>
+        <v>3.351973413847043e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.380374253474352e-07</v>
+        <v>3.012188149150887e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.66404283585847e-07</v>
+        <v>4.29062895003819e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7643,28 +7643,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.244429383841015e-08</v>
+        <v>1.244429383841014e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.128813806644363e-08</v>
+        <v>1.128813806644362e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.835597275164467e-08</v>
+        <v>1.83559727516447e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.159183122468248e-08</v>
+        <v>1.159183122468247e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.050025915866201e-08</v>
+        <v>1.0500259158662e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.483170171294425e-08</v>
+        <v>1.483170171294424e-08</v>
       </c>
       <c r="H2" t="n">
         <v>1.406106133903183e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.274606849379724e-08</v>
+        <v>1.274606849379723e-08</v>
       </c>
       <c r="J2" t="n">
         <v>1.383919747577827e-08</v>
@@ -7673,7 +7673,7 @@
         <v>1.212459359782233e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>2.284143835556942e-08</v>
+        <v>2.284143835556941e-08</v>
       </c>
     </row>
     <row r="3">
@@ -7689,31 +7689,31 @@
         <v>1.213300779113679e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.005171158775664e-08</v>
+        <v>2.005171158775666e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.244531332196224e-08</v>
+        <v>1.244531332196223e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.135374125594177e-08</v>
+        <v>1.135374125594176e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.599806984270482e-08</v>
+        <v>1.599806984270483e-08</v>
       </c>
       <c r="H3" t="n">
         <v>1.512885045379708e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.359901806160409e-08</v>
+        <v>1.359901806160408e-08</v>
       </c>
       <c r="J3" t="n">
         <v>1.484737830621497e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.297369308881505e-08</v>
+        <v>1.297369308881504e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.521072148248026e-08</v>
+        <v>2.521072148248027e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.512725346233609e-08</v>
+        <v>7.369810592411833e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>1.474483110652037e-08</v>
+        <v>7.451596972472051e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.86414960771692e-08</v>
+        <v>1.088405320724498e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.486692450062228e-08</v>
+        <v>7.473086937348702e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>1.486692450062229e-08</v>
+        <v>7.473086937348703e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.649019518297444e-08</v>
+        <v>8.779119697624422e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.608911833743953e-08</v>
+        <v>8.331675467515327e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.502068086016132e-08</v>
+        <v>7.499863847780014e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.59204265290954e-08</v>
+        <v>8.162983659171164e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.529084853734083e-08</v>
+        <v>7.533405667416566e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>2.130713348450619e-08</v>
+        <v>1.354969061458195e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.370753275857446e-07</v>
+        <v>2.883267152183291e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.595114902075135e-07</v>
+        <v>3.293052883618646e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.334414714788864e-07</v>
+        <v>8.388884848236326e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.595114920614344e-07</v>
+        <v>3.29305306901078e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.595114920614344e-07</v>
+        <v>3.29305306901078e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.657992410608488e-07</v>
+        <v>5.265751153437074e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.45547664349815e-07</v>
+        <v>4.871637934686458e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.595111471479632e-07</v>
+        <v>3.293018577663621e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.163174446076507e-07</v>
+        <v>4.343285864988345e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.535112060964245e-07</v>
+        <v>3.186018846599804e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.906803593981018e-07</v>
+        <v>4.13884282258948e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.913491179557228e-08</v>
+        <v>1.236915872177618e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.88311728542124e-08</v>
+        <v>9.93079310663205e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>3.312792321689422e-08</v>
+        <v>1.343366437002071e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.776217343874045e-08</v>
+        <v>9.742650738159674e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>2.903674991506242e-08</v>
+        <v>9.966976196776783e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>4.489558243555314e-08</v>
+        <v>1.124446755091525e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.505600754228378e-08</v>
+        <v>1.342984793994292e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.342606811273996e-08</v>
+        <v>1.249921197714433e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.446288906310566e-08</v>
+        <v>1.077713434851152e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.917121641690944e-08</v>
+        <v>9.976350400983295e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>3.551257297006467e-08</v>
+        <v>1.604984795049287e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.096132559932545e-08</v>
+        <v>1.367660725434792e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.085509605670087e-08</v>
+        <v>1.380700356926634e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.447320926344283e-08</v>
+        <v>1.719043469385737e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.085169044732258e-08</v>
+        <v>1.38064057096502e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.085169044732257e-08</v>
+        <v>1.38064057096502e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.232426731996373e-08</v>
+        <v>1.508591635956048e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.192319047442885e-08</v>
+        <v>1.463847212945141e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.085475299715063e-08</v>
+        <v>1.380666050971607e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.175449866608473e-08</v>
+        <v>1.446978032110727e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.112492067433013e-08</v>
+        <v>1.384020232935271e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.714120562149553e-08</v>
+        <v>1.985648727651801e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.46187038004881e-07</v>
+        <v>3.043633254691142e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.314757133978925e-07</v>
+        <v>4.559623204909936e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.527834179211459e-07</v>
+        <v>5.209303122848977e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.081230918770558e-07</v>
+        <v>4.148617221129761e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.487865474759686e-07</v>
+        <v>3.104294045329391e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.329283547717805e-07</v>
+        <v>4.687223557884272e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.325272779262441e-07</v>
+        <v>4.642479134873341e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.314588404489671e-07</v>
+        <v>4.559297972899836e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.323753654275768e-07</v>
+        <v>4.625905269887632e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.447646859289217e-07</v>
+        <v>3.032080092485897e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>3.26930145044619e-07</v>
+        <v>6.73393403576969e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.085723243320081e-07</v>
+        <v>2.381614297635793e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.352247848310851e-07</v>
+        <v>2.865606871309673e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.388452683757551e-07</v>
+        <v>3.203991701716083e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>1.661037336887389e-07</v>
+        <v>3.409076521022655e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.352247673071534e-07</v>
+        <v>2.865606715651599e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.366939560943481e-07</v>
+        <v>2.993498150339087e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.36292879248813e-07</v>
+        <v>2.94875372732818e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>1.352244417715349e-07</v>
+        <v>2.865572565354649e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.36124187440469e-07</v>
+        <v>2.931884546493767e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.199905241384862e-07</v>
+        <v>2.275912876365068e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.415108943958797e-07</v>
+        <v>3.470555242034843e-08</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia human toxicity non-carcinogenic results.xlsx
+++ b/Results/Ammonia/ammonia human toxicity non-carcinogenic results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.885664256064888e-08</v>
+        <v>1.211700851599092e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.346776542341749e-08</v>
+        <v>1.068127304282624e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.072215489419917e-08</v>
+        <v>1.221518672489976e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.377588483266511e-08</v>
+        <v>1.096390792530906e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.267104578056828e-08</v>
+        <v>1.004411504023728e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.783530532283531e-08</v>
+        <v>1.206325756570395e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>3.031208717097685e-08</v>
+        <v>1.271346906539649e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.490465436189716e-08</v>
+        <v>1.190915232275633e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.639511487928039e-08</v>
+        <v>1.205959590872921e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.521512318609966e-08</v>
+        <v>1.152565231837805e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.428351642036156e-08</v>
+        <v>1.293787608985553e-08</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.06262031124391e-08</v>
+        <v>1.43699221163891e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.463655127155319e-08</v>
+        <v>1.088771439821071e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.277192873573753e-08</v>
+        <v>1.507197933642356e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.495219696051093e-08</v>
+        <v>1.133571146238204e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.38473579084141e-08</v>
+        <v>9.817528108567532e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.945145371958195e-08</v>
+        <v>1.399323819903632e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.382082805233629e-08</v>
+        <v>1.870277498467597e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.607991453824048e-08</v>
+        <v>1.289363584854191e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.778104093822727e-08</v>
+        <v>1.354830587631659e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.651470052788694e-08</v>
+        <v>1.249644017695275e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.836971210138211e-08</v>
+        <v>2.023164017345976e-08</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.135574895314915e-08</v>
+        <v>1.135574895314947e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.891357279195099e-09</v>
+        <v>8.891357279195077e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.246471698698207e-08</v>
+        <v>1.246471698698213e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.917438337779829e-09</v>
+        <v>8.917438337779826e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>8.917438337779845e-09</v>
+        <v>8.917438337779827e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.073829498242929e-08</v>
+        <v>1.073829498242941e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.816324049938144e-08</v>
+        <v>1.816324049938142e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.954302206969341e-09</v>
+        <v>8.954302206969325e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>9.837482672416965e-09</v>
+        <v>9.837482672416977e-09</v>
       </c>
       <c r="K4" t="n">
         <v>9.495750247167161e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>2.052376817490749e-08</v>
+        <v>2.052376817490748e-08</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.011846701932901e-07</v>
+        <v>1.011846701932934e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>5.812684346704347e-08</v>
+        <v>5.812684346704343e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.243219172384107e-07</v>
+        <v>1.243219172384115e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>5.812684546109985e-08</v>
+        <v>5.812684546109972e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.812684546109985e-08</v>
+        <v>5.812684546109972e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.307219745413473e-08</v>
+        <v>9.307219745413392e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.607070550845649e-07</v>
+        <v>2.607070550845636e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>5.812638248076589e-08</v>
+        <v>5.812638248076569e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.690865386877494e-08</v>
+        <v>7.690865386877574e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.734654774440121e-08</v>
+        <v>6.734654774440225e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.115256013422915e-08</v>
+        <v>3.212807557633484e-07</v>
       </c>
     </row>
     <row r="6">
@@ -675,31 +675,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.4322683217472e-08</v>
+        <v>1.432268321747219e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.186838701431033e-08</v>
+        <v>1.186838701431022e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.552041941341128e-08</v>
+        <v>1.552038621930293e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.164774964843579e-08</v>
+        <v>1.164774964843581e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.192435251330763e-08</v>
+        <v>1.192435251330762e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.679870266963215e-08</v>
+        <v>1.679870266963217e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.437211867782731e-08</v>
+        <v>2.437211867782724e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.192123647129207e-08</v>
+        <v>1.501470989417215e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.298634150371553e-08</v>
+        <v>1.591825276529849e-08</v>
       </c>
       <c r="K6" t="n">
         <v>1.244417136526833e-08</v>
@@ -718,34 +718,34 @@
         <v>1.866831601603701e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.626733025613463e-08</v>
+        <v>1.626733025613462e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.977680442403902e-08</v>
+        <v>1.977680442403906e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.626614405910079e-08</v>
+        <v>1.626614405910078e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.626614405910079e-08</v>
+        <v>1.626614405910078e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.80508620453169e-08</v>
+        <v>1.805086204531691e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5475807562269e-08</v>
+        <v>2.547580756226896e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.626686926985689e-08</v>
+        <v>1.626686926985687e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.715004973530455e-08</v>
+        <v>1.715004973530451e-08</v>
       </c>
       <c r="K7" t="n">
         <v>1.68083173100547e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.783633523779503e-08</v>
+        <v>2.7836335237795e-08</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.800958927208113e-08</v>
+        <v>3.800958927208116e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.2976955494092e-08</v>
+        <v>5.297695549413409e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>6.008486259986679e-08</v>
+        <v>6.00848625998667e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.822722021622221e-08</v>
+        <v>4.822722021622219e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.615864118509563e-08</v>
+        <v>3.615864118509559e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.47575986452911e-08</v>
+        <v>5.475759864529095e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.218254416224336e-08</v>
+        <v>6.218254416224324e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>5.297360586983091e-08</v>
+        <v>5.297360586983094e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.386019914892967e-08</v>
+        <v>5.38601991489296e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.582701816881118e-08</v>
+        <v>3.582701816881114e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.268275037931078e-08</v>
+        <v>8.268275037931049e-08</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.376012470046716e-08</v>
+        <v>3.3760124700467e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.774230709017782e-08</v>
+        <v>3.774230709017776e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.125226142811128e-08</v>
+        <v>4.12522614281112e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.510834221115077e-08</v>
+        <v>4.510834221115068e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.774230263251069e-08</v>
+        <v>3.774230263251068e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.952583887936003e-08</v>
+        <v>3.952583887936007e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>4.69507843963122e-08</v>
+        <v>4.69507843963121e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.774184610390007e-08</v>
+        <v>3.774184610390004e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.862502656934773e-08</v>
+        <v>3.862502656934768e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.458486167846438e-08</v>
+        <v>3.024574591120608e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.931131207183823e-08</v>
+        <v>4.931131207183819e-08</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.234528055462373e-08</v>
+        <v>1.137237024324789e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.159186987567245e-08</v>
+        <v>1.0201404845065e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.323338844900698e-08</v>
+        <v>1.141910959780492e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.189494926859318e-08</v>
+        <v>1.047692713975779e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.08045749819207e-08</v>
+        <v>9.569171440251639e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.305318049983316e-08</v>
+        <v>1.140962561136174e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.314507626635254e-08</v>
+        <v>1.140219744445023e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.300525262081224e-08</v>
+        <v>1.140726091206411e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.394957594960647e-08</v>
+        <v>1.153527979021602e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.185057432791163e-08</v>
+        <v>1.090378009423716e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.289959104902772e-08</v>
+        <v>1.139913830661458e-08</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.313920667947442e-08</v>
+        <v>1.171288697854742e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.247641786306473e-08</v>
+        <v>9.989917981746864e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.416071472901126e-08</v>
+        <v>1.204599922953689e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.278845786901735e-08</v>
+        <v>1.042891398803023e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.169808358234485e-08</v>
+        <v>8.930602062919448e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.395343825749716e-08</v>
+        <v>1.197892574055505e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.407573220805123e-08</v>
+        <v>1.200653720902961e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3899582915166e-08</v>
+        <v>1.196222015702203e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.496936080810712e-08</v>
+        <v>1.241675600508983e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.265544451205606e-08</v>
+        <v>1.096107909026933e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.377696251163514e-08</v>
+        <v>1.192501208565391e-08</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.317988241935719e-09</v>
+        <v>7.317988241935758e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.634006777370891e-09</v>
+        <v>7.634006777370909e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.845930752822823e-09</v>
+        <v>7.845930752822851e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.654115403540847e-09</v>
+        <v>7.654115403540896e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.65411540354086e-09</v>
+        <v>7.654115403540875e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.729667856612586e-09</v>
+        <v>7.72966785661263e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.793990786973092e-09</v>
+        <v>7.793990786973132e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.666382279393063e-09</v>
+        <v>7.666382279393108e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.211843476299283e-09</v>
+        <v>8.211843476299316e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.361300291581951e-09</v>
+        <v>7.361300291581975e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.648528045033138e-09</v>
+        <v>7.648528045033171e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.875278514361892e-08</v>
+        <v>2.875278514361895e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.58416951672879e-08</v>
+        <v>3.584169516728791e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.784734867016852e-08</v>
+        <v>3.784734867016858e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.584169685970084e-08</v>
+        <v>3.584169685970087e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.584169685970084e-08</v>
+        <v>3.584169685970087e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.626180289992131e-08</v>
+        <v>3.626180289992133e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.986712018414837e-08</v>
+        <v>3.986712018414846e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.584163100269188e-08</v>
+        <v>3.584163100269199e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.497599616405379e-08</v>
+        <v>4.497599616405391e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.98549789035437e-08</v>
+        <v>2.985497890354373e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.758812100535913e-08</v>
+        <v>3.758812100535924e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1071,34 +1071,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.217797562626653e-08</v>
+        <v>9.750355854485562e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.009459004965352e-08</v>
+        <v>1.009459004965347e-08</v>
       </c>
       <c r="D6" t="n">
         <v>1.27529537132744e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.906437904977435e-09</v>
+        <v>9.906437904977407e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.010520082809905e-08</v>
+        <v>1.010520082809907e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.016203546916243e-08</v>
+        <v>1.258965524094342e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.275405190572822e-08</v>
+        <v>1.275405190572825e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.009874989194289e-08</v>
+        <v>1.009874989194291e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.309579289348713e-08</v>
+        <v>1.079252105383767e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.787461787564291e-09</v>
+        <v>9.787461787564367e-09</v>
       </c>
       <c r="L6" t="n">
         <v>1.008409105976049e-08</v>
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.360785822877263e-08</v>
+        <v>1.360785822877266e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.395631643082592e-08</v>
+        <v>1.395631643082595e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.413538499925055e-08</v>
+        <v>1.413538499925056e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.395654332014189e-08</v>
+        <v>1.395654332014191e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.395654332014189e-08</v>
+        <v>1.395654332014191e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.40195378434495e-08</v>
+        <v>1.401953784344951e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.408386077381001e-08</v>
+        <v>1.408386077381004e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.395625226622997e-08</v>
+        <v>1.395625226623001e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.450171346313619e-08</v>
+        <v>1.450171346313623e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.365117027841886e-08</v>
+        <v>1.365117027841889e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.393839803187005e-08</v>
+        <v>1.393839803187008e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.031223829069051e-08</v>
+        <v>3.031223829069061e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.56431475344458e-08</v>
+        <v>4.564314753448256e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.892488620362043e-08</v>
+        <v>4.892488620362052e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.154608625010712e-08</v>
+        <v>4.15460862501072e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.113588414817534e-08</v>
+        <v>3.11358841481754e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.570267951080038e-08</v>
+        <v>4.57026795108005e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.576700244116085e-08</v>
+        <v>4.576700244116092e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.563939393358087e-08</v>
+        <v>4.563939393358091e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.618779888857822e-08</v>
+        <v>4.618779888857832e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.007731215320168e-08</v>
+        <v>3.00773121532017e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.126810870188436e-08</v>
+        <v>6.126810870188444e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.270612976381961e-08</v>
+        <v>2.270612976381964e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.747063767244799e-08</v>
+        <v>2.747063767244802e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.765012362008193e-08</v>
+        <v>2.765012362008195e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.256666457459287e-08</v>
+        <v>3.256666457459291e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.747063616668632e-08</v>
+        <v>2.747063616668634e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.753385908507157e-08</v>
+        <v>2.753385908507156e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.759818201543209e-08</v>
+        <v>2.75981820154321e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.747057350785202e-08</v>
+        <v>2.747057350785206e-08</v>
       </c>
       <c r="J9" t="n">
         <v>2.801603470475828e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.460681566615905e-08</v>
+        <v>2.46068156661591e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.745271927349211e-08</v>
+        <v>2.745271927349214e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.315999459690331e-08</v>
+        <v>1.14411254460204e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.238433740991821e-08</v>
+        <v>9.618101363349035e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.703198635925439e-08</v>
+        <v>1.164490068207789e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.179368004376355e-08</v>
+        <v>9.895060848620012e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.179368004376355e-08</v>
+        <v>9.894900849913613e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.506508855794534e-08</v>
+        <v>1.154138675736878e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.092498744543486e-08</v>
+        <v>1.184021486484975e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.367682386043902e-08</v>
+        <v>1.146847050842569e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.493057545136671e-08</v>
+        <v>1.075665132028185e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.390406464433818e-08</v>
+        <v>1.168957350526862e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.637998050731256e-08</v>
+        <v>1.160884872511174e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.41018512144301e-08</v>
+        <v>1.190569533755057e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.354164010866873e-08</v>
+        <v>9.362581078876121e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.855544382181106e-08</v>
+        <v>1.337716851362518e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.281358300151297e-08</v>
+        <v>9.52636112498321e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.281358300151297e-08</v>
+        <v>9.526201126276926e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.629310390865359e-08</v>
+        <v>1.264202017843149e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.305190511471104e-08</v>
+        <v>1.485155183509219e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.469655256470756e-08</v>
+        <v>1.212119389064028e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.628819143829569e-08</v>
+        <v>1.159817132730745e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.491736904714864e-08</v>
+        <v>1.24731782908085e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.78056690077675e-08</v>
+        <v>1.314800077090501e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.920892713623225e-09</v>
+        <v>7.920892713623245e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>8.646404202595248e-09</v>
+        <v>8.646404202595253e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.022262774613229e-08</v>
+        <v>1.022262774613231e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.149532026353708e-09</v>
+        <v>8.149532026353772e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>8.149532026353706e-09</v>
+        <v>8.149532026353774e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>9.043500455938977e-09</v>
+        <v>9.043500455939016e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.253609971565133e-08</v>
+        <v>1.253609971565137e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.179123849633306e-09</v>
+        <v>8.179123849633323e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>9.566295937887467e-09</v>
+        <v>9.566295937887505e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>8.203653427930975e-09</v>
+        <v>8.203653427931001e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>9.83583274484035e-09</v>
+        <v>9.83583274484038e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.778837585772965e-08</v>
+        <v>2.778837585772971e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.564026437120587e-08</v>
+        <v>5.564026437120591e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.000668589744527e-08</v>
+        <v>8.000668589744528e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.461445150257769e-08</v>
+        <v>4.461445150257754e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.461445150257769e-08</v>
+        <v>4.461445150257754e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.021799741652365e-08</v>
+        <v>6.021799741652434e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.351760071912262e-07</v>
+        <v>1.351760071912261e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>4.461419913380418e-08</v>
+        <v>4.461419913380372e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.107623308949399e-08</v>
+        <v>7.107623308949389e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.401318102357781e-08</v>
+        <v>4.401318102357776e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.212738449863255e-08</v>
+        <v>8.212738449863246e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.057851626116099e-08</v>
+        <v>1.325718809566639e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.141246773678415e-08</v>
+        <v>1.141246773678419e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.293196849133986e-08</v>
+        <v>1.293194097698947e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.060729363852638e-08</v>
+        <v>1.060729363852637e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.084064138715791e-08</v>
+        <v>1.084064138715792e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.437979583798214e-08</v>
+        <v>1.170112400347674e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.815667859886979e-08</v>
+        <v>1.815667859886981e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.351541923167646e-08</v>
+        <v>1.083674739717108e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.497483324417948e-08</v>
+        <v>1.49748332441795e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.084683418834359e-08</v>
+        <v>1.08468341883436e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.250581503038705e-08</v>
+        <v>1.250581503038706e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.462332725187936e-08</v>
+        <v>1.462332725187939e-08</v>
       </c>
       <c r="C7" t="n">
         <v>1.547179418826776e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.692464633712478e-08</v>
+        <v>1.692464633712482e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.488208170477261e-08</v>
+        <v>1.488208170477259e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.488208170477261e-08</v>
+        <v>1.488208170477259e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.574593499419514e-08</v>
+        <v>1.574593499419518e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.923853425390748e-08</v>
+        <v>1.923853425390749e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.488155838788946e-08</v>
+        <v>1.488155838788945e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.626873047614361e-08</v>
+        <v>1.626873047614362e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.490608796618712e-08</v>
+        <v>1.490608796618713e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.653826728309651e-08</v>
+        <v>1.653826728309652e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.243671781223931e-08</v>
+        <v>3.243671781223939e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.92746091060397e-08</v>
+        <v>4.927460910603972e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.403864284544138e-08</v>
+        <v>5.403864284544142e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.431220572694948e-08</v>
+        <v>4.431220572694952e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.320232655029479e-08</v>
+        <v>3.32023265502948e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.95448192926495e-08</v>
+        <v>4.954481929264956e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.303741855237077e-08</v>
+        <v>5.303741855237075e-08</v>
       </c>
       <c r="I8" t="n">
         <v>4.868044268634385e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.007075638446518e-08</v>
+        <v>5.007075638446516e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.242253977317138e-08</v>
+        <v>3.242253977317147e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.703533647846905e-08</v>
+        <v>6.70353364784692e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1587,19 +1587,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.650383633078758e-08</v>
+        <v>2.650383633078761e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.266927643090009e-08</v>
+        <v>3.266927643090008e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.412254588456865e-08</v>
+        <v>3.412254588456869e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.821496298434867e-08</v>
+        <v>3.821496298434871e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.20792885712651e-08</v>
+        <v>3.207928857126512e-08</v>
       </c>
       <c r="G9" t="n">
         <v>3.294341723682744e-08</v>
@@ -1608,16 +1608,16 @@
         <v>3.643601649653979e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.207904063052178e-08</v>
+        <v>3.207904063052185e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.346621271877595e-08</v>
+        <v>3.346621271877598e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.902289564737242e-08</v>
+        <v>2.902289564737241e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.373574952572879e-08</v>
+        <v>3.373574952572885e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.246407726630162e-08</v>
+        <v>1.137522410943063e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.158643556388617e-08</v>
+        <v>9.513510024902735e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.568966487521941e-08</v>
+        <v>1.154498037875497e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.115423964260676e-08</v>
+        <v>9.810047971757798e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.115423964260676e-08</v>
+        <v>9.809887253997148e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.396257077776867e-08</v>
+        <v>1.14540868466913e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.703665882208002e-08</v>
+        <v>1.16050032052461e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.306560873392667e-08</v>
+        <v>1.140703237295663e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.342266082719068e-08</v>
+        <v>1.063931102476035e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.287984496719376e-08</v>
+        <v>1.156938223289262e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.345823016193381e-08</v>
+        <v>1.142467016786025e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.330466647602042e-08</v>
+        <v>1.16568851501635e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.263296532499072e-08</v>
+        <v>9.032575289851714e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.701476040473613e-08</v>
+        <v>1.288648503111457e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.208561374505136e-08</v>
+        <v>9.270714647831515e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.208561374505136e-08</v>
+        <v>9.270553930070862e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.502824442620327e-08</v>
+        <v>1.224060517560847e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.858205323116226e-08</v>
+        <v>1.339606607677521e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.399753774228033e-08</v>
+        <v>1.190446573308908e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.455871854336871e-08</v>
+        <v>1.103279796124258e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.374969849450687e-08</v>
+        <v>1.205422216856175e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.444839487664238e-08</v>
+        <v>1.205597203610072e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.458354043608166e-09</v>
+        <v>7.458354043608201e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>8.153765766935432e-09</v>
+        <v>8.153765766935446e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>9.375829197368615e-09</v>
+        <v>9.375829197368622e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.757797149230321e-09</v>
+        <v>7.757797149230328e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.757797149230321e-09</v>
+        <v>7.75779714923033e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>8.339471479183478e-09</v>
+        <v>8.339471479183496e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.017644966436013e-08</v>
+        <v>1.017644966436015e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>7.768446015684787e-09</v>
+        <v>7.76844601568482e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.62769590088373e-09</v>
+        <v>8.627695900883758e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.57417008064608e-09</v>
+        <v>7.574170080646098e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>8.050506566736143e-09</v>
+        <v>8.050506566736171e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.938691718372094e-08</v>
+        <v>1.938691718372095e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.523102902145629e-08</v>
+        <v>4.523102902145646e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.264988144388477e-08</v>
+        <v>6.264988144388474e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.63489949419097e-08</v>
+        <v>3.634899494190972e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.63489949419097e-08</v>
+        <v>3.634899494190972e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.594911864736816e-08</v>
+        <v>4.594911864736927e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.43581546157813e-08</v>
+        <v>8.435815461578134e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.634881043096814e-08</v>
+        <v>3.634881043096818e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.183545964876661e-08</v>
+        <v>5.183545964876663e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.210555191598416e-08</v>
+        <v>3.210555191598414e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.432505374619558e-08</v>
+        <v>4.432505374619557e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1866,10 +1866,10 @@
         <v>1.242806826944991e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.071827901540464e-08</v>
+        <v>1.071827901540453e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.44448682369673e-08</v>
+        <v>1.444486823696735e-08</v>
       </c>
       <c r="E6" t="n">
         <v>1.001750349237655e-08</v>
@@ -1878,22 +1878,22 @@
         <v>1.023047801698708e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.079596089887526e-08</v>
+        <v>1.330918570502518e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.544486970780212e-08</v>
+        <v>1.544486970780216e-08</v>
       </c>
       <c r="I6" t="n">
         <v>1.022493543537657e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.123788679503847e-08</v>
+        <v>1.12378867950385e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.001596953752393e-08</v>
+        <v>1.001596953752388e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.051109773287135e-08</v>
+        <v>1.051109773287138e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1903,34 +1903,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.385206157206756e-08</v>
+        <v>1.385206157206759e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.466604710342295e-08</v>
+        <v>1.466604710342297e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.576914361273274e-08</v>
+        <v>1.576914361273276e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.416692603118485e-08</v>
+        <v>1.416692603118487e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.416692603118485e-08</v>
+        <v>1.416692603118486e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.473317900764287e-08</v>
+        <v>1.47331790076429e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.657015719281953e-08</v>
+        <v>1.657015719281954e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.416215354414418e-08</v>
+        <v>1.416215354414421e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.50214034293431e-08</v>
+        <v>1.502140342934315e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.396787760910547e-08</v>
+        <v>1.396787760910548e-08</v>
       </c>
       <c r="L7" t="n">
         <v>1.444421409519555e-08</v>
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.073136783051429e-08</v>
+        <v>3.073136783051432e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.674532605654769e-08</v>
+        <v>4.674532605649515e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.099112515865045e-08</v>
+        <v>5.099112515865051e-08</v>
       </c>
       <c r="E8" t="n">
         <v>4.208577279288773e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.152618191893416e-08</v>
+        <v>3.152618191893419e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.680458631952483e-08</v>
+        <v>4.680458631952484e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.864156450472441e-08</v>
+        <v>4.864156450472448e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.623356085602614e-08</v>
+        <v>4.623356085602612e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.709579642650794e-08</v>
+        <v>4.709579642650796e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.05649827906334e-08</v>
+        <v>3.056498279063344e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.238504130230648e-08</v>
+        <v>6.238504130230647e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.384956816108298e-08</v>
+        <v>2.384956816108303e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.93727715281213e-08</v>
+        <v>2.937277152812129e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.047626270550662e-08</v>
+        <v>3.047626270550665e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.430339684529941e-08</v>
+        <v>3.430339684529946e-08</v>
       </c>
       <c r="F9" t="n">
         <v>2.886905882299567e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.943990343234119e-08</v>
+        <v>2.943990343234124e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.127688161751788e-08</v>
+        <v>3.12768816175179e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.886887796884249e-08</v>
+        <v>2.886887796884257e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.972812785404141e-08</v>
+        <v>2.972812785404147e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.594606337930249e-08</v>
+        <v>2.59460633793025e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.915093851989388e-08</v>
+        <v>2.915093851989398e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.205295168183222e-08</v>
+        <v>1.13103812759312e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.084956101107515e-08</v>
+        <v>9.414379867638153e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.460820613215824e-08</v>
+        <v>1.144485924250771e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.051822373895025e-08</v>
+        <v>9.717540546056858e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.051822373895025e-08</v>
+        <v>9.717379516723286e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.318047809855086e-08</v>
+        <v>1.13697207517952e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.487851782095149e-08</v>
+        <v>1.144763895369982e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.244986286676456e-08</v>
+        <v>1.133142251618054e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.196921079939231e-08</v>
+        <v>1.051805498237355e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.241873125942757e-08</v>
+        <v>1.148387838334105e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.259129516527715e-08</v>
+        <v>1.133591879467545e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.283508370952465e-08</v>
+        <v>1.148942415965498e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.179160086386522e-08</v>
+        <v>8.720774750989913e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.577415564676434e-08</v>
+        <v>1.24679980835913e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.136041018417783e-08</v>
+        <v>8.998791980586509e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.136041018417783e-08</v>
+        <v>8.998630951252956e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.41319726551447e-08</v>
+        <v>1.193390403549332e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.610255547867231e-08</v>
+        <v>1.256836468663458e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.32928033636906e-08</v>
+        <v>1.166043692686137e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.289054682943974e-08</v>
+        <v>1.04714872567372e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.322609232480784e-08</v>
+        <v>1.184511587071087e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34545324505705e-08</v>
+        <v>1.171553770001432e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.217266339068222e-09</v>
+        <v>7.217266339068231e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.727820107064171e-09</v>
+        <v>7.727820107064153e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>8.736256834471255e-09</v>
+        <v>8.736256834471235e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.39949422149456e-09</v>
+        <v>7.399494221494559e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.39949422149456e-09</v>
+        <v>7.39949422149457e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.877926441009754e-09</v>
+        <v>7.877926441009796e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>8.897152399142871e-09</v>
+        <v>8.897152399142858e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.406199643395649e-09</v>
+        <v>7.406199643395646e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.768178071098519e-09</v>
+        <v>7.768178071098499e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.317112411126578e-09</v>
+        <v>7.31711241112658e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.538449774691063e-09</v>
+        <v>7.538449774691046e-09</v>
       </c>
     </row>
     <row r="5">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.531789706496741e-08</v>
+        <v>1.53178970649674e-08</v>
       </c>
       <c r="C5" t="n">
         <v>3.803061989427201e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.192532374773193e-08</v>
+        <v>5.192532374773178e-08</v>
       </c>
       <c r="E5" t="n">
         <v>3.027291879893356e-08</v>
@@ -2234,22 +2234,22 @@
         <v>3.027291879893356e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.803079305991866e-08</v>
+        <v>3.803079305991902e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.004090917305197e-08</v>
+        <v>6.004090917305202e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.027275730387052e-08</v>
+        <v>3.027275730387056e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.664761561779244e-08</v>
+        <v>3.664761561779239e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.786618047038332e-08</v>
+        <v>2.786618047038323e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.45089962231829e-08</v>
+        <v>3.450899622318289e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.633869828261943e-09</v>
+        <v>9.633869828261926e-09</v>
       </c>
       <c r="C6" t="n">
         <v>1.025510895627183e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.118644576514425e-08</v>
+        <v>1.118647103241513e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.617958873024972e-09</v>
+        <v>9.617958873024928e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.828173739160457e-09</v>
+        <v>9.828173739160449e-09</v>
       </c>
       <c r="G6" t="n">
         <v>1.279831785087866e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.414976338612214e-08</v>
+        <v>1.414976338612216e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.232659105326452e-08</v>
+        <v>1.232659105326453e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.276594720838154e-08</v>
+        <v>1.276594720838151e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.722999578232878e-09</v>
+        <v>9.722999578232852e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>9.95749285997923e-09</v>
+        <v>9.957492859979196e-09</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.362911129469988e-08</v>
+        <v>1.362911129469987e-08</v>
       </c>
       <c r="C7" t="n">
         <v>1.426293936442795e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.514770953853839e-08</v>
+        <v>1.514770953853838e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.382410357117984e-08</v>
+        <v>1.382410357117983e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.382410357117984e-08</v>
+        <v>1.382410357117983e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.428977139664144e-08</v>
+        <v>1.428977139664142e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.530899735477452e-08</v>
+        <v>1.530899735477453e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.38180445990273e-08</v>
+        <v>1.381804459902729e-08</v>
       </c>
       <c r="J7" t="n">
         <v>1.418002302673016e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.372895736675823e-08</v>
+        <v>1.372895736675821e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.39502947303227e-08</v>
+        <v>1.395029473032269e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2342,34 +2342,34 @@
         <v>3.051818883860875e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.637977957215478e-08</v>
+        <v>4.637977957222019e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.041149594296811e-08</v>
+        <v>5.041149594296807e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.17718116268123e-08</v>
+        <v>4.177181162681217e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.119344295616118e-08</v>
+        <v>3.119344295616119e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.639748269929207e-08</v>
+        <v>4.639748269929203e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.741670865746188e-08</v>
+        <v>4.741670865746184e-08</v>
       </c>
       <c r="I8" t="n">
         <v>4.592575590167796e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.629072522903596e-08</v>
+        <v>4.629072522903592e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.033534097511451e-08</v>
+        <v>3.033534097511449e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.195514155752051e-08</v>
+        <v>6.195514155752048e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2379,34 +2379,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.268926946600639e-08</v>
+        <v>2.268926946600637e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.77819329523273e-08</v>
+        <v>2.778193295232727e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.866709704427009e-08</v>
+        <v>2.866709704427005e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.24825984858491e-08</v>
+        <v>3.248259848584908e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.733719629752737e-08</v>
+        <v>2.733719629752735e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.780876498454076e-08</v>
+        <v>2.780876498454078e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.882799094267386e-08</v>
+        <v>2.882799094267389e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.733703818692666e-08</v>
+        <v>2.733703818692661e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.769901661462947e-08</v>
+        <v>2.76990166146295e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.163348083399995e-08</v>
+        <v>2.455967035522406e-08</v>
       </c>
       <c r="L9" t="n">
         <v>2.746928831822202e-08</v>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.202667322870273e-08</v>
+        <v>1.133502660118107e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.656937077301575e-09</v>
+        <v>9.329721152553283e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.497162169118058e-08</v>
+        <v>1.149001338962251e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.064893833960792e-08</v>
+        <v>9.724509374804921e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.064893833960792e-08</v>
+        <v>9.724348569224525e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.395661517796723e-08</v>
+        <v>1.143659561279741e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.904687015669994e-08</v>
+        <v>1.16947912579115e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.261394980017975e-08</v>
+        <v>1.13660807128407e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.461923626230486e-08</v>
+        <v>1.064316591461391e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.320662082738271e-08</v>
+        <v>1.15529660258662e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.623387456784186e-08</v>
+        <v>1.155563429659133e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.279249453232953e-08</v>
+        <v>1.149123836901579e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.041767053602953e-08</v>
+        <v>8.224030665858906e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.617979530841523e-08</v>
+        <v>1.261589973454649e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.15033920891213e-08</v>
+        <v>9.026264413501327e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.15033920891213e-08</v>
+        <v>9.026103607920894e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.501232756025407e-08</v>
+        <v>1.223692698516854e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.088573351807176e-08</v>
+        <v>1.415396710241961e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.346911982948916e-08</v>
+        <v>1.173361501175635e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.593404080607928e-08</v>
+        <v>1.142733990250137e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.411965791040648e-08</v>
+        <v>1.215422114340977e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.763175125986963e-08</v>
+        <v>1.310461935847359e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.142627710455047e-09</v>
+        <v>7.142627710455064e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>6.9827879588972e-09</v>
+        <v>6.982787958897213e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>8.893274783346291e-09</v>
+        <v>8.893274783346294e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.43797254519317e-09</v>
+        <v>7.437972545193153e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.43797254519317e-09</v>
+        <v>7.437972545193152e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>8.280061144313032e-09</v>
+        <v>8.280061144313048e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.131525853136338e-08</v>
+        <v>1.131525853136339e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>7.443085647917436e-09</v>
+        <v>7.44308564791743e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>9.315275785000471e-09</v>
+        <v>9.315275785000485e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.725246734605169e-09</v>
+        <v>7.725246734605184e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>9.644155807229916e-09</v>
+        <v>9.644155807229934e-09</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.535676173150703e-08</v>
+        <v>1.535676173150705e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.723639430735786e-08</v>
+        <v>2.723639430735787e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.807789729386433e-08</v>
+        <v>5.807789729386437e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.318550173435451e-08</v>
+        <v>3.318550173435417e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.318550173435451e-08</v>
+        <v>3.318550173435417e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.807820593108227e-08</v>
+        <v>4.80782059310824e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.126760783512532e-07</v>
+        <v>1.126760783512533e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>3.318525684054813e-08</v>
+        <v>3.318525684054794e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.831167045301527e-08</v>
+        <v>6.831167045301533e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.728142459425861e-08</v>
+        <v>3.728142459425865e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.033525195911128e-08</v>
+        <v>8.033525195911131e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.725680311102123e-09</v>
+        <v>9.725680311102153e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>9.656592320546709e-09</v>
+        <v>9.656592320546673e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.150795890031739e-08</v>
+        <v>1.150798623814189e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.804192046373963e-09</v>
+        <v>9.804192046373912e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.003181904728412e-08</v>
+        <v>1.00318190472841e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.086311374496011e-08</v>
+        <v>1.086311374496012e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.679421133484121e-08</v>
+        <v>1.679421133484125e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.002613824856451e-08</v>
+        <v>1.264917177349155e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.459098955611175e-08</v>
+        <v>1.206395738377623e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.030241782021461e-08</v>
+        <v>1.030241782021462e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.224282830716234e-08</v>
+        <v>1.224282830716235e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.382884800797595e-08</v>
+        <v>1.382884800797598e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.380498203102373e-08</v>
+        <v>1.380498203102375e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.557908064785513e-08</v>
+        <v>1.557908064785517e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4136630074917e-08</v>
+        <v>1.413663007491701e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4136630074917e-08</v>
+        <v>1.413663007491701e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.496628144183394e-08</v>
+        <v>1.496628144183395e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.800147882888426e-08</v>
+        <v>1.800147882888432e-08</v>
       </c>
       <c r="I7" t="n">
         <v>1.412930594543835e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.600149608252135e-08</v>
+        <v>1.600149608252139e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.441146703212607e-08</v>
+        <v>1.441146703212609e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.633037610475082e-08</v>
+        <v>1.633037610475085e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.161310405730492e-08</v>
+        <v>3.161310405730497e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.755577807721538e-08</v>
+        <v>4.755577807726463e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.262846640340245e-08</v>
+        <v>5.26284664034026e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.351527799608213e-08</v>
+        <v>4.351527799608221e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.242406132380095e-08</v>
+        <v>3.242406132380097e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.870664908151298e-08</v>
+        <v>4.870664908151306e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.174184646857071e-08</v>
+        <v>5.174184646857082e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.786967358511743e-08</v>
+        <v>4.786967358511745e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.974499955764472e-08</v>
+        <v>4.974499955764482e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.189933011655844e-08</v>
+        <v>3.18993301165585e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.673823653114163e-08</v>
+        <v>6.673823653114171e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.540689448134575e-08</v>
+        <v>2.540689448134574e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.061162264321757e-08</v>
+        <v>3.061162264321758e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.238613711903685e-08</v>
+        <v>3.238613711903687e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.696987435755086e-08</v>
+        <v>3.696987435755089e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0936187327407e-08</v>
+        <v>3.093618732740692e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.17729220540278e-08</v>
+        <v>3.177292205402778e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.480811944107811e-08</v>
+        <v>3.480811944107818e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.093594655763221e-08</v>
+        <v>3.093594655763219e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.280813669471524e-08</v>
+        <v>3.280813669471523e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.463437395320582e-08</v>
+        <v>2.818864026577175e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.313701671694464e-08</v>
+        <v>3.31370167169447e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.216534207452423e-08</v>
+        <v>1.134941039811776e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.822465541363843e-09</v>
+        <v>9.296840395022326e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.289742891312574e-08</v>
+        <v>1.138793867439185e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.066852678930308e-08</v>
+        <v>9.688638101834129e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.066852678930308e-08</v>
+        <v>9.688476356572027e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.262751925355438e-08</v>
+        <v>1.137373386509232e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.301850535817242e-08</v>
+        <v>1.138228191046277e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.268968910904266e-08</v>
+        <v>1.13771666766854e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.242170198088307e-08</v>
+        <v>1.04745289688934e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.238591093560439e-08</v>
+        <v>1.144861020366127e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.292132056642476e-08</v>
+        <v>1.138718284440096e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.294591569447802e-08</v>
+        <v>1.160298549313255e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.061100949386499e-08</v>
+        <v>8.28283455156418e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.378796721020152e-08</v>
+        <v>1.189815651717605e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.15283204135232e-08</v>
+        <v>9.036946386141333e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.15283204135232e-08</v>
+        <v>9.036784640879169e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.347751519007705e-08</v>
+        <v>1.179769208030174e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.394520509622914e-08</v>
+        <v>1.193744165885631e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.355114627490719e-08</v>
+        <v>1.182181033538659e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.341191633569086e-08</v>
+        <v>1.058426436664693e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.318274216168206e-08</v>
+        <v>1.181879083223182e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.381563923602619e-08</v>
+        <v>1.191204838145701e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.171808513276143e-09</v>
+        <v>7.171808513276139e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.082678143505125e-09</v>
+        <v>7.082678143505132e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.607003117673926e-09</v>
+        <v>7.607003117673917e-09</v>
       </c>
       <c r="E4" t="n">
         <v>7.449769225506346e-09</v>
@@ -2986,19 +2986,19 @@
         <v>7.449769225506346e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.43725389482545e-09</v>
+        <v>7.437253894825447e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.67948291587745e-09</v>
+        <v>7.679482915877453e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.438633112311258e-09</v>
+        <v>7.438633112311246e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.001479631841112e-09</v>
+        <v>8.001479631841121e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.236149378458179e-09</v>
+        <v>7.236149378458171e-09</v>
       </c>
       <c r="L4" t="n">
         <v>7.622132860862875e-09</v>
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.577858158072264e-08</v>
+        <v>1.577858158072265e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.795230188791956e-08</v>
+        <v>2.795230188791954e-08</v>
       </c>
       <c r="D5" t="n">
         <v>3.394012126565769e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.201824602073725e-08</v>
+        <v>3.201824602073727e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.201824602073725e-08</v>
+        <v>3.201824602073727e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.156769277424368e-08</v>
+        <v>3.156769277424372e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.810450418781121e-08</v>
+        <v>3.810450418781112e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.201819391618328e-08</v>
+        <v>3.201819391618351e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.208562955191252e-08</v>
+        <v>4.208562955191249e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.76990595905797e-08</v>
+        <v>2.769905959057966e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.753855382043498e-08</v>
+        <v>3.753855382043502e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3051,34 +3051,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.565369922939535e-09</v>
+        <v>9.565369922939549e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>9.574777771543536e-09</v>
+        <v>9.574777771543521e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.000634668700595e-08</v>
+        <v>1.254395829888352e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.642726882808996e-09</v>
+        <v>9.64272688280899e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.839715429413731e-09</v>
+        <v>9.839715429413735e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.228356353437462e-08</v>
+        <v>9.830815304488836e-09</v>
       </c>
       <c r="H6" t="n">
         <v>1.280658073747521e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.228494275186043e-08</v>
+        <v>1.228494275186042e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.054301063289389e-08</v>
+        <v>1.291498029808541e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.625444785759071e-09</v>
+        <v>9.625444785759073e-09</v>
       </c>
       <c r="L6" t="n">
         <v>1.001897110450446e-08</v>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.354162223690247e-08</v>
+        <v>1.354162223690246e-08</v>
       </c>
       <c r="C7" t="n">
         <v>1.357210894858602e-08</v>
@@ -3100,19 +3100,19 @@
         <v>1.397642421752916e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.381772391102311e-08</v>
+        <v>1.381772391102312e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.381772391102311e-08</v>
+        <v>1.381772391102312e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.380706761845174e-08</v>
+        <v>1.380706761845175e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.404929663950377e-08</v>
+        <v>1.404929663950376e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.380844683593757e-08</v>
+        <v>1.380844683593756e-08</v>
       </c>
       <c r="J7" t="n">
         <v>1.437129335546744e-08</v>
@@ -3121,7 +3121,7 @@
         <v>1.360596310208449e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.399194658448918e-08</v>
+        <v>1.399194658448919e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.037917648509914e-08</v>
+        <v>3.037917648509915e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.556984113336417e-08</v>
+        <v>4.556984113331185e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.910326764068562e-08</v>
+        <v>4.910326764068559e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.166201304665161e-08</v>
+        <v>4.166201304665154e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.113195508536955e-08</v>
+        <v>3.113195508536952e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.57925059696222e-08</v>
+        <v>4.579250596962219e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.603473499069567e-08</v>
+        <v>4.603473499069561e-08</v>
       </c>
       <c r="I8" t="n">
         <v>4.579388518710807e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.635970870205091e-08</v>
+        <v>4.63597087020509e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.016213762591705e-08</v>
+        <v>3.016213762591702e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.180061652879752e-08</v>
+        <v>6.180061652879748e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3171,16 +3171,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.326208987958871e-08</v>
+        <v>2.32620898795887e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.791747883594661e-08</v>
+        <v>2.791747883594658e-08</v>
       </c>
       <c r="D9" t="n">
         <v>2.83221884930125e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.349090572370801e-08</v>
+        <v>3.3490905723708e-08</v>
       </c>
       <c r="F9" t="n">
         <v>2.815386576731802e-08</v>
@@ -3189,16 +3189,16 @@
         <v>2.815243750581234e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.839466652686434e-08</v>
+        <v>2.839466652686432e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.815381672329811e-08</v>
+        <v>2.815381672329813e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.871666324282801e-08</v>
+        <v>2.871666324282799e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.212775506398766e-08</v>
+        <v>2.52716472075678e-08</v>
       </c>
       <c r="L9" t="n">
         <v>2.833731647184975e-08</v>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.236360549604841e-08</v>
+        <v>1.150603135167804e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.986444727906915e-09</v>
+        <v>9.370524989520289e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.305173558019141e-08</v>
+        <v>1.154224627127006e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.063467247838515e-08</v>
+        <v>9.754202052214989e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.063467247838515e-08</v>
+        <v>9.754041165341083e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.272546131180704e-08</v>
+        <v>1.152507510455789e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.292672838597695e-08</v>
+        <v>1.152351644691306e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.275692610366723e-08</v>
+        <v>1.152689331802886e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.193064881037017e-08</v>
+        <v>1.055267806478886e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.244568088502389e-08</v>
+        <v>1.152615717579691e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.272060923494674e-08</v>
+        <v>1.152257429860526e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.317272875422183e-08</v>
+        <v>1.182178146396779e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.081351513346684e-08</v>
+        <v>8.38483884737542e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.396422089670378e-08</v>
+        <v>1.210045351078363e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.150333848323065e-08</v>
+        <v>9.067673133423995e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.150333848323065e-08</v>
+        <v>9.067512246550104e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.358893790055069e-08</v>
+        <v>1.197883233860732e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.383791043980729e-08</v>
+        <v>1.204680683676305e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.362734960376709e-08</v>
+        <v>1.199146558323908e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.285400074902071e-08</v>
+        <v>1.049002400602691e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.326408756184446e-08</v>
+        <v>1.189366804301624e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.358356433258188e-08</v>
+        <v>1.198007021910234e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.308001388493263e-09</v>
+        <v>7.30800138849329e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.25862495720149e-09</v>
+        <v>7.258624957201505e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.717065564971164e-09</v>
+        <v>7.717065564971184e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.507232735070738e-09</v>
+        <v>7.507232735070753e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.507232735070741e-09</v>
+        <v>7.507232735070754e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.513786788701426e-09</v>
+        <v>7.513786788701889e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.643307547691538e-09</v>
+        <v>7.643307547691526e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.496827440769815e-09</v>
+        <v>7.496827440769595e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.760071150458457e-09</v>
+        <v>7.760071150458496e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.344741310906084e-09</v>
+        <v>7.344741310906101e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.521224831816378e-09</v>
+        <v>7.521224831816379e-09</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.631825560438432e-08</v>
+        <v>1.631825560438453e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.921566349224487e-08</v>
+        <v>2.921566349224486e-08</v>
       </c>
       <c r="D5" t="n">
         <v>3.402362868511762e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.121379814809837e-08</v>
+        <v>3.121379814809848e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.121379814809837e-08</v>
+        <v>3.121379814809848e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.106597496824473e-08</v>
+        <v>3.106597496824483e-08</v>
       </c>
       <c r="H5" t="n">
         <v>3.539176747267723e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.121374189994382e-08</v>
+        <v>3.121374189994396e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.589613101745704e-08</v>
+        <v>3.5896131017457e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.775755922835141e-08</v>
+        <v>2.775755922835145e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.351005150894067e-08</v>
+        <v>3.351005150894071e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.220648234956294e-08</v>
+        <v>1.220648234956297e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.752573425621628e-09</v>
+        <v>9.752573425621629e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.011398271700429e-08</v>
+        <v>1.01139827170043e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.694574583819952e-09</v>
+        <v>9.694574583820008e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.896040145331882e-09</v>
+        <v>9.896040145331899e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.241226774977083e-08</v>
+        <v>1.241226774977085e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.287249057494518e-08</v>
+        <v>1.003847562876622e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>9.8889188526182e-09</v>
+        <v>1.23953084018394e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.273613009489623e-08</v>
+        <v>1.030123790141204e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.733197929045991e-09</v>
+        <v>9.733197929045809e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>9.915385552944623e-09</v>
+        <v>9.91538555294464e-09</v>
       </c>
     </row>
     <row r="7">
@@ -3487,34 +3487,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.374985371759311e-08</v>
+        <v>1.374985371759313e-08</v>
       </c>
       <c r="C7" t="n">
         <v>1.382177153668843e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.415852467692092e-08</v>
+        <v>1.415852467692093e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.394833823349281e-08</v>
+        <v>1.394833823349284e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.394833823349281e-08</v>
+        <v>1.394833823349284e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3955639117801e-08</v>
+        <v>1.395563911780103e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.408515987679138e-08</v>
+        <v>1.408515987679139e-08</v>
       </c>
       <c r="I7" t="n">
         <v>1.393867976986957e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.420192347955831e-08</v>
+        <v>1.420192347955834e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.378659364000593e-08</v>
+        <v>1.378659364000594e-08</v>
       </c>
       <c r="L7" t="n">
         <v>1.396307716091621e-08</v>
@@ -3530,34 +3530,34 @@
         <v>3.063775877809011e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.597935983948534e-08</v>
+        <v>4.597935983955394e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.946746599265441e-08</v>
+        <v>4.94674659926543e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.192221960775047e-08</v>
+        <v>4.192221960775045e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.131622730308116e-08</v>
+        <v>3.131622730308114e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.610054806931026e-08</v>
+        <v>4.61005480693103e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.623006882833646e-08</v>
+        <v>4.623006882833651e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.608358872137883e-08</v>
+        <v>4.608358872137881e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.634983087127948e-08</v>
+        <v>4.634983087127947e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.039109202007256e-08</v>
+        <v>3.03910920200726e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.204520244833215e-08</v>
+        <v>6.204520244833211e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.267450712763044e-08</v>
+        <v>2.267450712763045e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.71848106868798e-08</v>
+        <v>2.718481068687983e-08</v>
       </c>
       <c r="D9" t="n">
         <v>2.752195885009381e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.242357604209947e-08</v>
+        <v>3.242357604209949e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.730177213324848e-08</v>
+        <v>2.730177213324851e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.731867826799239e-08</v>
+        <v>2.731867826799244e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.744819902698275e-08</v>
+        <v>2.744819902698285e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.730171892006094e-08</v>
+        <v>2.730171892006098e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.756496262974972e-08</v>
+        <v>2.756496262974973e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.447368158261941e-08</v>
+        <v>2.457801542099218e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.732611631110758e-08</v>
+        <v>2.732611631110764e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.20633143096998e-08</v>
+        <v>1.131066011605797e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.703224222653484e-09</v>
+        <v>9.295895496726162e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.305454099449376e-08</v>
+        <v>1.136282640774412e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.063791734365443e-08</v>
+        <v>9.67018642584994e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.063791734365445e-08</v>
+        <v>9.670024837108081e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.290047661788505e-08</v>
+        <v>1.13547183055997e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.790729600573886e-08</v>
+        <v>1.160878592955564e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.263794696088657e-08</v>
+        <v>1.13410585207472e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.155220536720344e-08</v>
+        <v>1.039606821623508e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.237542446203799e-08</v>
+        <v>1.143255783705906e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.545634206786561e-08</v>
+        <v>1.148883226298124e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.282706551359728e-08</v>
+        <v>1.152262250496994e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.046533751663934e-08</v>
+        <v>8.245758784673333e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.396718153309945e-08</v>
+        <v>1.191495605037017e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.148842952104822e-08</v>
+        <v>9.004577941597745e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.148842952104796e-08</v>
+        <v>9.004416352855861e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.378997558565994e-08</v>
+        <v>1.185808936252299e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.956726063286607e-08</v>
+        <v>1.374189947434348e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.348995711616506e-08</v>
+        <v>1.176029544059181e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.241018702576593e-08</v>
+        <v>1.021633506748711e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.316573902298477e-08</v>
+        <v>1.179568398276878e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.672982606868506e-08</v>
+        <v>1.282889318829445e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.129320759723848e-09</v>
+        <v>7.129320759723927e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>6.991671755148476e-09</v>
+        <v>6.991671755148478e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.718563021996231e-09</v>
+        <v>7.718563021996345e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.431489560555355e-09</v>
+        <v>7.431489560555362e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.431489560555356e-09</v>
+        <v>7.431489560555362e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.617538141660014e-09</v>
+        <v>7.617538141660089e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.060275647830077e-08</v>
+        <v>1.060275647830082e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>7.425032473877185e-09</v>
+        <v>7.425032473877197e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.502245834515147e-09</v>
+        <v>7.502245834515223e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.234447514651421e-09</v>
+        <v>7.234447514651516e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>9.146747812555081e-09</v>
+        <v>9.146747812555134e-09</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.564930824994353e-08</v>
+        <v>1.564930824994354e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.777211586577842e-08</v>
+        <v>2.777211586577838e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.757290141484726e-08</v>
+        <v>3.757290141484728e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.332959885958149e-08</v>
+        <v>3.33295988595813e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.332959885958149e-08</v>
+        <v>3.33295988595813e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.640620992405931e-08</v>
+        <v>3.640620992405959e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.889765714524266e-08</v>
+        <v>9.889765714524291e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.33295018516309e-08</v>
+        <v>3.332950185163081e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.478149230105231e-08</v>
+        <v>3.478149230105239e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.897870632965957e-08</v>
+        <v>2.897870632965973e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.071079276226159e-08</v>
+        <v>7.071079276226184e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.670892595441067e-09</v>
+        <v>9.670892595441204e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>9.633032676957673e-09</v>
+        <v>9.633032676957646e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.026734745141567e-08</v>
+        <v>1.026734745141573e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.763135813943548e-09</v>
+        <v>9.763135813943535e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.974022281799496e-09</v>
+        <v>9.974022281799501e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.274844158570744e-08</v>
+        <v>1.015910997737736e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.600287186789942e-08</v>
+        <v>1.600287186789943e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.255593591792457e-08</v>
+        <v>9.966604309594492e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.26999427257503e-08</v>
+        <v>1.019691188598798e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.768549170047611e-09</v>
+        <v>9.768549170047639e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.170108280309126e-08</v>
+        <v>1.170108280309129e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.380144991567335e-08</v>
+        <v>1.380144991567344e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.379190620485868e-08</v>
+        <v>1.379190620485867e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.439027776817554e-08</v>
+        <v>1.439027776817549e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.410581085423674e-08</v>
+        <v>1.410581085423673e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.410581085423674e-08</v>
+        <v>1.410581085423673e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.428966729760953e-08</v>
+        <v>1.428966729760961e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.72748856342502e-08</v>
+        <v>1.727488563425032e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.409716162982671e-08</v>
+        <v>1.40971616298267e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.417437499046472e-08</v>
+        <v>1.41743749904648e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.390657667060097e-08</v>
+        <v>1.390657667060102e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.581887696850461e-08</v>
+        <v>1.58188769685047e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.155500217418637e-08</v>
+        <v>3.155500217418636e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.748506373465103e-08</v>
+        <v>4.748506373460198e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.137474696202544e-08</v>
+        <v>5.137474696202554e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.343294904937698e-08</v>
+        <v>4.343294904937692e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.236104578603035e-08</v>
+        <v>3.23610457860303e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.797099424081792e-08</v>
+        <v>4.797099424081785e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.095621257746582e-08</v>
+        <v>5.095621257746583e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.7778488573035e-08</v>
+        <v>4.777848857303498e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.785883220011146e-08</v>
+        <v>4.785883220011163e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.136426233678742e-08</v>
+        <v>3.13642623367874e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.613809643098225e-08</v>
+        <v>6.613809643098217e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.515399572071883e-08</v>
+        <v>2.515399572071897e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.030684056026662e-08</v>
+        <v>3.03068405602666e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.090562774339922e-08</v>
+        <v>3.090562774339929e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.65694760346795e-08</v>
+        <v>3.656947603467949e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.061218900985595e-08</v>
+        <v>3.061218900985592e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.080460165301752e-08</v>
+        <v>3.080460165301755e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.378981998965825e-08</v>
+        <v>3.378981998965827e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.061209598523467e-08</v>
+        <v>3.061209598523465e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.068930934587263e-08</v>
+        <v>3.068930934587271e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.743040333460538e-08</v>
+        <v>2.743040333460546e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.233381132391255e-08</v>
+        <v>3.233381132391261e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.257900105354376e-08</v>
+        <v>1.169317904866786e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.917250620845065e-09</v>
+        <v>9.375335100525709e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.325289181287596e-08</v>
+        <v>1.172864458087665e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.070047819680556e-08</v>
+        <v>9.751111592127308e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.070047819680556e-08</v>
+        <v>9.750949679431945e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.29247612957132e-08</v>
+        <v>1.171137572347809e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.314049669977477e-08</v>
+        <v>1.171063062501301e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.305661938225066e-08</v>
+        <v>1.171847689979724e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.185961435754816e-08</v>
+        <v>1.047842100056681e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.247737688334223e-08</v>
+        <v>1.152661631022493e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.289016348929122e-08</v>
+        <v>1.170730955272332e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.337377894391251e-08</v>
+        <v>1.212568490934029e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.071996272093379e-08</v>
+        <v>8.367534851245285e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.414889291319479e-08</v>
+        <v>1.239901188978126e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.156745942198065e-08</v>
+        <v>9.08183258374256e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.156745942198065e-08</v>
+        <v>9.081670671047177e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.377147484642578e-08</v>
+        <v>1.227668498118573e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.403750746510073e-08</v>
+        <v>1.235013012022136e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.392568132597552e-08</v>
+        <v>1.232696909343062e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.277304949488744e-08</v>
+        <v>1.037093911538026e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.328794598621558e-08</v>
+        <v>1.190187850246529e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.373188708915453e-08</v>
+        <v>1.226664482777613e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.208640746080827e-09</v>
+        <v>7.208640746080837e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.120167618865884e-09</v>
+        <v>7.120167618865875e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.609240247330088e-09</v>
+        <v>7.609240247330094e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.467928638284443e-09</v>
+        <v>7.467928638284441e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.467928638284445e-09</v>
+        <v>7.46792863828444e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.404885731263712e-09</v>
+        <v>7.404885731263677e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.542971538724346e-09</v>
+        <v>7.54297153872442e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.447719913044914e-09</v>
+        <v>7.447719913044895e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.678236938292497e-09</v>
+        <v>7.678236938292517e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.271135818669187e-09</v>
+        <v>7.271135818669168e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.394613878450285e-09</v>
+        <v>7.394613878450322e-09</v>
       </c>
     </row>
     <row r="5">
@@ -4202,31 +4202,31 @@
         <v>1.62366721207763e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.840796906903888e-08</v>
+        <v>2.840796906903889e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.379406885070882e-08</v>
+        <v>3.379406885070875e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.198793589314912e-08</v>
+        <v>3.198793589314911e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.198793589314912e-08</v>
+        <v>3.198793589314911e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.081251461333545e-08</v>
+        <v>3.081251461333473e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.528427513380939e-08</v>
+        <v>3.528427513380937e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.198789267833879e-08</v>
+        <v>3.198789267833881e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.612206432974415e-08</v>
+        <v>3.612206432974421e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.811129673605522e-08</v>
+        <v>2.811129673605521e-08</v>
       </c>
       <c r="L5" t="n">
         <v>3.288910603834863e-08</v>
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.592557310123458e-09</v>
+        <v>1.205133547495601e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.603459491001745e-09</v>
+        <v>9.603459491001737e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.999415856686137e-09</v>
+        <v>9.99939034502079e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>9.644164142771666e-09</v>
+        <v>9.644164142771664e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.839628384020018e-09</v>
+        <v>9.839628384019999e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>9.788802295306308e-09</v>
+        <v>9.788802295306282e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.266381582235995e-08</v>
+        <v>1.266381582235996e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.229041464192007e-08</v>
+        <v>1.229041464192006e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.258749986553287e-08</v>
+        <v>1.020806194447529e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.652710403096136e-09</v>
+        <v>9.652710403096044e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>9.780376685232679e-09</v>
+        <v>9.780376685232674e-09</v>
       </c>
     </row>
     <row r="7">
@@ -4282,22 +4282,22 @@
         <v>1.359480650989078e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.362530755431095e-08</v>
+        <v>1.362530755431096e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.399501359155683e-08</v>
+        <v>1.399501359155682e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.384563547355162e-08</v>
+        <v>1.384563547355159e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.384563547355162e-08</v>
+        <v>1.384563547355159e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.379105149507366e-08</v>
+        <v>1.379105149507362e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.392913730253438e-08</v>
+        <v>1.392913730253436e-08</v>
       </c>
       <c r="I7" t="n">
         <v>1.383388567685485e-08</v>
@@ -4306,10 +4306,10 @@
         <v>1.406440270210246e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.365730158247913e-08</v>
+        <v>1.365730158247911e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.378077964226028e-08</v>
+        <v>1.378077964226027e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4322,34 +4322,34 @@
         <v>3.042325876399272e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.562619627376447e-08</v>
+        <v>4.562619627376438e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.912468969618829e-08</v>
+        <v>4.912468969618814e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.168764542627292e-08</v>
+        <v>4.168764542627285e-08</v>
       </c>
       <c r="F8" t="n">
         <v>3.115007666571416e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.57772729851765e-08</v>
+        <v>4.577727298517639e-08</v>
       </c>
       <c r="H8" t="n">
         <v>4.591535879265837e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.582010716695765e-08</v>
+        <v>4.582010716695764e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.605360313034287e-08</v>
+        <v>4.605360313034283e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.020419049079439e-08</v>
+        <v>3.020419049079437e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.160055857354095e-08</v>
+        <v>6.160055857354088e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.328754750666648e-08</v>
+        <v>2.328754750666646e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.794210258444688e-08</v>
+        <v>2.794210258444685e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.831220281424582e-08</v>
+        <v>2.831220281424578e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.348678205851535e-08</v>
+        <v>3.348678205851532e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.81507209020184e-08</v>
+        <v>2.815072090201835e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.810784652520954e-08</v>
+        <v>2.810784652520951e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.82459323326703e-08</v>
+        <v>2.824593233267026e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.81506807069908e-08</v>
+        <v>2.815068070699072e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.838119773223835e-08</v>
+        <v>2.838119773223833e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.529490229132907e-08</v>
+        <v>2.215158673437359e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.80975746723962e-08</v>
+        <v>2.809757467239617e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.245966370834305e-08</v>
+        <v>1.168363284691634e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.003626787417313e-08</v>
+        <v>9.524123878070629e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.309132526562569e-08</v>
+        <v>1.171687594009522e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.064904977145343e-08</v>
+        <v>9.865254538209455e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.064904977145343e-08</v>
+        <v>9.865093178720407e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.280418138424921e-08</v>
+        <v>1.17017641279321e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.300826418668227e-08</v>
+        <v>1.170037929673789e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.285114127549325e-08</v>
+        <v>1.170439770515643e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.197583527254516e-08</v>
+        <v>1.064566733293494e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.250540406980697e-08</v>
+        <v>1.165088231519496e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.280048479362851e-08</v>
+        <v>1.169933362337378e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.328958135130797e-08</v>
+        <v>1.194389460443443e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.088136891045876e-08</v>
+        <v>8.461943720397096e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.40161229904804e-08</v>
+        <v>1.220139321775154e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.153823300199915e-08</v>
+        <v>9.079396244549417e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>1.153823300199915e-08</v>
+        <v>9.079234885060346e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.368584804522163e-08</v>
+        <v>1.209443393374911e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.393799541572041e-08</v>
+        <v>1.216347896663933e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.374248394292673e-08</v>
+        <v>1.211288032880717e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.292812400786477e-08</v>
+        <v>1.04881312371639e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.334896493098123e-08</v>
+        <v>1.193685168371238e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.368180512007601e-08</v>
+        <v>1.209609473258078e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.308371112004372e-09</v>
+        <v>7.308371112004347e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.248525496792053e-09</v>
+        <v>7.248525496792042e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.683867142038242e-09</v>
+        <v>7.683867142038211e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.516335874346423e-09</v>
+        <v>7.516335874346388e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.516335874346428e-09</v>
+        <v>7.516335874346388e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.503743568378678e-09</v>
+        <v>7.503743568378665e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.63504455456181e-09</v>
+        <v>7.635044554561787e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.495378943073399e-09</v>
+        <v>7.495378943073379e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.792665164611458e-09</v>
+        <v>7.792665164611427e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.362365313658341e-09</v>
+        <v>7.362365313658316e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.511971753489355e-09</v>
+        <v>7.511971753489334e-09</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.640013590344786e-08</v>
+        <v>1.640013590344782e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.910636177352823e-08</v>
+        <v>2.910636177352822e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.353078855194046e-08</v>
+        <v>3.353078855194032e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.127279386120735e-08</v>
+        <v>3.127279386120783e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.127279386120735e-08</v>
+        <v>3.127279386120783e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.096587725850077e-08</v>
+        <v>3.096587725850074e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.531472596909309e-08</v>
+        <v>3.531472596909298e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.127273884817457e-08</v>
+        <v>3.127273884817423e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.655326896352806e-08</v>
+        <v>3.655326896352805e-08</v>
       </c>
       <c r="K5" t="n">
         <v>2.813007629600898e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.341230737992864e-08</v>
+        <v>3.341230737992858e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.687029477501432e-09</v>
+        <v>1.219132334162479e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.728452121309261e-09</v>
+        <v>9.728452121309256e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.006684843274358e-08</v>
+        <v>1.006687381227047e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.682683224262011e-09</v>
+        <v>9.682683224261986e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.881825744567545e-09</v>
+        <v>9.881825744567536e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.238669579799912e-08</v>
+        <v>9.882401933875741e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.284068245818426e-08</v>
+        <v>1.284068245818423e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.237833117269382e-08</v>
+        <v>9.874037308570456e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.031863071493363e-08</v>
+        <v>1.275163385244796e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.738088448461476e-09</v>
+        <v>9.738088448461454e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>9.893275952738367e-09</v>
+        <v>9.893275952738399e-09</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.37618242004222e-08</v>
+        <v>1.376182420042218e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.382279169653838e-08</v>
+        <v>1.382279169653835e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.41369271325055e-08</v>
+        <v>1.413692713250549e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.396151675783194e-08</v>
+        <v>1.396151675783191e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.396151675783194e-08</v>
+        <v>1.396151675783191e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.39571966567965e-08</v>
+        <v>1.395719665679649e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.408849764297963e-08</v>
+        <v>1.40884976429796e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.394883203149124e-08</v>
+        <v>1.394883203149121e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.424611825302927e-08</v>
+        <v>1.424611825302925e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.381581840207616e-08</v>
+        <v>1.381581840207615e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.396542484190718e-08</v>
+        <v>1.396542484190716e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.063427469700336e-08</v>
+        <v>3.063427469700328e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.596462997753791e-08</v>
+        <v>4.596462997747052e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.942656404149906e-08</v>
+        <v>4.942656404149893e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.191718672329833e-08</v>
+        <v>4.191718672329823e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.131262867158606e-08</v>
+        <v>3.131262867158604e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.608346248857413e-08</v>
+        <v>4.608346248857403e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.621476347479249e-08</v>
+        <v>4.621476347479245e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.607509786326878e-08</v>
+        <v>4.607509786326874e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.637538189852236e-08</v>
+        <v>4.637538189852237e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.040492144727356e-08</v>
+        <v>3.040492144727359e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.202557629655807e-08</v>
+        <v>6.2025576296558e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.267042175703663e-08</v>
+        <v>2.267042175703662e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.716822088471698e-08</v>
+        <v>2.716822088471694e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.748275121314452e-08</v>
+        <v>2.748275121314445e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.241432370266672e-08</v>
+        <v>3.24143237026667e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.729431320947583e-08</v>
+        <v>2.729431320947573e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.730262584497515e-08</v>
+        <v>2.73026258449751e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.743392683115824e-08</v>
+        <v>2.743392683115818e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.729426121966985e-08</v>
+        <v>2.729426121966979e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.759154744120785e-08</v>
+        <v>2.759154744120781e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.448623336746414e-08</v>
+        <v>2.44862333674641e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.731085403008575e-08</v>
+        <v>2.731085403008569e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.771459907632718e-08</v>
+        <v>1.203182003729282e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.237585206017735e-08</v>
+        <v>1.057688787972531e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.049773754710638e-08</v>
+        <v>1.217829108725169e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.268595599509896e-08</v>
+        <v>1.08610294143222e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.157602798074652e-08</v>
+        <v>9.937000810093668e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.77813230064116e-08</v>
+        <v>1.203533158520876e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.911132806803282e-08</v>
+        <v>1.26245459901927e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.38411130297236e-08</v>
+        <v>1.182808537971609e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.559483223398554e-08</v>
+        <v>1.198093271407889e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.459619187563124e-08</v>
+        <v>1.144703158786176e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.362716886493413e-08</v>
+        <v>1.287781264635868e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.931721228615589e-08</v>
+        <v>1.392923013053391e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.338869220229864e-08</v>
+        <v>1.043871252597864e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.251839805294934e-08</v>
+        <v>1.497381434760496e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.370708417612333e-08</v>
+        <v>1.088900134655416e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.259715616177087e-08</v>
+        <v>9.363826047231455e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.939395862757343e-08</v>
+        <v>1.395939399997583e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.244352571761369e-08</v>
+        <v>1.823492106890783e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.486034229345187e-08</v>
+        <v>1.248292736013954e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.686735366909542e-08</v>
+        <v>1.322006946088746e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.581143524006128e-08</v>
+        <v>1.222451409531812e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.76194045508902e-08</v>
+        <v>1.997089873773236e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.059963346091396e-08</v>
+        <v>1.059963346091398e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.173596603698607e-09</v>
+        <v>8.173596603698597e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.225409135021135e-08</v>
+        <v>1.225409135021133e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.198936453927121e-09</v>
+        <v>8.198936453927108e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>8.198936453927121e-09</v>
+        <v>8.198936453927109e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.062863930336887e-08</v>
+        <v>1.062863930336894e-08</v>
       </c>
       <c r="H4" t="n">
         <v>1.737248543073304e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.242398093422759e-09</v>
+        <v>8.242398093422748e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>9.293267061507516e-09</v>
+        <v>9.293267061507514e-09</v>
       </c>
       <c r="K4" t="n">
         <v>9.066584203315466e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>2.005651432869051e-08</v>
+        <v>2.005651432869052e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.335111715210258e-08</v>
+        <v>8.335111715210313e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.41000890990958e-08</v>
+        <v>4.410008909909571e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.141957747113493e-07</v>
+        <v>1.141957747113491e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>4.410009118329398e-08</v>
+        <v>4.410009118329388e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.410009118329398e-08</v>
+        <v>4.410009118329388e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.692779666791406e-08</v>
+        <v>8.692779666791361e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.298417436387264e-07</v>
+        <v>2.298417436387263e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>4.409949084157216e-08</v>
+        <v>4.409949084157211e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.385552383482893e-08</v>
+        <v>6.385552383482887e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.726100308060181e-08</v>
+        <v>5.726100308060208e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.04825205071206e-08</v>
+        <v>7.048252050712053e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5031,34 +5031,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.623643000927902e-08</v>
+        <v>1.334175979923778e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.091725193316454e-08</v>
+        <v>1.091725193316451e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.508194522061272e-08</v>
+        <v>1.508191399652968e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.071249264644087e-08</v>
+        <v>1.071249264644085e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.098326610328813e-08</v>
+        <v>1.098326610328811e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.626543585173392e-08</v>
+        <v>1.337076564169262e-08</v>
       </c>
       <c r="H6" t="n">
         <v>2.314973615559761e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.387919464178783e-08</v>
+        <v>1.387919464178782e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.495370403346508e-08</v>
+        <v>1.220261059074621e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.178500063198786e-08</v>
+        <v>1.17850006319878e-08</v>
       </c>
       <c r="L6" t="n">
         <v>2.286991767868324e-08</v>
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.745078469248261e-08</v>
+        <v>1.745078469248262e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5094147582515e-08</v>
+        <v>1.509414758251499e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.910479664068581e-08</v>
+        <v>1.910479664068579e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.509253314160145e-08</v>
+        <v>1.509253314160143e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.509253314160145e-08</v>
+        <v>1.509253314160143e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.747979053493751e-08</v>
+        <v>1.747979053493755e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.422363666230167e-08</v>
+        <v>2.422363666230168e-08</v>
       </c>
       <c r="I7" t="n">
         <v>1.509354932499139e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.614441829307615e-08</v>
+        <v>1.614441829307616e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.59177354348841e-08</v>
+        <v>1.591773543488412e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.690766556025917e-08</v>
+        <v>2.690766556025916e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.555054695389845e-08</v>
+        <v>3.555054695389849e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.945792679721721e-08</v>
+        <v>4.945792679725677e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.683879241994161e-08</v>
+        <v>5.683879241994164e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.501011464661643e-08</v>
+        <v>4.501011464661642e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.370868749867102e-08</v>
+        <v>3.370868749867099e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.184135065182953e-08</v>
+        <v>5.184135065182955e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.858519677919395e-08</v>
+        <v>5.858519677919398e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.945510944188346e-08</v>
+        <v>4.945510944188352e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.05091743215477e-08</v>
+        <v>5.050917432154766e-08</v>
       </c>
       <c r="K8" t="n">
         <v>3.371542645209961e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>7.825603332882769e-08</v>
+        <v>7.82560333288277e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.001571787577781e-08</v>
+        <v>3.001571787577777e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.320640029263495e-08</v>
+        <v>3.320640029263488e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.721749604926507e-08</v>
+        <v>3.721749604926511e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.960788479527843e-08</v>
+        <v>3.960788479527846e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.320639647444944e-08</v>
+        <v>3.320639647444939e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.559204324505743e-08</v>
+        <v>3.559204324505742e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>4.23358893724216e-08</v>
+        <v>4.233588937242165e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.320580203511135e-08</v>
+        <v>3.320580203511134e-08</v>
       </c>
       <c r="J9" t="n">
         <v>3.42566710031961e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.081584974370207e-08</v>
+        <v>3.081584974370211e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.50199182703791e-08</v>
+        <v>4.501991827037908e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.672876203507606e-08</v>
+        <v>1.200913009475776e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.321689868574274e-08</v>
+        <v>1.068158219518731e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.003169902396019e-08</v>
+        <v>1.218295710832149e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.352937623589191e-08</v>
+        <v>1.096763484449515e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.241094569865643e-08</v>
+        <v>1.003652870182221e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.769423025335431e-08</v>
+        <v>1.205994076951143e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.700572210086011e-08</v>
+        <v>1.254179180027226e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.464200456530198e-08</v>
+        <v>1.18994365976566e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.492087081553379e-08</v>
+        <v>1.200624075780301e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.474227933662571e-08</v>
+        <v>1.150711793864314e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.214427920186074e-08</v>
+        <v>1.282795030553432e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.818524788212214e-08</v>
+        <v>1.357986400263784e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.435155120454914e-08</v>
+        <v>1.081086207019539e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.198430962067484e-08</v>
+        <v>1.481582178791677e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.467278267327741e-08</v>
+        <v>1.126460668851894e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.355435213604193e-08</v>
+        <v>9.727748810186136e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.929573632928119e-08</v>
+        <v>1.394409597754615e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.002293262543766e-08</v>
+        <v>1.74592356809391e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.578421096161955e-08</v>
+        <v>1.280033908920515e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.608802647132671e-08</v>
+        <v>1.302561345389675e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.597694827830415e-08</v>
+        <v>1.232522411210073e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.59157947866697e-08</v>
+        <v>1.942977541840208e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5347,34 +5347,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.002189085973559e-08</v>
+        <v>1.002189085973562e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.674087907367402e-09</v>
+        <v>8.67408790736741e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.198534694231475e-08</v>
+        <v>1.198534694231477e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.697122971946288e-09</v>
+        <v>8.697122971946293e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>8.697122971946288e-09</v>
+        <v>8.69712297194629e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.058551132571444e-08</v>
+        <v>1.058551132571455e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.612955428252009e-08</v>
+        <v>1.612955428252007e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.729248057446661e-09</v>
+        <v>8.729248057446681e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.876841909306918e-09</v>
+        <v>8.876841909306925e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>9.144031506107543e-09</v>
+        <v>9.144031506107553e-09</v>
       </c>
       <c r="L4" t="n">
         <v>1.918361215908945e-08</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.90701457427799e-08</v>
+        <v>6.907014574277995e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.88453901671798e-08</v>
+        <v>4.884539016717981e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.01385145767511e-07</v>
+        <v>1.013851457675114e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>4.88453921246368e-08</v>
+        <v>4.884539212463677e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.88453921246368e-08</v>
+        <v>4.884539212463678e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.003660636776182e-08</v>
+        <v>8.003660636776302e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.917569033676699e-07</v>
+        <v>1.917569033676695e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>4.884491312008832e-08</v>
+        <v>4.884491312008835e-08</v>
       </c>
       <c r="J5" t="n">
         <v>5.228266344932268e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.37572335784221e-08</v>
+        <v>5.37572335784222e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.228633886626511e-08</v>
+        <v>7.228633886626517e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.527331222610959e-08</v>
+        <v>1.256741311054591e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.122845532307327e-08</v>
+        <v>1.122845532307326e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.460127984976997e-08</v>
+        <v>1.460127984977061e-08</v>
       </c>
       <c r="E6" t="n">
         <v>1.103658004668028e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.127797419316095e-08</v>
+        <v>1.127797419316097e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.583693269208847e-08</v>
+        <v>1.313103357652488e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.150632161967805e-08</v>
+        <v>2.150632161967802e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.398066942382067e-08</v>
+        <v>1.398066942382066e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.415230501649335e-08</v>
+        <v>1.157695617977931e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.166889983583759e-08</v>
+        <v>1.16688998358376e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.179104323824574e-08</v>
+        <v>2.179104323824576e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.645701507406401e-08</v>
+        <v>1.645701507406402e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.516484931886654e-08</v>
+        <v>1.516484931886657e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.842005411547445e-08</v>
+        <v>1.842005411547452e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.516407885147586e-08</v>
+        <v>1.516407885147587e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.516407885147586e-08</v>
+        <v>1.516407885147587e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.702063554004294e-08</v>
+        <v>1.702063554004297e-08</v>
       </c>
       <c r="H7" t="n">
         <v>2.25646784968485e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.516437227177507e-08</v>
+        <v>1.516437227177508e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.531196612363532e-08</v>
+        <v>1.531196612363535e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.557915572043596e-08</v>
+        <v>1.557915572043598e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.561873637341786e-08</v>
+        <v>2.56187363734179e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.332387805276406e-08</v>
+        <v>3.332387805276409e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.723575525611247e-08</v>
+        <v>4.723575525611259e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.364067736230342e-08</v>
+        <v>5.364067736230348e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.307793868667976e-08</v>
+        <v>4.307793868667983e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.251335879696225e-08</v>
+        <v>3.251335879696229e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.908876095281996e-08</v>
+        <v>4.908876095282006e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.463280390962581e-08</v>
+        <v>5.463280390962584e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.723249768455218e-08</v>
+        <v>4.723249768455217e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.738307902221291e-08</v>
+        <v>4.738307902221302e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.216364744488417e-08</v>
+        <v>3.216364744488422e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>7.356585150952195e-08</v>
+        <v>7.3565851509522e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5547,34 +5547,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.70969603426046e-08</v>
+        <v>2.709696034260468e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.069911150928986e-08</v>
+        <v>3.069911150928997e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.395473426984346e-08</v>
+        <v>3.395473426984342e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.634704582244948e-08</v>
+        <v>3.634704582244955e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.069910832271506e-08</v>
+        <v>3.069910832271509e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.25548977304663e-08</v>
+        <v>3.255489773046633e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.809894068727184e-08</v>
+        <v>3.809894068727188e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.069863446219842e-08</v>
+        <v>3.069863446219846e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.084622831405872e-08</v>
+        <v>3.084622831405874e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.495059903456477e-08</v>
+        <v>2.827763185297141e-08</v>
       </c>
       <c r="L9" t="n">
         <v>4.115299856384125e-08</v>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.608664520365262e-08</v>
+        <v>1.198364720888366e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.493012813299794e-08</v>
+        <v>1.083354142709164e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.908683882398787e-08</v>
+        <v>1.214154144025741e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.524277559892836e-08</v>
+        <v>1.111952853363308e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.412253653574874e-08</v>
+        <v>1.018691630022678e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.718537056139727e-08</v>
+        <v>1.204147094221741e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.462790139365832e-08</v>
+        <v>1.242402909136769e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.628649970388828e-08</v>
+        <v>1.199431508531728e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.499571787002352e-08</v>
+        <v>1.206138744167445e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.460148395156016e-08</v>
+        <v>1.153077693476887e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.029043495936424e-08</v>
+        <v>1.273779956808179e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.744505851893307e-08</v>
+        <v>1.33467888627292e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.630991298713458e-08</v>
+        <v>1.15266404513312e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.089590267055475e-08</v>
+        <v>1.446792240749043e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.663163641150286e-08</v>
+        <v>1.198103073532602e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.551139734832332e-08</v>
+        <v>1.044168725283158e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.870882028061165e-08</v>
+        <v>1.376060761613204e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.728579327256022e-08</v>
+        <v>1.656121470412363e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.767570780233456e-08</v>
+        <v>1.342265034684652e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.616423050546665e-08</v>
+        <v>1.311740662197846e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.580899832769324e-08</v>
+        <v>1.230898444587503e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.378192911609643e-08</v>
+        <v>1.873170195016341e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5746,34 +5746,34 @@
         <v>9.715481373588648e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>9.752534440147097e-09</v>
+        <v>9.752534440147152e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.14989693518902e-08</v>
+        <v>1.149896935189021e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>9.774507715038931e-09</v>
+        <v>9.774507715039017e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>9.774507715038918e-09</v>
+        <v>9.774507715039019e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.035911290180268e-08</v>
+        <v>1.035911290180259e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.479177350778207e-08</v>
+        <v>1.479177350778208e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.787752652397771e-09</v>
+        <v>9.787752652397774e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.963933209217702e-09</v>
+        <v>8.963933209217709e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>9.118285930060484e-09</v>
+        <v>9.118285930060514e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.815717159395415e-08</v>
+        <v>1.815717159395429e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.185742993077395e-08</v>
+        <v>6.185742993077398e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.379773706090822e-08</v>
+        <v>6.379773706090848e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.041355629373891e-08</v>
+        <v>9.041355629373923e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.379773876232865e-08</v>
+        <v>6.379773876232923e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.379773876232865e-08</v>
+        <v>6.379773876232923e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.398437305451783e-08</v>
+        <v>7.398437305451744e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.599278375648994e-07</v>
+        <v>1.599278375648997e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>6.379755361862161e-08</v>
+        <v>6.379755361862237e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.236415795751431e-08</v>
+        <v>5.23641579575143e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.119516120150315e-08</v>
+        <v>5.119516120150319e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.340791761437902e-07</v>
+        <v>6.443276056918323e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.226934570594547e-08</v>
+        <v>1.226934570594551e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.233346422325798e-08</v>
+        <v>1.233346422325805e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.679479418924269e-08</v>
+        <v>1.410813979645838e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.213945177832181e-08</v>
+        <v>1.213945177832176e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.235449654758712e-08</v>
+        <v>1.235449654758709e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.291297723415953e-08</v>
+        <v>1.560527213491899e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.015933946979547e-08</v>
+        <v>2.015933946979549e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.503391188551427e-08</v>
+        <v>1.234161698475466e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.167472547263741e-08</v>
+        <v>1.423268815783213e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.165104845029818e-08</v>
+        <v>1.165104845029819e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.07680245481921e-08</v>
+        <v>2.076802454819219e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5863,25 +5863,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.618145003914192e-08</v>
+        <v>1.618145003914194e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.625390476023716e-08</v>
+        <v>1.625390476023714e-08</v>
       </c>
       <c r="D7" t="n">
         <v>1.796451867553435e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.625486168026996e-08</v>
+        <v>1.625486168027e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.625486168026996e-08</v>
+        <v>1.625486168027e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.682508156735588e-08</v>
+        <v>1.682508156735577e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.125774217333532e-08</v>
+        <v>2.125774217333537e-08</v>
       </c>
       <c r="I7" t="n">
         <v>1.625372131795109e-08</v>
@@ -5890,10 +5890,10 @@
         <v>1.5429901874771e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.558425459561378e-08</v>
+        <v>1.558425459561381e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.462314025950762e-08</v>
+        <v>2.462314025950754e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.303569504301643e-08</v>
+        <v>3.303569504301651e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.833310906690314e-08</v>
+        <v>4.833310906690325e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.319577698448788e-08</v>
+        <v>5.319577698448802e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.416984878654635e-08</v>
+        <v>4.416984878654639e-08</v>
       </c>
       <c r="F8" t="n">
         <v>3.359143843796651e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.889984656174076e-08</v>
+        <v>4.889984656174083e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.333250716772092e-08</v>
+        <v>5.3332507167721e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.832848631233589e-08</v>
+        <v>4.832848631233594e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.750765813960529e-08</v>
+        <v>4.750765813960538e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.215577062623972e-08</v>
+        <v>3.215577062623977e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>7.25970111051938e-08</v>
+        <v>7.259701110519401e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5946,34 +5946,34 @@
         <v>2.596253895752612e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.070366093464763e-08</v>
+        <v>3.070366093464767e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.241469518161426e-08</v>
+        <v>3.241469518161431e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.609120066105597e-08</v>
+        <v>3.609120066105596e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.070365792290529e-08</v>
+        <v>3.070365792290536e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.127483774176644e-08</v>
+        <v>3.12748377417664e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.570749834774584e-08</v>
+        <v>3.570749834774588e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.070347749236156e-08</v>
+        <v>3.070347749236161e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.987965804918153e-08</v>
+        <v>2.987965804918156e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.732896704290118e-08</v>
+        <v>2.73289670429012e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.907289643391799e-08</v>
+        <v>3.907289643391806e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.272978810631351e-08</v>
+        <v>1.138964463327186e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.100369855519e-08</v>
+        <v>1.012330989879279e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.433705516805334e-08</v>
+        <v>1.14742319064417e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.129918056279557e-08</v>
+        <v>1.03928427991044e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.023236141972938e-08</v>
+        <v>9.504694345695996e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.361922528295567e-08</v>
+        <v>1.143645394531402e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.733556426644123e-08</v>
+        <v>1.16217125146377e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.247353224648819e-08</v>
+        <v>1.13763045051633e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.409764696968274e-08</v>
+        <v>1.147527645984156e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.251625854397818e-08</v>
+        <v>1.092344251959106e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.692531803263927e-08</v>
+        <v>1.161049127070705e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.357580166304458e-08</v>
+        <v>1.185147587432823e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.180364900579631e-08</v>
+        <v>9.708908916149482e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.542449172841418e-08</v>
+        <v>1.245265441679693e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.210711967078177e-08</v>
+        <v>1.01374812680033e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.104030052771559e-08</v>
+        <v>8.671534260252086e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.459883866253915e-08</v>
+        <v>1.218555394634063e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.889101919925963e-08</v>
+        <v>1.357381489686571e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.32814456675105e-08</v>
+        <v>1.175848573480909e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.514649434084711e-08</v>
+        <v>1.238421609671352e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.341784148066607e-08</v>
+        <v>1.118815930326026e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.840154363279467e-08</v>
+        <v>1.343883867315703e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.531888352584277e-09</v>
+        <v>7.531888352584313e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.287045482993552e-09</v>
+        <v>7.287045482993555e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>8.487340515105955e-09</v>
+        <v>8.487340515105942e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.309796412555734e-09</v>
+        <v>7.309796412555725e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.309796412555738e-09</v>
+        <v>7.309796412555726e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>8.051035221859725e-09</v>
+        <v>8.05103522185972e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.026954874020152e-08</v>
+        <v>1.026954874020153e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>7.332468638952787e-09</v>
+        <v>7.332468638952788e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.334620502044309e-09</v>
+        <v>8.334620502044314e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.751808921260265e-09</v>
+        <v>7.75180892126028e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.002620545528832e-08</v>
+        <v>1.002620545528834e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.44436041737693e-08</v>
+        <v>3.444360417377012e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.278009700295486e-08</v>
+        <v>3.278009700295488e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.110489408119506e-08</v>
+        <v>5.110489408119515e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.278009883041323e-08</v>
+        <v>3.278009883041327e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.278009883041323e-08</v>
+        <v>3.278009883041328e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.442995482921254e-08</v>
+        <v>4.44299548292126e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.778948716838321e-08</v>
+        <v>8.778948716838319e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.277988265427463e-08</v>
+        <v>3.277988265427466e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.045064813219637e-08</v>
+        <v>5.045064813219684e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.827748985076016e-08</v>
+        <v>3.827748985076053e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.789248084693922e-08</v>
+        <v>8.78924808469393e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.017853075373925e-08</v>
+        <v>1.279816436975353e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.954264605422815e-09</v>
+        <v>9.954264605422823e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.380161014965575e-08</v>
+        <v>1.380161014965572e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.753323584981406e-09</v>
+        <v>9.753323584981425e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.982076762020073e-09</v>
+        <v>9.982076762020086e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.06976776230147e-08</v>
+        <v>1.331731123902896e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.565151234151566e-08</v>
+        <v>1.293504059056507e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>9.97911104010776e-09</v>
+        <v>1.259874465612197e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.362249564633386e-08</v>
+        <v>1.362249564633383e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.039828937533372e-08</v>
+        <v>1.039828937533374e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.269006415640134e-08</v>
+        <v>1.269006415640136e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6259,16 +6259,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.419183291002487e-08</v>
+        <v>1.419183291002488e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.399262754507359e-08</v>
+        <v>1.399262754507357e-08</v>
       </c>
       <c r="D7" t="n">
         <v>1.514684016791554e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.399231759307145e-08</v>
+        <v>1.399231759307143e-08</v>
       </c>
       <c r="F7" t="n">
         <v>1.399231759307145e-08</v>
@@ -6277,19 +6277,19 @@
         <v>1.471097977930032e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.692949329764214e-08</v>
+        <v>1.692949329764212e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.399241319639337e-08</v>
+        <v>1.399241319639336e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.49945650594849e-08</v>
+        <v>1.499456505948489e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.441175347870085e-08</v>
+        <v>1.441175347870082e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.668615001272891e-08</v>
+        <v>1.668615001272892e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.212515587296721e-08</v>
+        <v>3.212515587296726e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.792645844984659e-08</v>
+        <v>4.792645844984658e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.239480378690107e-08</v>
+        <v>5.239480378690104e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.355091319136889e-08</v>
+        <v>4.355091319136892e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.243311493090455e-08</v>
+        <v>3.243311493090453e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.864139682420555e-08</v>
+        <v>4.864139682420561e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.085991034254745e-08</v>
+        <v>5.085991034254743e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.792283024129862e-08</v>
+        <v>4.792283024129863e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.892812599414733e-08</v>
+        <v>4.892812599414726e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.204792220592986e-08</v>
+        <v>3.204792220592992e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.73268694837564e-08</v>
+        <v>6.732686948375643e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.592005831201868e-08</v>
+        <v>2.592005831201867e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.096759248082573e-08</v>
+        <v>3.096759248082571e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.212225134799784e-08</v>
+        <v>3.212225134799791e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.702221654150074e-08</v>
+        <v>3.702221654150081e-08</v>
       </c>
       <c r="F9" t="n">
         <v>3.096759018752211e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.168594471505246e-08</v>
+        <v>3.168594471505245e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.390445823339425e-08</v>
+        <v>3.390445823339427e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.096737813214551e-08</v>
+        <v>3.096737813214549e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.196952999523699e-08</v>
+        <v>3.196952999523708e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.834673748652982e-08</v>
+        <v>2.83467374865298e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.3661114948481e-08</v>
+        <v>3.366111494848105e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.260765916960241e-08</v>
+        <v>1.135845787206817e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.139493485087925e-08</v>
+        <v>1.014372940666106e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.293238189084629e-08</v>
+        <v>1.137554738393595e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.169126513861702e-08</v>
+        <v>1.041355929156328e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.062084954044759e-08</v>
+        <v>9.522416721600686e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.296493511622655e-08</v>
+        <v>1.137726059553181e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.265354482396114e-08</v>
+        <v>1.13483994104706e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.283355610758255e-08</v>
+        <v>1.137050303060023e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.364622755932708e-08</v>
+        <v>1.14500839709719e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.249295459317489e-08</v>
+        <v>1.091496979618842e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.241368429175276e-08</v>
+        <v>1.134556251477666e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.343806605142469e-08</v>
+        <v>1.179122799865934e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.225124862672149e-08</v>
+        <v>9.872192568907555e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.381156444696417e-08</v>
+        <v>1.191525238126516e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.255605045874391e-08</v>
+        <v>1.030181612400799e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.148563486057433e-08</v>
+        <v>8.830927128244747e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.384900739953191e-08</v>
+        <v>1.192690793557599e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3507944503067e-08</v>
+        <v>1.180468423011619e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.369892607938823e-08</v>
+        <v>1.187904675690846e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.462551337012592e-08</v>
+        <v>1.223040545304806e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.339040140601856e-08</v>
+        <v>1.118752520570748e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.32151570600644e-08</v>
+        <v>1.172245637479248e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.447078430433229e-09</v>
+        <v>7.447078430433236e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.503631922430806e-09</v>
+        <v>7.503631922430798e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.640112328543785e-09</v>
+        <v>7.64011232854378e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.523627100810265e-09</v>
+        <v>7.523627100810267e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.523627100810265e-09</v>
+        <v>7.523627100810275e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.650280310653563e-09</v>
+        <v>7.650280310653581e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.475005562829811e-09</v>
+        <v>7.475005562829815e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.537107702547145e-09</v>
+        <v>7.537107702547135e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.03627951113395e-09</v>
+        <v>8.036279511133947e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.712394684918585e-09</v>
+        <v>7.712394684918583e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.332882383696041e-09</v>
+        <v>7.332882383696038e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.1374568666812e-08</v>
+        <v>3.137456866681198e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.46946659661373e-08</v>
+        <v>3.469466596613732e-08</v>
       </c>
       <c r="D5" t="n">
         <v>3.585399810310547e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.469466767899235e-08</v>
+        <v>3.469466767899239e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.469466767899235e-08</v>
+        <v>3.469466767899239e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.589079743183871e-08</v>
+        <v>3.589079743183895e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.619118510425034e-08</v>
+        <v>3.619118510425035e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.46945905002634e-08</v>
+        <v>3.469459050026336e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.270162440302065e-08</v>
+        <v>4.270162440302066e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.58015649763112e-08</v>
+        <v>3.580156497631116e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.305740867469738e-08</v>
+        <v>3.305740867469741e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6615,31 +6615,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.230533097715128e-08</v>
+        <v>1.23053309771513e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.973376993588983e-09</v>
+        <v>9.973376993588975e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.008712909070204e-08</v>
+        <v>1.008710067593223e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.785643692952126e-09</v>
+        <v>9.78564369295213e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.986086164380971e-09</v>
+        <v>9.986086164380956e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.009565824899084e-08</v>
+        <v>1.250853285737162e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>9.920794567977318e-09</v>
+        <v>1.242435696752713e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>9.98248564088441e-09</v>
+        <v>1.239536024926518e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.291204620125395e-08</v>
+        <v>1.062652525260814e-08</v>
       </c>
       <c r="K6" t="n">
         <v>1.016228290644213e-08</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.368398474213951e-08</v>
+        <v>1.368398474213952e-08</v>
       </c>
       <c r="C7" t="n">
         <v>1.377408948012734e-08</v>
@@ -6670,13 +6670,13 @@
         <v>1.377411210347154e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.388718662235984e-08</v>
+        <v>1.388718662235986e-08</v>
       </c>
       <c r="H7" t="n">
         <v>1.371191187453607e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.377401401425339e-08</v>
+        <v>1.37740140142534e-08</v>
       </c>
       <c r="J7" t="n">
         <v>1.42731858228402e-08</v>
@@ -6685,7 +6685,7 @@
         <v>1.394930099662484e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.356978869540231e-08</v>
+        <v>1.356978869540232e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.036951751518556e-08</v>
+        <v>3.036951751518554e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.538315469792606e-08</v>
+        <v>4.5383154697926e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.857637142903947e-08</v>
+        <v>4.857637142903944e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.130217248165966e-08</v>
+        <v>4.130217248165965e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.09328267524987e-08</v>
+        <v>3.093282675249865e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.549276977059831e-08</v>
+        <v>4.549276977059827e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.53174950227744e-08</v>
+        <v>4.531749502277437e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.537959716249182e-08</v>
+        <v>4.53795971624918e-08</v>
       </c>
       <c r="J8" t="n">
         <v>4.588170119072599e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.035768617378059e-08</v>
+        <v>3.035768617378058e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.076061205695962e-08</v>
+        <v>6.076061205695966e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.352972941426666e-08</v>
+        <v>2.352972941426669e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.822225933314519e-08</v>
+        <v>2.822225933314523e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.832519019012982e-08</v>
+        <v>2.832519019012989e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.353335973553257e-08</v>
+        <v>3.353335973553259e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.82222579132273e-08</v>
+        <v>2.822225791322732e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.833535647537768e-08</v>
+        <v>2.833535647537772e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.816008172755392e-08</v>
+        <v>2.816008172755397e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.822218386727124e-08</v>
+        <v>2.822218386727125e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.872135567585807e-08</v>
+        <v>2.87213556758581e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.562261840298623e-08</v>
+        <v>2.573080833841002e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.801795854842015e-08</v>
+        <v>2.801795854842019e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.303070338771555e-08</v>
+        <v>1.140601103956404e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.164697103989865e-08</v>
+        <v>1.019862677261399e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.322838813834859e-08</v>
+        <v>1.141641479535631e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.194835774778809e-08</v>
+        <v>1.047265828763116e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.086344159199364e-08</v>
+        <v>9.569445818204215e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.30238554943515e-08</v>
+        <v>1.140565064853729e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.274976782058062e-08</v>
+        <v>1.137877133052718e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.30646019679524e-08</v>
+        <v>1.140795373780701e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.443561857029285e-08</v>
+        <v>1.155057079244328e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.240819567022472e-08</v>
+        <v>1.094216518613415e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.270388310724131e-08</v>
+        <v>1.138628332200832e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.392755734465627e-08</v>
+        <v>1.196538663539091e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.254041915596941e-08</v>
+        <v>1.000257838521666e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4154935758157e-08</v>
+        <v>1.204055053165113e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.285075641644948e-08</v>
+        <v>1.043918934684005e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.176584026065504e-08</v>
+        <v>8.948376823106329e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.391968084875077e-08</v>
+        <v>1.196442676638058e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.362103675375011e-08</v>
+        <v>1.185471900750636e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.396770217562235e-08</v>
+        <v>1.198068545573216e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.552989644069765e-08</v>
+        <v>1.258517442374979e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.329458739595283e-08</v>
+        <v>1.117996240447345e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.355183707819124e-08</v>
+        <v>1.18474753824067e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.724385407074104e-09</v>
+        <v>7.724385407074077e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.668326911628119e-09</v>
+        <v>7.668326911628103e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.841900614711969e-09</v>
+        <v>7.841900614711968e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.688304316226235e-09</v>
+        <v>7.688304316226241e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.688304316226246e-09</v>
+        <v>7.688304316226241e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.711198961486697e-09</v>
+        <v>7.711198961486664e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.558023457709094e-09</v>
+        <v>7.558023457709077e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.700763686374978e-09</v>
+        <v>7.700763686374959e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.505707411260669e-09</v>
+        <v>8.505707411260634e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.682980233223255e-09</v>
+        <v>7.682980233223237e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.531168009106399e-09</v>
+        <v>7.531168009106367e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.531018252067839e-08</v>
+        <v>3.531018252067835e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.639575081163042e-08</v>
+        <v>3.639575081163179e-08</v>
       </c>
       <c r="D5" t="n">
         <v>3.786113590533187e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.639575251999767e-08</v>
+        <v>3.639575251999826e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.639575251999767e-08</v>
+        <v>3.639575251999826e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.606458112368062e-08</v>
+        <v>3.606458112368002e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.597456970327376e-08</v>
+        <v>3.59745697032737e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.639569869703815e-08</v>
+        <v>3.639569869703766e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.999259612737508e-08</v>
+        <v>4.999259612737501e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.475890686344421e-08</v>
+        <v>3.475890686344416e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.541433206894874e-08</v>
+        <v>3.559537054926831e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.016697964114839e-08</v>
+        <v>1.016697964114836e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.013583607848748e-08</v>
+        <v>1.013583607848738e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.028865356052976e-08</v>
+        <v>1.028865356052974e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.947309958469486e-09</v>
+        <v>9.947309958469502e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.014650690072747e-08</v>
+        <v>1.014650690072745e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.258841293333175e-08</v>
+        <v>1.015379319556095e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.251842978864049e-08</v>
+        <v>1.251842978864046e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.014335792044926e-08</v>
+        <v>1.014335792044924e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.339242174550923e-08</v>
+        <v>1.109484667623021e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.012529850231571e-08</v>
+        <v>1.01252985023157e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>9.972764991518236e-09</v>
+        <v>9.972764991518223e-09</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.400255894351525e-08</v>
+        <v>1.400255894351521e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.397898933741023e-08</v>
+        <v>1.39789893374102e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.411965870120992e-08</v>
+        <v>1.411965870120989e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.397898382818468e-08</v>
+        <v>1.397898382818466e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.397898382818468e-08</v>
+        <v>1.397898382818466e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.398937249792784e-08</v>
+        <v>1.398937249792781e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.383619699415026e-08</v>
+        <v>1.383619699415021e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.397893722281612e-08</v>
+        <v>1.397893722281611e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.478388094770182e-08</v>
+        <v>1.478388094770178e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.396115376966441e-08</v>
+        <v>1.396115376966437e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.380934154554753e-08</v>
+        <v>1.380934154554749e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.069572298179914e-08</v>
+        <v>3.069572298179913e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.563775466149985e-08</v>
+        <v>4.563775466149979e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.887787266784153e-08</v>
+        <v>4.887787266784159e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.154526393138255e-08</v>
+        <v>4.154526393138261e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.114667527663947e-08</v>
+        <v>3.114667527663946e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.564467428332426e-08</v>
+        <v>4.564467428332418e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.549149877954674e-08</v>
+        <v>4.549149877954671e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.563423900821254e-08</v>
+        <v>4.563423900821249e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.644212322411695e-08</v>
+        <v>4.644212322411686e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.037638841751677e-08</v>
+        <v>3.037638841751676e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.109384732352002e-08</v>
+        <v>6.109384732351987e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.31014310268223e-08</v>
+        <v>2.310143102682225e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.748994342615766e-08</v>
+        <v>2.748994342615758e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.763102991931188e-08</v>
+        <v>2.76310299193118e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.258139182257457e-08</v>
+        <v>3.258139182257449e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.748994200401948e-08</v>
+        <v>2.748994200401941e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.750032658667526e-08</v>
+        <v>2.750032658667521e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.734715108289766e-08</v>
+        <v>2.734715108289762e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.748989131156354e-08</v>
+        <v>2.748989131156348e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.829483503644926e-08</v>
+        <v>2.82948350364492e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.481201541364688e-08</v>
+        <v>2.481201541364681e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.732029563429497e-08</v>
+        <v>2.732029563429491e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.529751214578468e-08</v>
+        <v>1.180710717557792e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.188456540627385e-08</v>
+        <v>1.044297831370451e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.006658491067291e-08</v>
+        <v>1.205809400305252e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.218890531750104e-08</v>
+        <v>1.072171097754445e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1096079387941e-08</v>
+        <v>9.811917106758682e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.684772375174111e-08</v>
+        <v>1.188869173343115e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.850998777627049e-08</v>
+        <v>1.249586364856522e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.336406311017389e-08</v>
+        <v>1.170547665568243e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.490682520211062e-08</v>
+        <v>1.181815470584377e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.392247243978424e-08</v>
+        <v>1.12949188703023e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.065983065831605e-08</v>
+        <v>1.262280725967882e-08</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.653303018115163e-08</v>
+        <v>1.297182819417731e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.282180018581687e-08</v>
+        <v>1.018812025604815e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.201845177122014e-08</v>
+        <v>1.475416457124448e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.313435672163433e-08</v>
+        <v>1.063001500830563e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.204153079207429e-08</v>
+        <v>9.12833708074027e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.831609465336826e-08</v>
+        <v>1.355448116988456e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.174766700088854e-08</v>
+        <v>1.793039440396304e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.430799565897e-08</v>
+        <v>1.225152286916734e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.607757027410978e-08</v>
+        <v>1.287124121979866e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.503617585849451e-08</v>
+        <v>1.189392825022368e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.420240052226174e-08</v>
+        <v>1.879440814977104e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.130396830796694e-09</v>
+        <v>9.130396830796677e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.863283674818235e-09</v>
+        <v>7.863283674818212e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.196540850676749e-08</v>
+        <v>1.196540850676747e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>7.888052768884992e-09</v>
+        <v>7.888052768884969e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.88805276888499e-09</v>
+        <v>7.888052768884969e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.004144579847816e-08</v>
+        <v>1.00414457984781e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.698255208776946e-08</v>
+        <v>1.698255208776936e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>7.927633397901898e-09</v>
+        <v>7.927633397901885e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.874052294475708e-09</v>
+        <v>8.874052294475705e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>8.648305078306334e-09</v>
+        <v>8.64830507830631e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.82606076563872e-08</v>
+        <v>1.826060765638719e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.889182487364593e-08</v>
+        <v>5.889182487364587e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.993318303933662e-08</v>
+        <v>3.993318303933647e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.075077570746474e-07</v>
+        <v>1.075077570746473e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>3.993318506655812e-08</v>
+        <v>3.993318506655808e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.993318506655812e-08</v>
+        <v>3.993318506655808e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.651692951705073e-08</v>
+        <v>7.651692951704997e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.093486419801545e-07</v>
+        <v>2.093486419801539e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>3.993264768917963e-08</v>
+        <v>3.993264768917953e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.720787421711368e-08</v>
+        <v>5.720787421711359e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.073277947911024e-08</v>
+        <v>5.073277947911013e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>2.572488626618239e-07</v>
+        <v>5.489826848737425e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.184800848855519e-08</v>
+        <v>1.184800848855517e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.058506153699536e-08</v>
+        <v>1.058506153699538e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.477550077017752e-08</v>
+        <v>1.477550077017754e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.038156234154944e-08</v>
+        <v>1.038156234154937e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.064447721302374e-08</v>
+        <v>1.064447721302372e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.558713614279606e-08</v>
+        <v>1.558713614279601e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.267636127100831e-08</v>
+        <v>2.267636127100825e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.34733237422198e-08</v>
+        <v>1.347332374221971e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.444967249646204e-08</v>
+        <v>1.444967249646203e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.134481602398574e-08</v>
+        <v>1.13448160239857e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.104046120437002e-08</v>
+        <v>2.104046120437001e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.592369188688991e-08</v>
+        <v>1.592369188688987e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.47214638041521e-08</v>
+        <v>1.472146380415208e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.875825806894521e-08</v>
+        <v>1.875825806894517e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.472024427382433e-08</v>
+        <v>1.472024427382428e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.472024427382433e-08</v>
+        <v>1.472024427382428e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.683474085457136e-08</v>
+        <v>1.683474085457133e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.377584714386265e-08</v>
+        <v>2.37758471438626e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.472092845399511e-08</v>
+        <v>1.472092845399509e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.566734735056891e-08</v>
+        <v>1.566734735056887e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.544160013439954e-08</v>
+        <v>1.544160013439951e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.505390271248036e-08</v>
+        <v>2.505390271248032e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.397630366056856e-08</v>
+        <v>3.397630366056848e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.896084286091384e-08</v>
+        <v>4.896084286087425e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.635139795029252e-08</v>
+        <v>5.635139795029243e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.453421831486585e-08</v>
+        <v>4.453421831486578e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.328662835584814e-08</v>
+        <v>3.328662835584806e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.107153880741024e-08</v>
+        <v>5.107153880741016e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.801264509670201e-08</v>
+        <v>5.801264509670187e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.8957726406834e-08</v>
+        <v>4.895772640683393e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.990732596207866e-08</v>
+        <v>4.990732596207855e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.319358234061042e-08</v>
+        <v>3.319358234061028e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>7.619643643130991e-08</v>
+        <v>7.619643643130977e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.830130447620472e-08</v>
+        <v>2.830130447620462e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.257385059205361e-08</v>
+        <v>3.257385059205347e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.661109092367767e-08</v>
+        <v>3.661109092367753e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.889161919191428e-08</v>
+        <v>3.88916191919142e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.257384679009921e-08</v>
+        <v>3.257384679009913e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.468712764247289e-08</v>
+        <v>3.46871276424728e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>4.162823393176419e-08</v>
+        <v>4.162823393176416e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.257331524189661e-08</v>
+        <v>3.257331524189659e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.351973413847043e-08</v>
+        <v>3.351973413847035e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.012188149150887e-08</v>
+        <v>3.012188149150883e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.29062895003819e-08</v>
+        <v>4.290628950038186e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.244429383841014e-08</v>
+        <v>1.149645002364791e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.128813806644362e-08</v>
+        <v>1.026888752570476e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.83559727516447e-08</v>
+        <v>1.180756994331137e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.159183122468247e-08</v>
+        <v>1.054589343385714e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0500259158662e-08</v>
+        <v>9.637141959974935e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.483170171294424e-08</v>
+        <v>1.162209455831067e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.406106133903183e-08</v>
+        <v>1.1568273159138e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.274606849379723e-08</v>
+        <v>1.151246881468818e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.383919747577827e-08</v>
+        <v>1.161713160480077e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.212459359782233e-08</v>
+        <v>1.101575601277017e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>2.284143835556941e-08</v>
+        <v>1.204692716500617e-08</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.325205623693927e-08</v>
+        <v>1.181797741691259e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.213300779113679e-08</v>
+        <v>9.900775644087486e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>2.005171158775666e-08</v>
+        <v>1.402475709687073e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.244531332196223e-08</v>
+        <v>1.034100384841757e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.135374125594176e-08</v>
+        <v>8.841047421186947e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.599806984270483e-08</v>
+        <v>1.27122650413921e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.512885045379708e-08</v>
+        <v>1.241794213067491e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.359901806160408e-08</v>
+        <v>1.19341340064103e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.484737830621497e-08</v>
+        <v>1.240354300423151e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.297369308881504e-08</v>
+        <v>1.110422312982558e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.521072148248027e-08</v>
+        <v>1.574699651280769e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.369810592411833e-09</v>
+        <v>7.369810592411831e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.451596972472051e-09</v>
+        <v>7.451596972472007e-09</v>
       </c>
       <c r="D4" t="n">
         <v>1.088405320724498e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>7.473086937348702e-09</v>
+        <v>7.473086937348723e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.473086937348703e-09</v>
+        <v>7.47308693734872e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>8.779119697624422e-09</v>
+        <v>8.779119697624406e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>8.331675467515327e-09</v>
+        <v>8.331675467515296e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.499863847780014e-09</v>
+        <v>7.499863847779996e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.162983659171164e-09</v>
+        <v>8.162983659171162e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.533405667416566e-09</v>
+        <v>7.533405667416587e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.354969061458195e-08</v>
+        <v>1.354969061458194e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.883267152183291e-08</v>
+        <v>2.883267152183293e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.293052883618646e-08</v>
+        <v>3.293052883618645e-08</v>
       </c>
       <c r="D5" t="n">
         <v>8.388884848236326e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.29305306901078e-08</v>
+        <v>3.293053069010782e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.29305306901078e-08</v>
+        <v>3.293053069010782e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.265751153437074e-08</v>
+        <v>5.265751153437108e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.871637934686458e-08</v>
+        <v>4.871637934686466e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.293018577663621e-08</v>
+        <v>3.293018577663619e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.343285864988345e-08</v>
+        <v>4.34328586498834e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.186018846599804e-08</v>
+        <v>3.186018846599808e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.13884282258948e-08</v>
+        <v>1.489593776416438e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7803,34 +7803,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.236915872177618e-08</v>
+        <v>1.236915872177619e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.93079310663205e-09</v>
+        <v>9.930793106632016e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.343366437002071e-08</v>
+        <v>1.343363622794431e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.742650738159674e-09</v>
+        <v>9.742650738159649e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.966976196776783e-09</v>
+        <v>9.966976196776773e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.124446755091525e-08</v>
+        <v>1.377846782698876e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.342984793994292e-08</v>
+        <v>1.34298479399429e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.249921197714433e-08</v>
+        <v>1.249921197714435e-08</v>
       </c>
       <c r="J6" t="n">
         <v>1.077713434851152e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.976350400983295e-09</v>
+        <v>9.976350400983305e-09</v>
       </c>
       <c r="L6" t="n">
         <v>1.604984795049287e-08</v>
@@ -7843,13 +7843,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.367660725434792e-08</v>
+        <v>1.367660725434791e-08</v>
       </c>
       <c r="C7" t="n">
         <v>1.380700356926634e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.719043469385737e-08</v>
+        <v>1.719043469385734e-08</v>
       </c>
       <c r="E7" t="n">
         <v>1.38064057096502e-08</v>
@@ -7858,22 +7858,22 @@
         <v>1.38064057096502e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.508591635956048e-08</v>
+        <v>1.508591635956049e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.463847212945141e-08</v>
+        <v>1.463847212945137e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.380666050971607e-08</v>
+        <v>1.380666050971608e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.446978032110727e-08</v>
+        <v>1.446978032110723e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.384020232935271e-08</v>
+        <v>1.384020232935268e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.985648727651801e-08</v>
+        <v>1.9856487276518e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.043633254691142e-08</v>
+        <v>3.043633254691139e-08</v>
       </c>
       <c r="C8" t="n">
         <v>4.559623204909936e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.209303122848977e-08</v>
+        <v>5.209303122848969e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.148617221129761e-08</v>
+        <v>4.148617221129756e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.104294045329391e-08</v>
+        <v>3.104294045329394e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.687223557884272e-08</v>
+        <v>4.687223557884273e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.642479134873341e-08</v>
+        <v>4.642479134873333e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.559297972899836e-08</v>
+        <v>4.55929797289983e-08</v>
       </c>
       <c r="J8" t="n">
         <v>4.625905269887632e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.032080092485897e-08</v>
+        <v>3.032080092485893e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.73393403576969e-08</v>
+        <v>6.733934035769681e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.381614297635793e-08</v>
+        <v>2.381614297635791e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.865606871309673e-08</v>
+        <v>2.865606871309675e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.203991701716083e-08</v>
+        <v>3.203991701716081e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.409076521022655e-08</v>
+        <v>3.409076521022657e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.865606715651599e-08</v>
+        <v>2.8656067156516e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.993498150339087e-08</v>
+        <v>2.993498150339092e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.94875372732818e-08</v>
+        <v>2.948753727328178e-08</v>
       </c>
       <c r="I9" t="n">
         <v>2.865572565354649e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.931884546493767e-08</v>
+        <v>2.931884546493765e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.275912876365068e-08</v>
+        <v>2.596054847336879e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.470555242034843e-08</v>
+        <v>3.470555242034842e-08</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia human toxicity non-carcinogenic results.xlsx
+++ b/Results/Ammonia/ammonia human toxicity non-carcinogenic results.xlsx
@@ -515,25 +515,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.211700851599092e-08</v>
+        <v>1.211700851599095e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.068127304282624e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.221518672489976e-08</v>
+        <v>1.221518672489977e-08</v>
       </c>
       <c r="E2" t="n">
         <v>1.096390792530906e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.004411504023728e-08</v>
+        <v>1.004411504023729e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.206325756570395e-08</v>
+        <v>1.206325756570396e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.271346906539649e-08</v>
+        <v>1.27134690653965e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.190915232275633e-08</v>
@@ -545,7 +545,7 @@
         <v>1.152565231837805e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.293787608985553e-08</v>
+        <v>1.293787608985554e-08</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.43699221163891e-08</v>
+        <v>1.436992211638912e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.088771439821071e-08</v>
+        <v>1.088771439821072e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.507197933642356e-08</v>
+        <v>1.507197933642357e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.133571146238204e-08</v>
+        <v>1.133571146238203e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>9.817528108567532e-09</v>
+        <v>9.817528108567542e-09</v>
       </c>
       <c r="G3" t="n">
         <v>1.399323819903632e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.870277498467597e-08</v>
+        <v>1.870277498467599e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.289363584854191e-08</v>
+        <v>1.289363584854193e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.354830587631659e-08</v>
+        <v>1.35483058763166e-08</v>
       </c>
       <c r="K3" t="n">
         <v>1.249644017695275e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.023164017345976e-08</v>
+        <v>2.023164017345978e-08</v>
       </c>
     </row>
     <row r="4">
@@ -598,34 +598,34 @@
         <v>1.135574895314947e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.891357279195077e-09</v>
+        <v>8.891357279195079e-09</v>
       </c>
       <c r="D4" t="n">
         <v>1.246471698698213e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.917438337779826e-09</v>
+        <v>8.917438337779834e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>8.917438337779827e-09</v>
+        <v>8.917438337779832e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.073829498242941e-08</v>
+        <v>1.073829498242937e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.816324049938142e-08</v>
+        <v>1.816324049938143e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.954302206969325e-09</v>
+        <v>8.954302206969333e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>9.837482672416977e-09</v>
+        <v>9.837482672416983e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>9.495750247167161e-09</v>
+        <v>9.495750247167168e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>2.052376817490748e-08</v>
+        <v>2.052376817490749e-08</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.011846701932934e-07</v>
+        <v>1.011846701932935e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>5.812684346704343e-08</v>
+        <v>5.812684346704361e-08</v>
       </c>
       <c r="D5" t="n">
         <v>1.243219172384115e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>5.812684546109972e-08</v>
+        <v>5.812684546109984e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.812684546109972e-08</v>
+        <v>5.812684546109984e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.307219745413392e-08</v>
+        <v>9.307219745413318e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.607070550845636e-07</v>
+        <v>2.607070550845639e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>5.812638248076569e-08</v>
+        <v>5.812638248076587e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.690865386877574e-08</v>
+        <v>7.690865386877582e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>6.734654774440225e-08</v>
+        <v>6.73465477444024e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.212807557633484e-07</v>
+        <v>3.212807557633493e-07</v>
       </c>
     </row>
     <row r="6">
@@ -678,31 +678,31 @@
         <v>1.432268321747219e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.186838701431022e-08</v>
+        <v>1.186838701431027e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.552038621930293e-08</v>
+        <v>1.552038621930295e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.164774964843581e-08</v>
+        <v>1.164774964843579e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.192435251330762e-08</v>
+        <v>1.192435251330764e-08</v>
       </c>
       <c r="G6" t="n">
         <v>1.679870266963217e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.437211867782724e-08</v>
+        <v>2.437211867782726e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.501470989417215e-08</v>
+        <v>1.501470989417214e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.591825276529849e-08</v>
+        <v>1.59182527652985e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.244417136526833e-08</v>
+        <v>1.244417136526839e-08</v>
       </c>
       <c r="L6" t="n">
         <v>2.356834409765356e-08</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.866831601603701e-08</v>
+        <v>1.866831601603705e-08</v>
       </c>
       <c r="C7" t="n">
         <v>1.626733025613462e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.977680442403906e-08</v>
+        <v>1.977680442403905e-08</v>
       </c>
       <c r="E7" t="n">
         <v>1.626614405910078e-08</v>
@@ -730,22 +730,22 @@
         <v>1.626614405910078e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.805086204531691e-08</v>
+        <v>1.805086204531692e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.547580756226896e-08</v>
+        <v>2.547580756226898e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.626686926985687e-08</v>
+        <v>1.626686926985688e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.715004973530451e-08</v>
+        <v>1.715004973530455e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.68083173100547e-08</v>
+        <v>1.680831731005471e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.7836335237795e-08</v>
+        <v>2.783633523779501e-08</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.800958927208116e-08</v>
+        <v>3.800958927208122e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.297695549413409e-08</v>
+        <v>5.297695549413418e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>6.00848625998667e-08</v>
+        <v>6.008486259986675e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.822722021622219e-08</v>
+        <v>4.822722021622226e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.615864118509559e-08</v>
+        <v>3.615864118509562e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.475759864529095e-08</v>
+        <v>5.475759864529112e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.218254416224324e-08</v>
+        <v>6.218254416224335e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>5.297360586983094e-08</v>
+        <v>5.297360586983105e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.38601991489296e-08</v>
+        <v>5.386019914892964e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.582701816881114e-08</v>
+        <v>3.582701816881116e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.268275037931049e-08</v>
+        <v>8.268275037931066e-08</v>
       </c>
     </row>
     <row r="9">
@@ -795,31 +795,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3760124700467e-08</v>
+        <v>3.376012470046702e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.774230709017776e-08</v>
+        <v>3.77423070901778e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.12522614281112e-08</v>
+        <v>4.125226142811121e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.510834221115068e-08</v>
+        <v>4.510834221115073e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.774230263251068e-08</v>
+        <v>3.774230263251071e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.952583887936007e-08</v>
+        <v>3.952583887936009e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>4.69507843963121e-08</v>
+        <v>4.695078439631216e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.774184610390004e-08</v>
+        <v>3.774184610390006e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.862502656934768e-08</v>
+        <v>3.862502656934771e-08</v>
       </c>
       <c r="K9" t="n">
         <v>3.024574591120608e-08</v>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.137237024324789e-08</v>
+        <v>1.137237024324788e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0201404845065e-08</v>
+        <v>1.020140484506501e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.141910959780492e-08</v>
+        <v>1.14191095978049e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.047692713975779e-08</v>
+        <v>1.047692713975778e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>9.569171440251639e-09</v>
+        <v>9.569171440251631e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.140962561136174e-08</v>
+        <v>1.140962561136175e-08</v>
       </c>
       <c r="H2" t="n">
         <v>1.140219744445023e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.140726091206411e-08</v>
+        <v>1.140726091206409e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.153527979021602e-08</v>
+        <v>1.153527979021601e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.090378009423716e-08</v>
+        <v>1.090378009423715e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.139913830661458e-08</v>
+        <v>1.139913830661453e-08</v>
       </c>
     </row>
     <row r="3">
@@ -954,34 +954,34 @@
         <v>1.171288697854742e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.989917981746864e-09</v>
+        <v>9.989917981746863e-09</v>
       </c>
       <c r="D3" t="n">
         <v>1.204599922953689e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.042891398803023e-08</v>
+        <v>1.042891398803022e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.930602062919448e-09</v>
+        <v>8.93060206291943e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.197892574055505e-08</v>
+        <v>1.197892574055503e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.200653720902961e-08</v>
+        <v>1.200653720902962e-08</v>
       </c>
       <c r="I3" t="n">
         <v>1.196222015702203e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.241675600508983e-08</v>
+        <v>1.241675600508981e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.096107909026933e-08</v>
+        <v>1.096107909026938e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.192501208565391e-08</v>
+        <v>1.192501208565388e-08</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.317988241935758e-09</v>
+        <v>7.31798824193572e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.634006777370909e-09</v>
+        <v>7.634006777370902e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.845930752822851e-09</v>
+        <v>7.845930752822826e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.654115403540896e-09</v>
+        <v>7.654115403540863e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.654115403540875e-09</v>
+        <v>7.654115403540863e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.72966785661263e-09</v>
+        <v>7.729667856612594e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.793990786973132e-09</v>
+        <v>7.793990786973099e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.666382279393108e-09</v>
+        <v>7.666382279393076e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.211843476299316e-09</v>
+        <v>8.211843476299281e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.361300291581975e-09</v>
+        <v>7.361300291581944e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.648528045033171e-09</v>
+        <v>7.648528045033142e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.875278514361895e-08</v>
+        <v>2.875278514361894e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.584169516728791e-08</v>
+        <v>3.584169516728792e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.784734867016858e-08</v>
+        <v>3.78473486701686e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.584169685970087e-08</v>
+        <v>3.584169685970081e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.584169685970087e-08</v>
+        <v>3.584169685970081e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.626180289992133e-08</v>
+        <v>3.626180289992128e-08</v>
       </c>
       <c r="H5" t="n">
         <v>3.986712018414846e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.584163100269199e-08</v>
+        <v>3.584163100269203e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.497599616405391e-08</v>
+        <v>4.497599616405374e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.985497890354373e-08</v>
+        <v>2.985497890354371e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.758812100535924e-08</v>
+        <v>3.758812100535916e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.750355854485562e-09</v>
+        <v>9.750355854485547e-09</v>
       </c>
       <c r="C6" t="n">
         <v>1.009459004965347e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.27529537132744e-08</v>
+        <v>1.275295371327439e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.906437904977407e-09</v>
+        <v>9.906437904977447e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.010520082809907e-08</v>
+        <v>1.010520082809906e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.258965524094342e-08</v>
+        <v>1.258965524094338e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.275405190572825e-08</v>
+        <v>1.275405190572822e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.009874989194291e-08</v>
+        <v>1.00987498919429e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.079252105383767e-08</v>
+        <v>1.079252105383764e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.787461787564367e-09</v>
+        <v>9.787461787564354e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.008409105976049e-08</v>
+        <v>1.008409105976047e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1120,28 +1120,28 @@
         <v>1.413538499925056e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.395654332014191e-08</v>
+        <v>1.395654332014189e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.395654332014191e-08</v>
+        <v>1.395654332014189e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.401953784344951e-08</v>
+        <v>1.401953784344952e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.408386077381004e-08</v>
+        <v>1.408386077381003e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.395625226623001e-08</v>
+        <v>1.395625226622998e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.450171346313623e-08</v>
+        <v>1.450171346313621e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.365117027841889e-08</v>
+        <v>1.365117027841888e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.393839803187008e-08</v>
+        <v>1.393839803187006e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.031223829069061e-08</v>
+        <v>3.031223829069059e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.564314753448256e-08</v>
+        <v>4.564314753448253e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.892488620362052e-08</v>
+        <v>4.892488620362053e-08</v>
       </c>
       <c r="E8" t="n">
         <v>4.15460862501072e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.11358841481754e-08</v>
+        <v>3.113588414817534e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.57026795108005e-08</v>
+        <v>4.570267951080046e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.576700244116092e-08</v>
+        <v>4.576700244116095e-08</v>
       </c>
       <c r="I8" t="n">
         <v>4.563939393358091e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.618779888857832e-08</v>
+        <v>4.61877988885783e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.00773121532017e-08</v>
+        <v>3.007731215320172e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.126810870188444e-08</v>
+        <v>6.126810870188449e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.270612976381964e-08</v>
+        <v>2.27061297638196e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.747063767244802e-08</v>
+        <v>2.7470637672448e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.765012362008195e-08</v>
+        <v>2.765012362008194e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.256666457459291e-08</v>
+        <v>3.256666457459292e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.747063616668634e-08</v>
+        <v>2.747063616668636e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.753385908507156e-08</v>
+        <v>2.753385908507157e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.75981820154321e-08</v>
+        <v>2.759818201543212e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.747057350785206e-08</v>
+        <v>2.747057350785205e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.801603470475828e-08</v>
+        <v>2.80160347047583e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.46068156661591e-08</v>
+        <v>2.460681566615907e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.745271927349214e-08</v>
+        <v>2.745271927349212e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.14411254460204e-08</v>
+        <v>1.144112544602045e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.618101363349035e-09</v>
+        <v>9.61810136334903e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.164490068207789e-08</v>
+        <v>1.164490068207794e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.895060848620012e-09</v>
+        <v>9.895060848620025e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>9.894900849913613e-09</v>
+        <v>9.894900849913666e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.154138675736878e-08</v>
+        <v>1.154138675736874e-08</v>
       </c>
       <c r="H2" t="n">
         <v>1.184021486484975e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.146847050842569e-08</v>
+        <v>1.146847050842571e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.075665132028185e-08</v>
+        <v>1.075665132028193e-08</v>
       </c>
       <c r="K2" t="n">
         <v>1.168957350526862e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.160884872511174e-08</v>
+        <v>1.160884872511176e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1347,34 +1347,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.190569533755057e-08</v>
+        <v>1.190569533755063e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.362581078876121e-09</v>
+        <v>9.362581078876111e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.337716851362518e-08</v>
+        <v>1.337716851362524e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.52636112498321e-09</v>
+        <v>9.526361124983218e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.526201126276926e-09</v>
+        <v>9.52620112627684e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.264202017843149e-08</v>
+        <v>1.26420201784315e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.485155183509219e-08</v>
+        <v>1.485155183509223e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.212119389064028e-08</v>
+        <v>1.212119389064031e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.159817132730745e-08</v>
+        <v>1.159817132730742e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.24731782908085e-08</v>
+        <v>1.247317829080848e-08</v>
       </c>
       <c r="L3" t="n">
         <v>1.314800077090501e-08</v>
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.920892713623245e-09</v>
+        <v>7.920892713623234e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>8.646404202595253e-09</v>
+        <v>8.646404202595261e-09</v>
       </c>
       <c r="D4" t="n">
         <v>1.022262774613231e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.149532026353772e-09</v>
+        <v>8.149532026353776e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>8.149532026353774e-09</v>
+        <v>8.149532026353769e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>9.043500455939016e-09</v>
+        <v>9.043500455939011e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.253609971565137e-08</v>
+        <v>1.253609971565139e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.179123849633323e-09</v>
+        <v>8.17912384963332e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>9.566295937887505e-09</v>
+        <v>9.566295937887499e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>8.203653427931001e-09</v>
+        <v>8.203653427930981e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>9.83583274484038e-09</v>
+        <v>9.835832744840353e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1430,34 +1430,34 @@
         <v>2.778837585772971e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.564026437120591e-08</v>
+        <v>5.5640264371206e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.000668589744528e-08</v>
+        <v>8.000668589744518e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.461445150257754e-08</v>
+        <v>4.461445150257779e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.461445150257754e-08</v>
+        <v>4.461445150257785e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>6.021799741652434e-08</v>
+        <v>6.021799741652357e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.351760071912261e-07</v>
+        <v>1.351760071912268e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>4.461419913380372e-08</v>
+        <v>4.461419913380434e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.107623308949389e-08</v>
+        <v>7.107623308949384e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.401318102357776e-08</v>
+        <v>4.401318102357783e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.212738449863246e-08</v>
+        <v>8.212738449863253e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1467,31 +1467,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.325718809566639e-08</v>
+        <v>1.325718809566641e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.141246773678419e-08</v>
+        <v>1.141246773678417e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.293194097698947e-08</v>
+        <v>1.293194097698948e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.060729363852637e-08</v>
+        <v>1.060729363852641e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.084064138715792e-08</v>
+        <v>1.084064138715793e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.170112400347674e-08</v>
+        <v>1.170112400347677e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.815667859886981e-08</v>
+        <v>1.815667859886985e-08</v>
       </c>
       <c r="I6" t="n">
         <v>1.083674739717108e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.49748332441795e-08</v>
+        <v>1.497483324417951e-08</v>
       </c>
       <c r="K6" t="n">
         <v>1.08468341883436e-08</v>
@@ -1507,31 +1507,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.462332725187939e-08</v>
+        <v>1.46233272518794e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.547179418826776e-08</v>
+        <v>1.547179418826777e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.692464633712482e-08</v>
+        <v>1.692464633712483e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.488208170477259e-08</v>
+        <v>1.488208170477263e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.488208170477259e-08</v>
+        <v>1.488208170477264e-08</v>
       </c>
       <c r="G7" t="n">
         <v>1.574593499419518e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.923853425390749e-08</v>
+        <v>1.923853425390755e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.488155838788945e-08</v>
+        <v>1.488155838788948e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.626873047614362e-08</v>
+        <v>1.626873047614364e-08</v>
       </c>
       <c r="K7" t="n">
         <v>1.490608796618713e-08</v>
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.243671781223939e-08</v>
+        <v>3.243671781223934e-08</v>
       </c>
       <c r="C8" t="n">
         <v>4.927460910603972e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.403864284544142e-08</v>
+        <v>5.403864284544144e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.431220572694952e-08</v>
+        <v>4.431220572694944e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.32023265502948e-08</v>
+        <v>3.320232655029485e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.954481929264956e-08</v>
+        <v>4.954481929264954e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.303741855237075e-08</v>
+        <v>5.303741855237084e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.868044268634385e-08</v>
+        <v>4.868044268634374e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.007075638446516e-08</v>
+        <v>5.007075638446524e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.242253977317147e-08</v>
+        <v>3.242253977317142e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.70353364784692e-08</v>
+        <v>6.703533647846907e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.650383633078761e-08</v>
+        <v>2.65038363307876e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.266927643090008e-08</v>
+        <v>3.266927643090015e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.412254588456869e-08</v>
+        <v>3.412254588456875e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.821496298434871e-08</v>
+        <v>3.821496298434874e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.207928857126512e-08</v>
+        <v>3.207928857126518e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.294341723682744e-08</v>
+        <v>3.294341723682754e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.643601649653979e-08</v>
+        <v>3.643601649653986e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.207904063052185e-08</v>
+        <v>3.207904063052181e-08</v>
       </c>
       <c r="J9" t="n">
         <v>3.346621271877598e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.902289564737241e-08</v>
+        <v>2.902289564737246e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.373574952572885e-08</v>
+        <v>3.373574952572884e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1703,25 +1703,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.137522410943063e-08</v>
+        <v>1.137522410943067e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.513510024902735e-09</v>
+        <v>9.51351002490275e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.154498037875497e-08</v>
+        <v>1.154498037875501e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.810047971757798e-09</v>
+        <v>9.810047971757852e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>9.809887253997148e-09</v>
+        <v>9.809887253997168e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.14540868466913e-08</v>
+        <v>1.145408684669135e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.16050032052461e-08</v>
+        <v>1.160500320524608e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.140703237295663e-08</v>
@@ -1730,10 +1730,10 @@
         <v>1.063931102476035e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.156938223289262e-08</v>
+        <v>1.156938223289257e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.142467016786025e-08</v>
+        <v>1.142467016786024e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.16568851501635e-08</v>
+        <v>1.165688515016352e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.032575289851714e-09</v>
+        <v>9.032575289851697e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.288648503111457e-08</v>
+        <v>1.28864850311146e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.270714647831515e-09</v>
+        <v>9.270714647831539e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.270553930070862e-09</v>
+        <v>9.270553930070918e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.224060517560847e-08</v>
+        <v>1.224060517560848e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.339606607677521e-08</v>
+        <v>1.33960660767752e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.190446573308908e-08</v>
+        <v>1.190446573308906e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.103279796124258e-08</v>
+        <v>1.103279796124259e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.205422216856175e-08</v>
+        <v>1.205422216856169e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.205597203610072e-08</v>
+        <v>1.205597203610069e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.458354043608201e-09</v>
+        <v>7.458354043608184e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>8.153765766935446e-09</v>
+        <v>8.153765766935435e-09</v>
       </c>
       <c r="D4" t="n">
         <v>9.375829197368622e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.757797149230328e-09</v>
+        <v>7.757797149230338e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.75779714923033e-09</v>
+        <v>7.75779714923034e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>8.339471479183496e-09</v>
+        <v>8.339471479183509e-09</v>
       </c>
       <c r="H4" t="n">
         <v>1.017644966436015e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>7.76844601568482e-09</v>
+        <v>7.768446015684819e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.627695900883758e-09</v>
+        <v>8.62769590088377e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.574170080646098e-09</v>
+        <v>7.574170080646113e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>8.050506566736171e-09</v>
+        <v>8.050506566736151e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.938691718372095e-08</v>
+        <v>1.938691718372096e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.523102902145646e-08</v>
+        <v>4.523102902145642e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.264988144388474e-08</v>
+        <v>6.264988144388484e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.634899494190972e-08</v>
+        <v>3.634899494190979e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.634899494190972e-08</v>
+        <v>3.634899494190979e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.594911864736927e-08</v>
+        <v>4.594911864736918e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.435815461578134e-08</v>
+        <v>8.435815461578101e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.634881043096818e-08</v>
+        <v>3.634881043096814e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.183545964876663e-08</v>
+        <v>5.183545964876661e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.210555191598414e-08</v>
+        <v>3.210555191598412e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.432505374619557e-08</v>
+        <v>4.432505374619564e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.242806826944991e-08</v>
+        <v>1.242806826944988e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.071827901540453e-08</v>
+        <v>1.071827901540461e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.444486823696735e-08</v>
+        <v>1.444486823696732e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.001750349237655e-08</v>
+        <v>1.001750349237658e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.023047801698708e-08</v>
+        <v>1.023047801698707e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.330918570502518e-08</v>
+        <v>1.330918570502519e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.544486970780216e-08</v>
+        <v>1.544486970780213e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.022493543537657e-08</v>
+        <v>1.022493543537654e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.12378867950385e-08</v>
+        <v>1.123788679503851e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.001596953752388e-08</v>
+        <v>1.001596953752392e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.051109773287138e-08</v>
+        <v>1.05110977328714e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.385206157206759e-08</v>
+        <v>1.385206157206756e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.466604710342297e-08</v>
+        <v>1.466604710342296e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.576914361273276e-08</v>
+        <v>1.576914361273273e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.416692603118487e-08</v>
+        <v>1.41669260311849e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.416692603118486e-08</v>
+        <v>1.41669260311849e-08</v>
       </c>
       <c r="G7" t="n">
         <v>1.47331790076429e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.657015719281954e-08</v>
+        <v>1.657015719281952e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.416215354414421e-08</v>
+        <v>1.41621535441442e-08</v>
       </c>
       <c r="J7" t="n">
         <v>1.502140342934315e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.396787760910548e-08</v>
+        <v>1.396787760910549e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.444421409519555e-08</v>
+        <v>1.444421409519558e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.073136783051432e-08</v>
+        <v>3.073136783051438e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.674532605649515e-08</v>
+        <v>4.674532605649504e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.099112515865051e-08</v>
+        <v>5.09911251586505e-08</v>
       </c>
       <c r="E8" t="n">
         <v>4.208577279288773e-08</v>
@@ -1958,22 +1958,22 @@
         <v>3.152618191893419e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.680458631952484e-08</v>
+        <v>4.680458631952494e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.864156450472448e-08</v>
+        <v>4.864156450472438e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.623356085602612e-08</v>
+        <v>4.623356085602606e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.709579642650796e-08</v>
+        <v>4.709579642650781e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.056498279063344e-08</v>
+        <v>3.056498279063343e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.238504130230647e-08</v>
+        <v>6.238504130230652e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.384956816108303e-08</v>
+        <v>2.384956816108298e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.937277152812129e-08</v>
+        <v>2.937277152812132e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.047626270550665e-08</v>
+        <v>3.047626270550663e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.430339684529946e-08</v>
+        <v>3.43033968452994e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.886905882299567e-08</v>
+        <v>2.886905882299565e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.943990343234124e-08</v>
+        <v>2.943990343234123e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.12768816175179e-08</v>
+        <v>3.127688161751784e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.886887796884257e-08</v>
+        <v>2.886887796884247e-08</v>
       </c>
       <c r="J9" t="n">
         <v>2.972812785404147e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.59460633793025e-08</v>
+        <v>2.594606337930251e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.915093851989398e-08</v>
+        <v>2.915093851989396e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.13103812759312e-08</v>
+        <v>1.131038127593121e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.414379867638153e-09</v>
+        <v>9.414379867638158e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.144485924250771e-08</v>
+        <v>1.144485924250773e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.717540546056858e-09</v>
+        <v>9.717540546056889e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>9.717379516723286e-09</v>
+        <v>9.717379516723283e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.13697207517952e-08</v>
+        <v>1.136972075179526e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.144763895369982e-08</v>
+        <v>1.144763895369983e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.133142251618054e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.051805498237355e-08</v>
+        <v>1.05180549823735e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.148387838334105e-08</v>
+        <v>1.148387838334109e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.133591879467545e-08</v>
+        <v>1.133591879467546e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.148942415965498e-08</v>
+        <v>1.148942415965501e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.720774750989913e-09</v>
+        <v>8.720774750989916e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.24679980835913e-08</v>
+        <v>1.246799808359133e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>8.998791980586509e-09</v>
+        <v>8.998791980586451e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>8.998630951252956e-09</v>
+        <v>8.998630951252872e-09</v>
       </c>
       <c r="G3" t="n">
         <v>1.193390403549332e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.256836468663458e-08</v>
+        <v>1.25683646866346e-08</v>
       </c>
       <c r="I3" t="n">
         <v>1.166043692686137e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.04714872567372e-08</v>
+        <v>1.047148725673731e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.184511587071087e-08</v>
+        <v>1.184511587071094e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.171553770001432e-08</v>
+        <v>1.171553770001435e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.217266339068231e-09</v>
+        <v>7.217266339068246e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.727820107064153e-09</v>
+        <v>7.727820107064174e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>8.736256834471235e-09</v>
+        <v>8.736256834471255e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.399494221494559e-09</v>
+        <v>7.399494221494572e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.39949422149457e-09</v>
+        <v>7.399494221494573e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.877926441009796e-09</v>
+        <v>7.877926441009769e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>8.897152399142858e-09</v>
+        <v>8.897152399142891e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.406199643395646e-09</v>
+        <v>7.406199643395668e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.768178071098499e-09</v>
+        <v>7.768178071098519e-09</v>
       </c>
       <c r="K4" t="n">
         <v>7.31711241112658e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.538449774691046e-09</v>
+        <v>7.538449774691066e-09</v>
       </c>
     </row>
     <row r="5">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.53178970649674e-08</v>
+        <v>1.531789706496745e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.803061989427201e-08</v>
+        <v>3.803061989427203e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.192532374773178e-08</v>
+        <v>5.192532374773169e-08</v>
       </c>
       <c r="E5" t="n">
         <v>3.027291879893356e-08</v>
@@ -2234,22 +2234,22 @@
         <v>3.027291879893356e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.803079305991902e-08</v>
+        <v>3.803079305991893e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>6.004090917305202e-08</v>
+        <v>6.004090917305217e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.027275730387056e-08</v>
+        <v>3.027275730387053e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.664761561779239e-08</v>
+        <v>3.664761561779242e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.786618047038323e-08</v>
+        <v>2.786618047038328e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.450899622318289e-08</v>
+        <v>3.450899622318292e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.633869828261926e-09</v>
+        <v>9.633869828261944e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.025510895627183e-08</v>
+        <v>1.025510895627182e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.118647103241513e-08</v>
+        <v>1.118647103241504e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.617958873024928e-09</v>
+        <v>9.617958873024968e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.828173739160449e-09</v>
+        <v>9.828173739160468e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.279831785087866e-08</v>
+        <v>1.279831785087868e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.414976338612216e-08</v>
+        <v>1.414976338612219e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.232659105326453e-08</v>
+        <v>1.232659105326456e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.276594720838151e-08</v>
+        <v>1.276594720838154e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.722999578232852e-09</v>
+        <v>9.722999578232777e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>9.957492859979196e-09</v>
+        <v>9.957492859979233e-09</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.362911129469987e-08</v>
+        <v>1.36291112946999e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.426293936442795e-08</v>
+        <v>1.426293936442797e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.514770953853838e-08</v>
+        <v>1.514770953853839e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.382410357117983e-08</v>
+        <v>1.382410357117985e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.382410357117983e-08</v>
+        <v>1.382410357117985e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.428977139664142e-08</v>
+        <v>1.428977139664143e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.530899735477453e-08</v>
+        <v>1.530899735477455e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.381804459902729e-08</v>
+        <v>1.38180445990273e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.418002302673016e-08</v>
+        <v>1.418002302673017e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.372895736675821e-08</v>
+        <v>1.372895736675823e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.395029473032269e-08</v>
+        <v>1.395029473032272e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.051818883860875e-08</v>
+        <v>3.051818883860877e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.637977957222019e-08</v>
+        <v>4.637977957222023e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.041149594296807e-08</v>
+        <v>5.041149594296808e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.177181162681217e-08</v>
+        <v>4.17718116268123e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.119344295616119e-08</v>
+        <v>3.119344295616122e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.639748269929203e-08</v>
+        <v>4.63974826992921e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.741670865746184e-08</v>
+        <v>4.741670865746191e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.592575590167796e-08</v>
+        <v>4.592575590167795e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.629072522903592e-08</v>
+        <v>4.629072522903594e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.033534097511449e-08</v>
+        <v>3.033534097511448e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.195514155752048e-08</v>
+        <v>6.195514155752051e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.268926946600637e-08</v>
+        <v>2.268926946600641e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.778193295232727e-08</v>
+        <v>2.778193295232733e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.866709704427005e-08</v>
+        <v>2.866709704427012e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.248259848584908e-08</v>
+        <v>3.248259848584912e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.733719629752735e-08</v>
+        <v>2.733719629752738e-08</v>
       </c>
       <c r="G9" t="n">
         <v>2.780876498454078e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.882799094267389e-08</v>
+        <v>2.882799094267393e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.733703818692661e-08</v>
+        <v>2.733703818692668e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.76990166146295e-08</v>
+        <v>2.769901661462955e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.455967035522406e-08</v>
+        <v>2.455967035522407e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.746928831822202e-08</v>
+        <v>2.746928831822211e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.133502660118107e-08</v>
+        <v>1.13350266011837e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.329721152553283e-09</v>
+        <v>9.329721152552709e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.149001338962251e-08</v>
+        <v>1.149001338962262e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.724509374804921e-09</v>
+        <v>9.724509374802767e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>9.724348569224525e-09</v>
+        <v>9.72434856922347e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.143659561279741e-08</v>
+        <v>1.143659561279692e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.16947912579115e-08</v>
+        <v>1.169479125790958e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.13660807128407e-08</v>
+        <v>1.136608071284083e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.064316591461391e-08</v>
+        <v>1.064316591461506e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.15529660258662e-08</v>
+        <v>1.155296602586951e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.155563429659133e-08</v>
+        <v>1.155563429659213e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.149123836901579e-08</v>
+        <v>1.149123836901555e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.224030665858906e-09</v>
+        <v>8.224030665857751e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.261589973454649e-08</v>
+        <v>1.261589973454574e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.026264413501327e-09</v>
+        <v>9.026264413501325e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.026103607920894e-09</v>
+        <v>9.02610360792278e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.223692698516854e-08</v>
+        <v>1.223692698517018e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.415396710241961e-08</v>
+        <v>1.415396710242076e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.173361501175635e-08</v>
+        <v>1.173361501175707e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.142733990250137e-08</v>
+        <v>1.142733990250052e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.215422114340977e-08</v>
+        <v>1.21542211434098e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.310461935847359e-08</v>
+        <v>1.31046193584741e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.142627710455064e-09</v>
+        <v>7.142627710457753e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>6.982787958897213e-09</v>
+        <v>6.982787958900562e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>8.893274783346294e-09</v>
+        <v>8.893274783347791e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.437972545193153e-09</v>
+        <v>7.437972545194574e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.437972545193152e-09</v>
+        <v>7.437972545193965e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>8.280061144313048e-09</v>
+        <v>8.280061144316405e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.131525853136339e-08</v>
+        <v>1.131525853136417e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>7.44308564791743e-09</v>
+        <v>7.44308564791746e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>9.315275785000485e-09</v>
+        <v>9.31527578500249e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.725246734605184e-09</v>
+        <v>7.725246734607032e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>9.644155807229934e-09</v>
+        <v>9.64415580723121e-09</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.535676173150705e-08</v>
+        <v>1.535676173150327e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.723639430735787e-08</v>
+        <v>2.723639430735414e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.807789729386437e-08</v>
+        <v>5.807789729386634e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.318550173435417e-08</v>
+        <v>3.318550173435715e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.318550173435417e-08</v>
+        <v>3.318550173435715e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.80782059310824e-08</v>
+        <v>4.80782059310818e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.126760783512533e-07</v>
+        <v>1.126760783512545e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>3.318525684054794e-08</v>
+        <v>3.318525684055064e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.831167045301533e-08</v>
+        <v>6.831167045301964e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.728142459425865e-08</v>
+        <v>3.728142459425656e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.033525195911131e-08</v>
+        <v>8.033525195911253e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.725680311102153e-09</v>
+        <v>9.725680311101829e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>9.656592320546673e-09</v>
+        <v>9.65659232054483e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.150798623814189e-08</v>
+        <v>1.150798623814549e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.804192046373912e-09</v>
+        <v>9.804192046373948e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.00318190472841e-08</v>
+        <v>1.003181904727979e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.086311374496012e-08</v>
+        <v>1.086311374495988e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.679421133484125e-08</v>
+        <v>1.679421133484436e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.264917177349155e-08</v>
+        <v>1.264917177349136e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.206395738377623e-08</v>
+        <v>1.206395738377564e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.030241782021462e-08</v>
+        <v>1.030241782021469e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.224282830716235e-08</v>
+        <v>1.224282830716641e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.382884800797598e-08</v>
+        <v>1.382884800797445e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.380498203102375e-08</v>
+        <v>1.38049820310313e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.557908064785517e-08</v>
+        <v>1.557908064785706e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.413663007491701e-08</v>
+        <v>1.413663007492652e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.413663007491701e-08</v>
+        <v>1.413663007492652e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.496628144183395e-08</v>
+        <v>1.496628144183489e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.800147882888432e-08</v>
+        <v>1.800147882887925e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.412930594543835e-08</v>
+        <v>1.412930594544773e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.600149608252139e-08</v>
+        <v>1.600149608252355e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.441146703212609e-08</v>
+        <v>1.441146703212143e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.633037610475085e-08</v>
+        <v>1.63303761047536e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.161310405730497e-08</v>
+        <v>3.161310405730666e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.755577807726463e-08</v>
+        <v>4.755577807726524e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.26284664034026e-08</v>
+        <v>5.262846640340708e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.351527799608221e-08</v>
+        <v>4.351527799608217e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.242406132380097e-08</v>
+        <v>3.24240613238037e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.870664908151306e-08</v>
+        <v>4.870664908151682e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.174184646857082e-08</v>
+        <v>5.174184646856713e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.786967358511745e-08</v>
+        <v>4.786967358512407e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.974499955764482e-08</v>
+        <v>4.974499955764584e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.18993301165585e-08</v>
+        <v>3.189933011656144e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.673823653114171e-08</v>
+        <v>6.673823653115007e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.540689448134574e-08</v>
+        <v>2.540689448135033e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.061162264321758e-08</v>
+        <v>3.061162264321892e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.238613711903687e-08</v>
+        <v>3.238613711903849e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.696987435755089e-08</v>
+        <v>3.696987435755585e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.093618732740692e-08</v>
+        <v>3.093618732740802e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.177292205402778e-08</v>
+        <v>3.177292205403036e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.480811944107818e-08</v>
+        <v>3.480811944108233e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.093594655763219e-08</v>
+        <v>3.093594655763535e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.280813669471523e-08</v>
+        <v>3.280813669471378e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.818864026577175e-08</v>
+        <v>2.81886402657706e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.31370167169447e-08</v>
+        <v>3.313701671694469e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.134941039811776e-08</v>
+        <v>1.134941039811777e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.296840395022326e-09</v>
+        <v>9.296840395022314e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.138793867439185e-08</v>
+        <v>1.138793867439177e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.688638101834129e-09</v>
+        <v>9.688638101834146e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>9.688476356572027e-09</v>
+        <v>9.688476356572029e-09</v>
       </c>
       <c r="G2" t="n">
         <v>1.137373386509232e-08</v>
@@ -2912,16 +2912,16 @@
         <v>1.138228191046277e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.13771666766854e-08</v>
+        <v>1.137716667668541e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04745289688934e-08</v>
+        <v>1.047452896889339e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.144861020366127e-08</v>
+        <v>1.14486102036613e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.138718284440096e-08</v>
+        <v>1.138718284440097e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2931,19 +2931,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.160298549313255e-08</v>
+        <v>1.160298549313252e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.28283455156418e-09</v>
+        <v>8.282834551564179e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.189815651717605e-08</v>
+        <v>1.189815651717604e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.036946386141333e-09</v>
+        <v>9.036946386141253e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.036784640879169e-09</v>
+        <v>9.036784640879121e-09</v>
       </c>
       <c r="G3" t="n">
         <v>1.179769208030174e-08</v>
@@ -2952,13 +2952,13 @@
         <v>1.193744165885631e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.182181033538659e-08</v>
+        <v>1.182181033538656e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.058426436664693e-08</v>
+        <v>1.058426436664691e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.181879083223182e-08</v>
+        <v>1.181879083223183e-08</v>
       </c>
       <c r="L3" t="n">
         <v>1.191204838145701e-08</v>
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.171808513276139e-09</v>
+        <v>7.171808513276131e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.082678143505132e-09</v>
+        <v>7.08267814350513e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.607003117673917e-09</v>
+        <v>7.607003117673909e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.449769225506346e-09</v>
+        <v>7.44976922550634e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.449769225506346e-09</v>
+        <v>7.44976922550634e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.437253894825447e-09</v>
+        <v>7.437253894825444e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.679482915877453e-09</v>
+        <v>7.679482915877443e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.438633112311246e-09</v>
+        <v>7.438633112311248e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.001479631841121e-09</v>
+        <v>8.001479631841119e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.236149378458171e-09</v>
+        <v>7.236149378458169e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.622132860862875e-09</v>
+        <v>7.622132860862877e-09</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.577858158072265e-08</v>
+        <v>1.577858158072264e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.795230188791954e-08</v>
+        <v>2.795230188791956e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.394012126565769e-08</v>
+        <v>3.394012126565765e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.201824602073727e-08</v>
+        <v>3.201824602073728e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.201824602073727e-08</v>
+        <v>3.201824602073728e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.156769277424372e-08</v>
+        <v>3.156769277424378e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.810450418781112e-08</v>
+        <v>3.810450418781118e-08</v>
       </c>
       <c r="I5" t="n">
         <v>3.201819391618351e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.208562955191249e-08</v>
+        <v>4.208562955191254e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.769905959057966e-08</v>
+        <v>2.769905959057967e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.753855382043502e-08</v>
+        <v>3.7538553820435e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3051,34 +3051,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.565369922939549e-09</v>
+        <v>9.565369922939527e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>9.574777771543521e-09</v>
+        <v>9.574777771543505e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.254395829888352e-08</v>
+        <v>1.254395829888355e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.64272688280899e-09</v>
+        <v>9.642726882808993e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.839715429413735e-09</v>
+        <v>9.839715429413731e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>9.830815304488836e-09</v>
+        <v>9.830815304488834e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.280658073747521e-08</v>
+        <v>1.280658073747522e-08</v>
       </c>
       <c r="I6" t="n">
         <v>1.228494275186042e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.291498029808541e-08</v>
+        <v>1.29149802980854e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.625444785759073e-09</v>
+        <v>9.625444785758947e-09</v>
       </c>
       <c r="L6" t="n">
         <v>1.001897110450446e-08</v>
@@ -3094,34 +3094,34 @@
         <v>1.354162223690246e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.357210894858602e-08</v>
+        <v>1.357210894858601e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.397642421752916e-08</v>
+        <v>1.397642421752915e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.381772391102312e-08</v>
+        <v>1.381772391102313e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.381772391102312e-08</v>
+        <v>1.381772391102313e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.380706761845175e-08</v>
+        <v>1.380706761845174e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.404929663950376e-08</v>
+        <v>1.404929663950377e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.380844683593756e-08</v>
+        <v>1.380844683593757e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.437129335546744e-08</v>
+        <v>1.437129335546742e-08</v>
       </c>
       <c r="K7" t="n">
         <v>1.360596310208449e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.399194658448919e-08</v>
+        <v>1.39919465844892e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.037917648509915e-08</v>
+        <v>3.037917648509914e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.556984113331185e-08</v>
+        <v>4.556984113331182e-08</v>
       </c>
       <c r="D8" t="n">
         <v>4.910326764068559e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.166201304665154e-08</v>
+        <v>4.16620130466516e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.113195508536952e-08</v>
+        <v>3.113195508536955e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.579250596962219e-08</v>
+        <v>4.579250596962218e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.603473499069561e-08</v>
+        <v>4.603473499069562e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.579388518710807e-08</v>
+        <v>4.579388518710806e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.63597087020509e-08</v>
+        <v>4.635970870205088e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.016213762591702e-08</v>
+        <v>3.016213762591698e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.180061652879748e-08</v>
+        <v>6.180061652879736e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.32620898795887e-08</v>
+        <v>2.326208987958873e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.791747883594658e-08</v>
+        <v>2.791747883594661e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.83221884930125e-08</v>
+        <v>2.832218849301251e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3490905723708e-08</v>
+        <v>3.349090572370803e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.815386576731802e-08</v>
+        <v>2.815386576731801e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.815243750581234e-08</v>
+        <v>2.815243750581231e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.839466652686432e-08</v>
+        <v>2.839466652686437e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.815381672329813e-08</v>
+        <v>2.815381672329815e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.871666324282799e-08</v>
+        <v>2.871666324282804e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.52716472075678e-08</v>
+        <v>2.527164720756781e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.833731647184975e-08</v>
+        <v>2.833731647184978e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.150603135167804e-08</v>
+        <v>1.150603135167793e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.370524989520289e-09</v>
+        <v>9.370524989520278e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.154224627127006e-08</v>
+        <v>1.154224627127e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.754202052214989e-09</v>
+        <v>9.754202052215085e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>9.754041165341083e-09</v>
+        <v>9.754041165341042e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.152507510455789e-08</v>
+        <v>1.152507510455787e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.152351644691306e-08</v>
+        <v>1.152351644691304e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.152689331802886e-08</v>
+        <v>1.152689331802878e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.055267806478886e-08</v>
+        <v>1.055267806478878e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.152615717579691e-08</v>
+        <v>1.152615717579687e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.152257429860526e-08</v>
+        <v>1.152257429860525e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.182178146396779e-08</v>
+        <v>1.182178146396767e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.38483884737542e-09</v>
+        <v>8.384838847375403e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.210045351078363e-08</v>
+        <v>1.210045351078345e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.067673133423995e-09</v>
+        <v>9.067673133423929e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.067512246550104e-09</v>
+        <v>9.067512246550245e-09</v>
       </c>
       <c r="G3" t="n">
         <v>1.197883233860732e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.204680683676305e-08</v>
+        <v>1.204680683676303e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.199146558323908e-08</v>
+        <v>1.199146558323903e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.049002400602691e-08</v>
+        <v>1.049002400602678e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.189366804301624e-08</v>
+        <v>1.189366804301642e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.198007021910234e-08</v>
+        <v>1.198007021910232e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.30800138849329e-09</v>
+        <v>7.308001388493262e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.258624957201505e-09</v>
+        <v>7.258624957201458e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.717065564971184e-09</v>
+        <v>7.717065564971163e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.507232735070753e-09</v>
+        <v>7.507232735070743e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.507232735070754e-09</v>
+        <v>7.507232735070746e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.513786788701889e-09</v>
+        <v>7.513786788701234e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.643307547691526e-09</v>
+        <v>7.643307547691533e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.496827440769595e-09</v>
+        <v>7.496827440769706e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.760071150458496e-09</v>
+        <v>7.760071150458468e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.344741310906101e-09</v>
+        <v>7.344741310906081e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.521224831816379e-09</v>
+        <v>7.521224831816376e-09</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.631825560438453e-08</v>
+        <v>1.631825560438432e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.921566349224486e-08</v>
+        <v>2.921566349224487e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.402362868511762e-08</v>
+        <v>3.40236286851176e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.121379814809848e-08</v>
+        <v>3.121379814809837e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.121379814809848e-08</v>
+        <v>3.121379814809836e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.106597496824483e-08</v>
+        <v>3.106597496824431e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.539176747267723e-08</v>
+        <v>3.539176747267721e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.121374189994396e-08</v>
+        <v>3.121374189994385e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5896131017457e-08</v>
+        <v>3.589613101745703e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.775755922835145e-08</v>
+        <v>2.775755922835144e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.351005150894071e-08</v>
+        <v>3.351005150894067e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3450,34 +3450,34 @@
         <v>1.220648234956297e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.752573425621629e-09</v>
+        <v>9.752573425621623e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.01139827170043e-08</v>
+        <v>1.011398271700429e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.694574583820008e-09</v>
+        <v>9.694574583820038e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.896040145331899e-09</v>
+        <v>9.896040145331882e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.241226774977085e-08</v>
+        <v>1.241226774977093e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.003847562876622e-08</v>
+        <v>1.003847562876621e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.23953084018394e-08</v>
+        <v>1.239530840183939e-08</v>
       </c>
       <c r="J6" t="n">
         <v>1.030123790141204e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.733197929045809e-09</v>
+        <v>9.733197929045816e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>9.91538555294464e-09</v>
+        <v>9.91538555294463e-09</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.374985371759313e-08</v>
+        <v>1.374985371759312e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.382177153668843e-08</v>
+        <v>1.38217715366884e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.415852467692093e-08</v>
+        <v>1.415852467692092e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.394833823349284e-08</v>
+        <v>1.394833823349282e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.394833823349284e-08</v>
+        <v>1.394833823349282e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.395563911780103e-08</v>
+        <v>1.395563911780097e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.408515987679139e-08</v>
+        <v>1.408515987679138e-08</v>
       </c>
       <c r="I7" t="n">
         <v>1.393867976986957e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.420192347955834e-08</v>
+        <v>1.420192347955832e-08</v>
       </c>
       <c r="K7" t="n">
         <v>1.378659364000594e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.396307716091621e-08</v>
+        <v>1.396307716091623e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.063775877809011e-08</v>
+        <v>3.063775877809012e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.597935983955394e-08</v>
+        <v>4.597935983955389e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.94674659926543e-08</v>
+        <v>4.946746599265433e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.192221960775045e-08</v>
+        <v>4.19222196077504e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.131622730308114e-08</v>
+        <v>3.131622730308112e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.61005480693103e-08</v>
+        <v>4.610054806931034e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.623006882833651e-08</v>
+        <v>4.623006882833645e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.608358872137881e-08</v>
+        <v>4.608358872137876e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.634983087127947e-08</v>
+        <v>4.634983087127941e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.03910920200726e-08</v>
+        <v>3.039109202007256e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.204520244833211e-08</v>
+        <v>6.204520244833205e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.267450712763045e-08</v>
+        <v>2.267450712763048e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.718481068687983e-08</v>
+        <v>2.718481068687982e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.752195885009381e-08</v>
+        <v>2.752195885009386e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.242357604209949e-08</v>
+        <v>3.242357604209953e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.730177213324851e-08</v>
+        <v>2.730177213324855e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.731867826799244e-08</v>
+        <v>2.731867826799251e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.744819902698285e-08</v>
+        <v>2.74481990269828e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.730171892006098e-08</v>
+        <v>2.730171892006097e-08</v>
       </c>
       <c r="J9" t="n">
         <v>2.756496262974973e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.457801542099218e-08</v>
+        <v>2.457801542099215e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.732611631110764e-08</v>
+        <v>2.732611631110762e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.131066011605797e-08</v>
+        <v>1.131066011605812e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.295895496726162e-09</v>
+        <v>9.295895496726321e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.136282640774412e-08</v>
+        <v>1.136282640774402e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.67018642584994e-09</v>
+        <v>9.670186425850158e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>9.670024837108081e-09</v>
+        <v>9.670024837108232e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.13547183055997e-08</v>
+        <v>1.135471830559964e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.160878592955564e-08</v>
+        <v>1.160878592955577e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.13410585207472e-08</v>
+        <v>1.134105852074712e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.039606821623508e-08</v>
+        <v>1.039606821623514e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.143255783705906e-08</v>
+        <v>1.143255783705919e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.148883226298124e-08</v>
+        <v>1.14888322629812e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3723,34 +3723,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.152262250496994e-08</v>
+        <v>1.152262250496997e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.245758784673333e-09</v>
+        <v>8.245758784673338e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.191495605037017e-08</v>
+        <v>1.191495605037006e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.004577941597745e-09</v>
+        <v>9.004577941597662e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.004416352855861e-09</v>
+        <v>9.004416352855798e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.185808936252299e-08</v>
+        <v>1.1858089362523e-08</v>
       </c>
       <c r="H3" t="n">
         <v>1.374189947434348e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.176029544059181e-08</v>
+        <v>1.176029544059187e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.021633506748711e-08</v>
+        <v>1.021633506748707e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.179568398276878e-08</v>
+        <v>1.179568398276884e-08</v>
       </c>
       <c r="L3" t="n">
         <v>1.282889318829445e-08</v>
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.129320759723927e-09</v>
+        <v>7.129320759723914e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>6.991671755148478e-09</v>
+        <v>6.991671755148469e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.718563021996345e-09</v>
+        <v>7.718563021996317e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.431489560555362e-09</v>
+        <v>7.43148956055537e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.431489560555362e-09</v>
+        <v>7.431489560555365e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.617538141660089e-09</v>
+        <v>7.617538141660066e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.060275647830082e-08</v>
+        <v>1.060275647830079e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>7.425032473877197e-09</v>
+        <v>7.425032473877196e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.502245834515223e-09</v>
+        <v>7.502245834515243e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.234447514651516e-09</v>
+        <v>7.234447514651527e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>9.146747812555134e-09</v>
+        <v>9.146747812555166e-09</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.564930824994354e-08</v>
+        <v>1.564930824994355e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.777211586577838e-08</v>
+        <v>2.777211586577841e-08</v>
       </c>
       <c r="D5" t="n">
         <v>3.757290141484728e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.33295988595813e-08</v>
+        <v>3.332959885958118e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.33295988595813e-08</v>
+        <v>3.332959885958118e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.640620992405959e-08</v>
+        <v>3.640620992405972e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.889765714524291e-08</v>
+        <v>9.889765714524311e-08</v>
       </c>
       <c r="I5" t="n">
         <v>3.332950185163081e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.478149230105239e-08</v>
+        <v>3.478149230105243e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.897870632965973e-08</v>
+        <v>2.897870632965969e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.071079276226184e-08</v>
+        <v>7.071079276226177e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.670892595441204e-09</v>
+        <v>9.670892595441216e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>9.633032676957646e-09</v>
+        <v>9.633032676957628e-09</v>
       </c>
       <c r="D6" t="n">
         <v>1.026734745141573e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.763135813943535e-09</v>
+        <v>9.763135813943524e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.974022281799501e-09</v>
+        <v>9.974022281799516e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.015910997737736e-08</v>
+        <v>1.015910997737738e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.600287186789943e-08</v>
+        <v>1.600287186789942e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>9.966604309594492e-09</v>
+        <v>9.966604309594501e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.019691188598798e-08</v>
+        <v>1.019691188598794e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.768549170047639e-09</v>
+        <v>9.768549170047856e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.170108280309129e-08</v>
+        <v>1.170108280309131e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3886,34 +3886,34 @@
         <v>1.380144991567344e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.379190620485867e-08</v>
+        <v>1.37919062048587e-08</v>
       </c>
       <c r="D7" t="n">
         <v>1.439027776817549e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.410581085423673e-08</v>
+        <v>1.410581085423677e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.410581085423673e-08</v>
+        <v>1.410581085423677e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.428966729760961e-08</v>
+        <v>1.42896672976096e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.727488563425032e-08</v>
+        <v>1.72748856342503e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.40971616298267e-08</v>
+        <v>1.409716162982673e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.41743749904648e-08</v>
+        <v>1.417437499046478e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.390657667060102e-08</v>
+        <v>1.390657667060105e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.58188769685047e-08</v>
+        <v>1.581887696850472e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.155500217418636e-08</v>
+        <v>3.155500217418644e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.748506373460198e-08</v>
+        <v>4.748506373460205e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.137474696202554e-08</v>
+        <v>5.137474696202564e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.343294904937692e-08</v>
+        <v>4.343294904937699e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.23610457860303e-08</v>
+        <v>3.236104578603042e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.797099424081785e-08</v>
+        <v>4.797099424081795e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.095621257746583e-08</v>
+        <v>5.095621257746591e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.777848857303498e-08</v>
+        <v>4.777848857303507e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.785883220011163e-08</v>
+        <v>4.785883220011162e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.13642623367874e-08</v>
+        <v>3.136426233678743e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.613809643098217e-08</v>
+        <v>6.613809643098229e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3963,28 +3963,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.515399572071897e-08</v>
+        <v>2.515399572071899e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.03068405602666e-08</v>
+        <v>3.030684056026662e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.090562774339929e-08</v>
+        <v>3.090562774339932e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.656947603467949e-08</v>
+        <v>3.656947603467953e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.061218900985592e-08</v>
+        <v>3.061218900985595e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.080460165301755e-08</v>
+        <v>3.080460165301754e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.378981998965827e-08</v>
+        <v>3.378981998965824e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.061209598523465e-08</v>
+        <v>3.061209598523468e-08</v>
       </c>
       <c r="J9" t="n">
         <v>3.068930934587271e-08</v>
@@ -3993,7 +3993,7 @@
         <v>2.743040333460546e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.233381132391261e-08</v>
+        <v>3.233381132391265e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4079,34 +4079,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.169317904866786e-08</v>
+        <v>1.169317904866738e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.375335100525709e-09</v>
+        <v>9.375335100525699e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.172864458087665e-08</v>
+        <v>1.172864458087608e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.751111592127308e-09</v>
+        <v>9.751111592127166e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>9.750949679431945e-09</v>
+        <v>9.750949679431889e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.171137572347809e-08</v>
+        <v>1.171137572347758e-08</v>
       </c>
       <c r="H2" t="n">
         <v>1.171063062501301e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.171847689979724e-08</v>
+        <v>1.171847689979676e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.047842100056681e-08</v>
+        <v>1.047842100056671e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.152661631022493e-08</v>
+        <v>1.152661631022483e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.170730955272332e-08</v>
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.212568490934029e-08</v>
+        <v>1.212568490934016e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>8.367534851245285e-09</v>
+        <v>8.367534851245281e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.239901188978126e-08</v>
+        <v>1.239901188978115e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.08183258374256e-09</v>
+        <v>9.081832583742755e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.081670671047177e-09</v>
+        <v>9.081670671047382e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.227668498118573e-08</v>
+        <v>1.227668498118562e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.235013012022136e-08</v>
+        <v>1.235013012022135e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.232696909343062e-08</v>
+        <v>1.232696909343046e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.037093911538026e-08</v>
+        <v>1.03709391153803e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.190187850246529e-08</v>
+        <v>1.19018785024653e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.226664482777613e-08</v>
+        <v>1.226664482777612e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.208640746080837e-09</v>
+        <v>7.208640746080855e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.120167618865875e-09</v>
+        <v>7.120167618865877e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.609240247330094e-09</v>
+        <v>7.609240247330123e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.467928638284441e-09</v>
+        <v>7.46792863828444e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.46792863828444e-09</v>
+        <v>7.467928638284438e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.404885731263677e-09</v>
+        <v>7.404885731263688e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.54297153872442e-09</v>
+        <v>7.54297153872443e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.447719913044895e-09</v>
+        <v>7.447719913044897e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.678236938292517e-09</v>
+        <v>7.678236938292494e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.271135818669168e-09</v>
+        <v>7.271135818669129e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.394613878450322e-09</v>
+        <v>7.394613878450316e-09</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.62366721207763e-08</v>
+        <v>1.623667212077631e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.840796906903889e-08</v>
+        <v>2.840796906903881e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.379406885070875e-08</v>
+        <v>3.379406885070879e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.198793589314911e-08</v>
+        <v>3.198793589314906e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.198793589314911e-08</v>
+        <v>3.198793589314906e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.081251461333473e-08</v>
+        <v>3.081251461333479e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.528427513380937e-08</v>
+        <v>3.528427513380935e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.198789267833881e-08</v>
+        <v>3.198789267833876e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.612206432974421e-08</v>
+        <v>3.61220643297441e-08</v>
       </c>
       <c r="K5" t="n">
         <v>2.811129673605521e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.288910603834863e-08</v>
+        <v>3.288910603834857e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.205133547495601e-08</v>
+        <v>1.205133547495604e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.603459491001737e-09</v>
+        <v>9.603459491001619e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.99939034502079e-09</v>
+        <v>9.999390345020777e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>9.644164142771664e-09</v>
+        <v>9.644164142771674e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.839628384019999e-09</v>
+        <v>9.839628384020012e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>9.788802295306282e-09</v>
+        <v>9.78880229530629e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.266381582235996e-08</v>
+        <v>1.266381582236001e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.229041464192006e-08</v>
+        <v>1.229041464192007e-08</v>
       </c>
       <c r="J6" t="n">
         <v>1.020806194447529e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.652710403096044e-09</v>
+        <v>9.652710403096082e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>9.780376685232674e-09</v>
+        <v>9.780376685232647e-09</v>
       </c>
     </row>
     <row r="7">
@@ -4279,13 +4279,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.359480650989078e-08</v>
+        <v>1.359480650989073e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.362530755431096e-08</v>
+        <v>1.362530755431095e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.399501359155682e-08</v>
+        <v>1.399501359155684e-08</v>
       </c>
       <c r="E7" t="n">
         <v>1.384563547355159e-08</v>
@@ -4294,22 +4294,22 @@
         <v>1.384563547355159e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.379105149507362e-08</v>
+        <v>1.37910514950736e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.392913730253436e-08</v>
+        <v>1.392913730253432e-08</v>
       </c>
       <c r="I7" t="n">
         <v>1.383388567685485e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.406440270210246e-08</v>
+        <v>1.406440270210245e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.365730158247911e-08</v>
+        <v>1.36573015824791e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.378077964226027e-08</v>
+        <v>1.378077964226026e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.042325876399272e-08</v>
+        <v>3.042325876399274e-08</v>
       </c>
       <c r="C8" t="n">
         <v>4.562619627376438e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.912468969618814e-08</v>
+        <v>4.912468969618813e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.168764542627285e-08</v>
+        <v>4.168764542627284e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.115007666571416e-08</v>
+        <v>3.115007666571415e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.577727298517639e-08</v>
+        <v>4.577727298517635e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.591535879265837e-08</v>
+        <v>4.591535879265832e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.582010716695764e-08</v>
+        <v>4.582010716695762e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.605360313034283e-08</v>
+        <v>4.605360313034282e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.020419049079437e-08</v>
+        <v>3.020419049079432e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.160055857354088e-08</v>
+        <v>6.160055857354095e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.328754750666646e-08</v>
+        <v>2.328754750666645e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.794210258444685e-08</v>
+        <v>2.794210258444684e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.831220281424578e-08</v>
+        <v>2.831220281424575e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.348678205851532e-08</v>
+        <v>3.348678205851533e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.815072090201835e-08</v>
+        <v>2.815072090201836e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.810784652520951e-08</v>
+        <v>2.810784652520947e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.824593233267026e-08</v>
+        <v>2.824593233267024e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.815068070699072e-08</v>
+        <v>2.815068070699074e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.838119773223833e-08</v>
+        <v>2.838119773223834e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.215158673437359e-08</v>
+        <v>2.215158673437353e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.809757467239617e-08</v>
+        <v>2.809757467239619e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4475,34 +4475,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.168363284691634e-08</v>
+        <v>1.168363284691633e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.524123878070629e-09</v>
+        <v>9.524123878070631e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.171687594009522e-08</v>
+        <v>1.17168759400952e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>9.865254538209455e-09</v>
+        <v>9.86525453820946e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>9.865093178720407e-09</v>
+        <v>9.865093178720401e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.17017641279321e-08</v>
+        <v>1.170176412793208e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.170037929673789e-08</v>
+        <v>1.17003792967379e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.170439770515643e-08</v>
+        <v>1.170439770515641e-08</v>
       </c>
       <c r="J2" t="n">
         <v>1.064566733293494e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.165088231519496e-08</v>
+        <v>1.165088231519497e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.169933362337378e-08</v>
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.194389460443443e-08</v>
+        <v>1.194389460443445e-08</v>
       </c>
       <c r="C3" t="n">
         <v>8.461943720397096e-09</v>
@@ -4524,28 +4524,28 @@
         <v>1.220139321775154e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>9.079396244549417e-09</v>
+        <v>9.079396244549405e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>9.079234885060346e-09</v>
+        <v>9.079234885060352e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.209443393374911e-08</v>
+        <v>1.209443393374909e-08</v>
       </c>
       <c r="H3" t="n">
         <v>1.216347896663933e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.211288032880717e-08</v>
+        <v>1.211288032880716e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.04881312371639e-08</v>
+        <v>1.048813123716386e-08</v>
       </c>
       <c r="K3" t="n">
         <v>1.193685168371238e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.209609473258078e-08</v>
+        <v>1.209609473258077e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4558,34 +4558,34 @@
         <v>7.308371112004347e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.248525496792042e-09</v>
+        <v>7.248525496792033e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.683867142038211e-09</v>
+        <v>7.683867142038214e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.516335874346388e-09</v>
+        <v>7.516335874346412e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.516335874346388e-09</v>
+        <v>7.516335874346412e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.503743568378665e-09</v>
+        <v>7.503743568378667e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.635044554561787e-09</v>
+        <v>7.635044554561797e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.495378943073379e-09</v>
+        <v>7.495378943073393e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.792665164611427e-09</v>
+        <v>7.792665164611413e-09</v>
       </c>
       <c r="K4" t="n">
         <v>7.362365313658316e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.511971753489334e-09</v>
+        <v>7.511971753489337e-09</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.640013590344782e-08</v>
+        <v>1.640013590344785e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.910636177352822e-08</v>
+        <v>2.91063617735282e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.353078855194032e-08</v>
+        <v>3.353078855194039e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.127279386120783e-08</v>
+        <v>3.127279386120785e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.127279386120783e-08</v>
+        <v>3.127279386120785e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.096587725850074e-08</v>
+        <v>3.096587725850146e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.531472596909298e-08</v>
+        <v>3.5314725969093e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.127273884817423e-08</v>
+        <v>3.127273884817422e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.655326896352805e-08</v>
+        <v>3.655326896352811e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>2.813007629600898e-08</v>
+        <v>2.813007629600899e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.341230737992858e-08</v>
+        <v>3.341230737992859e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.219132334162479e-08</v>
+        <v>1.21913233416248e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.728452121309256e-09</v>
+        <v>9.728452121309238e-09</v>
       </c>
       <c r="D6" t="n">
         <v>1.006687381227047e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.682683224261986e-09</v>
+        <v>9.682683224262001e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.881825744567536e-09</v>
+        <v>9.881825744567553e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>9.882401933875741e-09</v>
+        <v>9.882401933875742e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.284068245818423e-08</v>
+        <v>1.284068245818424e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>9.874037308570456e-09</v>
+        <v>9.874037308570473e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.275163385244796e-08</v>
+        <v>1.275163385244794e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.738088448461454e-09</v>
+        <v>9.738088448461457e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>9.893275952738399e-09</v>
+        <v>9.89327595273841e-09</v>
       </c>
     </row>
     <row r="7">
@@ -4675,31 +4675,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.376182420042218e-08</v>
+        <v>1.376182420042219e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.382279169653835e-08</v>
+        <v>1.382279169653837e-08</v>
       </c>
       <c r="D7" t="n">
         <v>1.413692713250549e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.396151675783191e-08</v>
+        <v>1.396151675783193e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.396151675783191e-08</v>
+        <v>1.396151675783193e-08</v>
       </c>
       <c r="G7" t="n">
         <v>1.395719665679649e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.40884976429796e-08</v>
+        <v>1.408849764297961e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.394883203149121e-08</v>
+        <v>1.394883203149123e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.424611825302925e-08</v>
+        <v>1.424611825302926e-08</v>
       </c>
       <c r="K7" t="n">
         <v>1.381581840207615e-08</v>
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.063427469700328e-08</v>
+        <v>3.063427469700327e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.596462997747052e-08</v>
+        <v>4.596462997747053e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.942656404149893e-08</v>
+        <v>4.942656404149902e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.191718672329823e-08</v>
+        <v>4.191718672329829e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.131262867158604e-08</v>
+        <v>3.131262867158606e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.608346248857403e-08</v>
+        <v>4.608346248857405e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.621476347479245e-08</v>
+        <v>4.621476347479243e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.607509786326874e-08</v>
+        <v>4.60750978632688e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.637538189852237e-08</v>
+        <v>4.637538189852239e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.040492144727359e-08</v>
+        <v>3.040492144727354e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.2025576296558e-08</v>
+        <v>6.202557629655804e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.267042175703662e-08</v>
+        <v>2.267042175703666e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.716822088471694e-08</v>
+        <v>2.716822088471699e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.748275121314445e-08</v>
+        <v>2.748275121314454e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.24143237026667e-08</v>
+        <v>3.24143237026668e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.729431320947573e-08</v>
+        <v>2.72943132094758e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.73026258449751e-08</v>
+        <v>2.730262584497511e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.743392683115818e-08</v>
+        <v>2.743392683115825e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.729426121966979e-08</v>
+        <v>2.729426121966987e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.759154744120781e-08</v>
+        <v>2.759154744120789e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.44862333674641e-08</v>
+        <v>2.448623336746417e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.731085403008569e-08</v>
+        <v>2.731085403008578e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4871,34 +4871,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.203182003729282e-08</v>
+        <v>1.203182003729281e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.057688787972531e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.217829108725169e-08</v>
+        <v>1.217829108725171e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.08610294143222e-08</v>
+        <v>1.086102941432221e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>9.937000810093668e-09</v>
+        <v>9.937000810093678e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.203533158520876e-08</v>
+        <v>1.203533158520877e-08</v>
       </c>
       <c r="H2" t="n">
         <v>1.26245459901927e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.182808537971609e-08</v>
+        <v>1.182808537971611e-08</v>
       </c>
       <c r="J2" t="n">
         <v>1.198093271407889e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.144703158786176e-08</v>
+        <v>1.144703158786175e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.287781264635868e-08</v>
@@ -4911,28 +4911,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.392923013053391e-08</v>
+        <v>1.392923013053389e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.043871252597864e-08</v>
+        <v>1.043871252597863e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.497381434760496e-08</v>
+        <v>1.497381434760497e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.088900134655416e-08</v>
+        <v>1.088900134655417e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>9.363826047231455e-09</v>
+        <v>9.363826047231452e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.395939399997583e-08</v>
+        <v>1.395939399997585e-08</v>
       </c>
       <c r="H3" t="n">
         <v>1.823492106890783e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.248292736013954e-08</v>
+        <v>1.248292736013955e-08</v>
       </c>
       <c r="J3" t="n">
         <v>1.322006946088746e-08</v>
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.059963346091398e-08</v>
+        <v>1.059963346091397e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.173596603698597e-09</v>
+        <v>8.173596603698617e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.225409135021133e-08</v>
+        <v>1.225409135021136e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.198936453927108e-09</v>
+        <v>8.198936453927123e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>8.198936453927109e-09</v>
+        <v>8.198936453927121e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.062863930336894e-08</v>
+        <v>1.062863930336888e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.737248543073304e-08</v>
+        <v>1.737248543073305e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.242398093422748e-09</v>
+        <v>8.242398093422784e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>9.293267061507514e-09</v>
+        <v>9.293267061507539e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>9.066584203315466e-09</v>
+        <v>9.066584203315491e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>2.005651432869052e-08</v>
+        <v>2.005651432869054e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.335111715210313e-08</v>
+        <v>8.33511171521028e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.410008909909571e-08</v>
+        <v>4.410008909909579e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.141957747113491e-07</v>
+        <v>1.141957747113493e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>4.410009118329388e-08</v>
+        <v>4.410009118329395e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.410009118329388e-08</v>
+        <v>4.410009118329395e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.692779666791361e-08</v>
+        <v>8.692779666791434e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.298417436387263e-07</v>
+        <v>2.298417436387261e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>4.409949084157211e-08</v>
+        <v>4.409949084157216e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>6.385552383482887e-08</v>
+        <v>6.385552383482891e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.726100308060208e-08</v>
+        <v>5.726100308060206e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.048252050712053e-08</v>
+        <v>7.048252050712051e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5031,22 +5031,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.334175979923778e-08</v>
+        <v>1.334175979923774e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.091725193316451e-08</v>
+        <v>1.091725193316457e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.508191399652968e-08</v>
+        <v>1.508191399652969e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.071249264644085e-08</v>
+        <v>1.071249264644087e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.098326610328811e-08</v>
+        <v>1.098326610328813e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.337076564169262e-08</v>
+        <v>1.337076564169266e-08</v>
       </c>
       <c r="H6" t="n">
         <v>2.314973615559761e-08</v>
@@ -5055,10 +5055,10 @@
         <v>1.387919464178782e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.220261059074621e-08</v>
+        <v>1.22026105907462e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.17850006319878e-08</v>
+        <v>1.178500063198785e-08</v>
       </c>
       <c r="L6" t="n">
         <v>2.286991767868324e-08</v>
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.745078469248262e-08</v>
+        <v>1.745078469248259e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.509414758251499e-08</v>
+        <v>1.5094147582515e-08</v>
       </c>
       <c r="D7" t="n">
         <v>1.910479664068579e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.509253314160143e-08</v>
+        <v>1.509253314160146e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.509253314160143e-08</v>
+        <v>1.509253314160146e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.747979053493755e-08</v>
+        <v>1.747979053493752e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.422363666230168e-08</v>
+        <v>2.422363666230169e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.509354932499139e-08</v>
+        <v>1.50935493249914e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.614441829307616e-08</v>
+        <v>1.614441829307615e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.591773543488412e-08</v>
+        <v>1.591773543488411e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.690766556025916e-08</v>
+        <v>2.690766556025918e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.555054695389849e-08</v>
+        <v>3.555054695389845e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.945792679725677e-08</v>
+        <v>4.945792679725679e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.683879241994164e-08</v>
+        <v>5.683879241994154e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.501011464661642e-08</v>
+        <v>4.501011464661638e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.370868749867099e-08</v>
+        <v>3.370868749867094e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.184135065182955e-08</v>
+        <v>5.184135065182945e-08</v>
       </c>
       <c r="H8" t="n">
         <v>5.858519677919398e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.945510944188352e-08</v>
+        <v>4.945510944188338e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.050917432154766e-08</v>
+        <v>5.050917432154763e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.371542645209961e-08</v>
+        <v>3.371542645209953e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>7.82560333288277e-08</v>
+        <v>7.825603332882773e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5151,34 +5151,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.001571787577777e-08</v>
+        <v>3.001571787577781e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.320640029263488e-08</v>
+        <v>3.320640029263495e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.721749604926511e-08</v>
+        <v>3.721749604926507e-08</v>
       </c>
       <c r="E9" t="n">
         <v>3.960788479527846e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.320639647444939e-08</v>
+        <v>3.320639647444945e-08</v>
       </c>
       <c r="G9" t="n">
         <v>3.559204324505742e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>4.233588937242165e-08</v>
+        <v>4.23358893724216e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.320580203511134e-08</v>
+        <v>3.320580203511133e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.42566710031961e-08</v>
+        <v>3.425667100319609e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.081584974370211e-08</v>
+        <v>3.081584974370206e-08</v>
       </c>
       <c r="L9" t="n">
         <v>4.501991827037908e-08</v>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.200913009475776e-08</v>
+        <v>1.200913009475777e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.068158219518731e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.218295710832149e-08</v>
+        <v>1.21829571083215e-08</v>
       </c>
       <c r="E2" t="n">
         <v>1.096763484449515e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.003652870182221e-08</v>
+        <v>1.003652870182222e-08</v>
       </c>
       <c r="G2" t="n">
         <v>1.205994076951143e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.254179180027226e-08</v>
+        <v>1.254179180027227e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.18994365976566e-08</v>
+        <v>1.189943659765662e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.200624075780301e-08</v>
+        <v>1.200624075780303e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.150711793864314e-08</v>
+        <v>1.150711793864315e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.282795030553432e-08</v>
+        <v>1.282795030553435e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.357986400263784e-08</v>
+        <v>1.357986400263785e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.081086207019539e-08</v>
+        <v>1.081086207019542e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.481582178791677e-08</v>
+        <v>1.48158217879168e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.126460668851894e-08</v>
+        <v>1.126460668851895e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>9.727748810186136e-09</v>
+        <v>9.727748810186141e-09</v>
       </c>
       <c r="G3" t="n">
         <v>1.394409597754615e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.74592356809391e-08</v>
+        <v>1.745923568093913e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.280033908920515e-08</v>
+        <v>1.280033908920516e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.302561345389675e-08</v>
+        <v>1.302561345389676e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.232522411210073e-08</v>
+        <v>1.232522411210074e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.942977541840208e-08</v>
+        <v>1.942977541840211e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5347,34 +5347,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.002189085973562e-08</v>
+        <v>1.002189085973561e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.67408790736741e-09</v>
+        <v>8.674087907367407e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.198534694231477e-08</v>
+        <v>1.19853469423148e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.697122971946293e-09</v>
+        <v>8.697122971946288e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>8.69712297194629e-09</v>
+        <v>8.697122971946287e-09</v>
       </c>
       <c r="G4" t="n">
         <v>1.058551132571455e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.612955428252007e-08</v>
+        <v>1.612955428252008e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.729248057446681e-09</v>
+        <v>8.729248057446664e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.876841909306925e-09</v>
+        <v>8.876841909306935e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>9.144031506107553e-09</v>
+        <v>9.144031506107548e-09</v>
       </c>
       <c r="L4" t="n">
         <v>1.918361215908945e-08</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.907014574277995e-08</v>
+        <v>6.907014574278007e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.884539016717981e-08</v>
+        <v>4.88453901671799e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.013851457675114e-07</v>
+        <v>1.013851457675119e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>4.884539212463677e-08</v>
+        <v>4.884539212463681e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.884539212463678e-08</v>
+        <v>4.884539212463681e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.003660636776302e-08</v>
+        <v>8.003660636776311e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.917569033676695e-07</v>
+        <v>1.917569033676697e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>4.884491312008835e-08</v>
+        <v>4.884491312008839e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.228266344932268e-08</v>
+        <v>5.228266344932272e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.37572335784222e-08</v>
+        <v>5.375723357842207e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.228633886626517e-08</v>
+        <v>7.228633886626483e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.256741311054591e-08</v>
+        <v>1.256741311054593e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.122845532307326e-08</v>
+        <v>1.122845532307327e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.460127984977061e-08</v>
+        <v>1.460127984977064e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.103658004668028e-08</v>
+        <v>1.103658004668029e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.127797419316097e-08</v>
+        <v>1.127797419316096e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.313103357652488e-08</v>
+        <v>1.313103357652489e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.150632161967802e-08</v>
+        <v>2.150632161967808e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.398066942382066e-08</v>
+        <v>1.398066942382067e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.157695617977931e-08</v>
+        <v>1.157695617977933e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.16688998358376e-08</v>
+        <v>1.166889983583761e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.179104323824576e-08</v>
+        <v>2.179104323824574e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.645701507406402e-08</v>
+        <v>1.645701507406403e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.516484931886657e-08</v>
+        <v>1.516484931886656e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.842005411547452e-08</v>
+        <v>1.842005411547456e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.516407885147587e-08</v>
+        <v>1.516407885147589e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.516407885147587e-08</v>
+        <v>1.516407885147589e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.702063554004297e-08</v>
+        <v>1.702063554004302e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.25646784968485e-08</v>
+        <v>2.256467849684851e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.516437227177508e-08</v>
+        <v>1.516437227177511e-08</v>
       </c>
       <c r="J7" t="n">
         <v>1.531196612363535e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.557915572043598e-08</v>
+        <v>1.557915572043599e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.56187363734179e-08</v>
+        <v>2.561873637341789e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.332387805276409e-08</v>
+        <v>3.332387805276412e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.723575525611259e-08</v>
+        <v>4.723575525611255e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.364067736230348e-08</v>
+        <v>5.364067736230352e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.307793868667983e-08</v>
+        <v>4.307793868667984e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.251335879696229e-08</v>
+        <v>3.25133587969623e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.908876095282006e-08</v>
+        <v>4.908876095282004e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.463280390962584e-08</v>
+        <v>5.463280390962587e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.723249768455217e-08</v>
+        <v>4.72324976845522e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.738307902221302e-08</v>
+        <v>4.738307902221303e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.216364744488422e-08</v>
+        <v>3.216364744488426e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>7.3565851509522e-08</v>
+        <v>7.356585150952203e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.709696034260468e-08</v>
+        <v>2.709696034260471e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.069911150928997e-08</v>
+        <v>3.069911150928992e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.395473426984342e-08</v>
+        <v>3.39547342698435e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.634704582244955e-08</v>
+        <v>3.634704582244957e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.069910832271509e-08</v>
+        <v>3.06991083227151e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.255489773046633e-08</v>
+        <v>3.255489773046638e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.809894068727188e-08</v>
+        <v>3.809894068727191e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.069863446219846e-08</v>
+        <v>3.06986344621985e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.084622831405874e-08</v>
+        <v>3.084622831405881e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.827763185297141e-08</v>
+        <v>2.827763185297145e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.115299856384125e-08</v>
+        <v>4.115299856384131e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5663,34 +5663,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.198364720888366e-08</v>
+        <v>1.198364720888377e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.083354142709164e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.214154144025741e-08</v>
+        <v>1.214154144025755e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.111952853363308e-08</v>
+        <v>1.111952853363319e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.018691630022678e-08</v>
+        <v>1.018691630022676e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.204147094221741e-08</v>
+        <v>1.204147094221757e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.242402909136769e-08</v>
+        <v>1.242402909136771e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.199431508531728e-08</v>
+        <v>1.199431508531741e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.206138744167445e-08</v>
+        <v>1.206138744167447e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.153077693476887e-08</v>
+        <v>1.153077693476882e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.273779956808179e-08</v>
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.33467888627292e-08</v>
+        <v>1.334678886272921e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.15266404513312e-08</v>
+        <v>1.152664045133121e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.446792240749043e-08</v>
+        <v>1.446792240749051e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.198103073532602e-08</v>
+        <v>1.198103073532601e-08</v>
       </c>
       <c r="F3" t="n">
         <v>1.044168725283158e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.376060761613204e-08</v>
+        <v>1.376060761613211e-08</v>
       </c>
       <c r="H3" t="n">
         <v>1.656121470412363e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.342265034684652e-08</v>
+        <v>1.34226503468464e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.311740662197846e-08</v>
+        <v>1.311740662197832e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.230898444587503e-08</v>
+        <v>1.230898444587504e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.873170195016341e-08</v>
+        <v>1.873170195016342e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.715481373588648e-09</v>
+        <v>9.71548137358867e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>9.752534440147152e-09</v>
+        <v>9.752534440147143e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.149896935189021e-08</v>
+        <v>1.149896935189024e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>9.774507715039017e-09</v>
+        <v>9.774507715039004e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>9.774507715039019e-09</v>
+        <v>9.774507715039006e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.035911290180259e-08</v>
+        <v>1.035911290180265e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.479177350778208e-08</v>
+        <v>1.47917735077821e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.787752652397774e-09</v>
+        <v>9.787752652397768e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.963933209217709e-09</v>
+        <v>8.963933209217742e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>9.118285930060514e-09</v>
+        <v>9.118285930060534e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.815717159395429e-08</v>
+        <v>1.815717159395431e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.185742993077398e-08</v>
+        <v>6.185742993077402e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.379773706090848e-08</v>
+        <v>6.379773706090836e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.041355629373923e-08</v>
+        <v>9.041355629373907e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.379773876232923e-08</v>
+        <v>6.379773876232913e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.379773876232923e-08</v>
+        <v>6.379773876232913e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.398437305451744e-08</v>
+        <v>7.398437305451848e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.599278375648997e-07</v>
+        <v>1.599278375648995e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>6.379755361862237e-08</v>
+        <v>6.379755361862226e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.23641579575143e-08</v>
+        <v>5.236415795751432e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.119516120150319e-08</v>
+        <v>5.119516120150325e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>6.443276056918323e-08</v>
+        <v>6.443276056918364e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5826,34 +5826,34 @@
         <v>1.226934570594551e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.233346422325805e-08</v>
+        <v>1.233346422325803e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.410813979645838e-08</v>
+        <v>1.410813979645839e-08</v>
       </c>
       <c r="E6" t="n">
         <v>1.213945177832176e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.235449654758709e-08</v>
+        <v>1.23544965475871e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.560527213491899e-08</v>
+        <v>1.560527213491915e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.015933946979549e-08</v>
+        <v>2.01593394697955e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.234161698475466e-08</v>
+        <v>1.234161698475464e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.423268815783213e-08</v>
+        <v>1.423268815783212e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.165104845029819e-08</v>
+        <v>1.16510484502982e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.076802454819219e-08</v>
+        <v>2.07680245481922e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5866,10 +5866,10 @@
         <v>1.618145003914194e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.625390476023714e-08</v>
+        <v>1.625390476023715e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.796451867553435e-08</v>
+        <v>1.796451867553439e-08</v>
       </c>
       <c r="E7" t="n">
         <v>1.625486168027e-08</v>
@@ -5878,22 +5878,22 @@
         <v>1.625486168027e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.682508156735577e-08</v>
+        <v>1.682508156735596e-08</v>
       </c>
       <c r="H7" t="n">
         <v>2.125774217333537e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.625372131795109e-08</v>
+        <v>1.62537213179511e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5429901874771e-08</v>
+        <v>1.542990187477102e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.558425459561381e-08</v>
+        <v>1.558425459561382e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.462314025950754e-08</v>
+        <v>2.462314025950757e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.303569504301651e-08</v>
+        <v>3.303569504301655e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.833310906690325e-08</v>
+        <v>4.83331090669033e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.319577698448802e-08</v>
+        <v>5.319577698448809e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.416984878654639e-08</v>
+        <v>4.416984878654641e-08</v>
       </c>
       <c r="F8" t="n">
         <v>3.359143843796651e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.889984656174083e-08</v>
+        <v>4.889984656174084e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3332507167721e-08</v>
+        <v>5.333250716772104e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.832848631233594e-08</v>
+        <v>4.832848631233597e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.750765813960538e-08</v>
+        <v>4.750765813960548e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.215577062623977e-08</v>
+        <v>3.215577062623979e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>7.259701110519401e-08</v>
+        <v>7.259701110519403e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.596253895752612e-08</v>
+        <v>2.596253895752617e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.070366093464767e-08</v>
+        <v>3.070366093464768e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.241469518161431e-08</v>
+        <v>3.24146951816143e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.609120066105596e-08</v>
+        <v>3.6091200661056e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.070365792290536e-08</v>
+        <v>3.070365792290532e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.12748377417664e-08</v>
+        <v>3.12748377417665e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.570749834774588e-08</v>
+        <v>3.570749834774594e-08</v>
       </c>
       <c r="I9" t="n">
         <v>3.070347749236161e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.987965804918156e-08</v>
+        <v>2.987965804918158e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.73289670429012e-08</v>
+        <v>2.732896704290122e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.907289643391806e-08</v>
+        <v>3.907289643391812e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6065,28 +6065,28 @@
         <v>1.012330989879279e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.14742319064417e-08</v>
+        <v>1.147423190644171e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.03928427991044e-08</v>
+        <v>1.039284279910441e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>9.504694345695996e-09</v>
+        <v>9.504694345696003e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.143645394531402e-08</v>
+        <v>1.1436453945314e-08</v>
       </c>
       <c r="H2" t="n">
         <v>1.16217125146377e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.13763045051633e-08</v>
+        <v>1.137630450516329e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.147527645984156e-08</v>
+        <v>1.147527645984163e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.092344251959106e-08</v>
+        <v>1.092344251959108e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.161049127070705e-08</v>
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.185147587432823e-08</v>
+        <v>1.185147587432819e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.708908916149482e-09</v>
+        <v>9.708908916149501e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.245265441679693e-08</v>
+        <v>1.245265441679694e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.01374812680033e-08</v>
+        <v>1.013748126800335e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.671534260252086e-09</v>
+        <v>8.671534260252068e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.218555394634063e-08</v>
+        <v>1.21855539463406e-08</v>
       </c>
       <c r="H3" t="n">
         <v>1.357381489686571e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.175848573480909e-08</v>
+        <v>1.175848573480907e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.238421609671352e-08</v>
+        <v>1.238421609671362e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.118815930326026e-08</v>
+        <v>1.118815930326027e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.343883867315703e-08</v>
+        <v>1.343883867315704e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.531888352584313e-09</v>
+        <v>7.531888352584275e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.287045482993555e-09</v>
+        <v>7.287045482993553e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>8.487340515105942e-09</v>
+        <v>8.487340515105952e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.309796412555725e-09</v>
+        <v>7.309796412555729e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.309796412555726e-09</v>
+        <v>7.309796412555729e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>8.05103522185972e-09</v>
+        <v>8.051035221859717e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>1.026954874020153e-08</v>
+        <v>1.026954874020152e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>7.332468638952788e-09</v>
+        <v>7.332468638952768e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.334620502044314e-09</v>
+        <v>8.334620502044317e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.75180892126028e-09</v>
+        <v>7.751808921260266e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.002620545528834e-08</v>
+        <v>1.002620545528833e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.444360417377012e-08</v>
+        <v>3.444360417376932e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.278009700295488e-08</v>
+        <v>3.278009700295484e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.110489408119515e-08</v>
+        <v>5.110489408119506e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.278009883041327e-08</v>
+        <v>3.278009883041321e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.278009883041328e-08</v>
+        <v>3.278009883041321e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.44299548292126e-08</v>
+        <v>4.442995482921239e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.778948716838319e-08</v>
+        <v>8.778948716838307e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.277988265427466e-08</v>
+        <v>3.277988265427461e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.045064813219684e-08</v>
+        <v>5.045064813219672e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.827748985076053e-08</v>
+        <v>3.827748985076018e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.78924808469393e-08</v>
+        <v>8.789248084693919e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.279816436975353e-08</v>
+        <v>1.279816436975346e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.954264605422823e-09</v>
+        <v>9.954264605422853e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.380161014965572e-08</v>
+        <v>1.380161014965571e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.753323584981425e-09</v>
+        <v>9.753323584981421e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.982076762020086e-09</v>
+        <v>9.982076762020089e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.331731123902896e-08</v>
+        <v>1.331731123902891e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.293504059056507e-08</v>
+        <v>1.293504059056506e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.259874465612197e-08</v>
+        <v>1.259874465612195e-08</v>
       </c>
       <c r="J6" t="n">
         <v>1.362249564633383e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.039828937533374e-08</v>
+        <v>1.039828937533372e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.269006415640136e-08</v>
+        <v>1.269006415640135e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6265,16 +6265,16 @@
         <v>1.399262754507357e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.514684016791554e-08</v>
+        <v>1.514684016791555e-08</v>
       </c>
       <c r="E7" t="n">
         <v>1.399231759307143e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.399231759307145e-08</v>
+        <v>1.399231759307143e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.471097977930032e-08</v>
+        <v>1.471097977930031e-08</v>
       </c>
       <c r="H7" t="n">
         <v>1.692949329764212e-08</v>
@@ -6283,13 +6283,13 @@
         <v>1.399241319639336e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.499456505948489e-08</v>
+        <v>1.499456505948493e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.441175347870082e-08</v>
+        <v>1.441175347870085e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.668615001272892e-08</v>
+        <v>1.668615001272891e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.212515587296726e-08</v>
+        <v>3.212515587296722e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.792645844984658e-08</v>
+        <v>4.792645844984657e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.239480378690104e-08</v>
+        <v>5.239480378690106e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.355091319136892e-08</v>
+        <v>4.355091319136887e-08</v>
       </c>
       <c r="F8" t="n">
         <v>3.243311493090453e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.864139682420561e-08</v>
+        <v>4.864139682420553e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.085991034254743e-08</v>
+        <v>5.085991034254747e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.792283024129863e-08</v>
+        <v>4.792283024129858e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.892812599414726e-08</v>
+        <v>4.892812599414732e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.204792220592992e-08</v>
+        <v>3.204792220592983e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.732686948375643e-08</v>
+        <v>6.732686948375647e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.592005831201867e-08</v>
+        <v>2.592005831201869e-08</v>
       </c>
       <c r="C9" t="n">
         <v>3.096759248082571e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.212225134799791e-08</v>
+        <v>3.212225134799789e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.702221654150081e-08</v>
+        <v>3.702221654150074e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.096759018752211e-08</v>
+        <v>3.096759018752213e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.168594471505245e-08</v>
+        <v>3.168594471505243e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.390445823339427e-08</v>
+        <v>3.390445823339424e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.096737813214549e-08</v>
+        <v>3.096737813214547e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.196952999523708e-08</v>
+        <v>3.196952999523703e-08</v>
       </c>
       <c r="K9" t="n">
         <v>2.83467374865298e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.366111494848105e-08</v>
+        <v>3.366111494848101e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.135845787206817e-08</v>
+        <v>1.135845787206816e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.014372940666106e-08</v>
@@ -6464,10 +6464,10 @@
         <v>1.137554738393595e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.041355929156328e-08</v>
+        <v>1.041355929156327e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>9.522416721600686e-09</v>
+        <v>9.522416721600678e-09</v>
       </c>
       <c r="G2" t="n">
         <v>1.137726059553181e-08</v>
@@ -6479,13 +6479,13 @@
         <v>1.137050303060023e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.14500839709719e-08</v>
+        <v>1.145008397097188e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.091496979618842e-08</v>
+        <v>1.091496979618843e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.134556251477666e-08</v>
+        <v>1.134556251477665e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6495,10 +6495,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.179122799865934e-08</v>
+        <v>1.179122799865933e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.872192568907555e-09</v>
+        <v>9.872192568907544e-09</v>
       </c>
       <c r="D3" t="n">
         <v>1.191525238126516e-08</v>
@@ -6507,25 +6507,25 @@
         <v>1.030181612400799e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.830927128244747e-09</v>
+        <v>8.830927128244737e-09</v>
       </c>
       <c r="G3" t="n">
         <v>1.192690793557599e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.180468423011619e-08</v>
+        <v>1.180468423011618e-08</v>
       </c>
       <c r="I3" t="n">
         <v>1.187904675690846e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.223040545304806e-08</v>
+        <v>1.223040545304802e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.118752520570748e-08</v>
+        <v>1.118752520570747e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.172245637479248e-08</v>
+        <v>1.172245637479249e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6538,34 +6538,34 @@
         <v>7.447078430433236e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.503631922430798e-09</v>
+        <v>7.503631922430796e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.64011232854378e-09</v>
+        <v>7.640112328543785e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.523627100810267e-09</v>
+        <v>7.523627100810258e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.523627100810275e-09</v>
+        <v>7.523627100810258e-09</v>
       </c>
       <c r="G4" t="n">
         <v>7.650280310653581e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.475005562829815e-09</v>
+        <v>7.47500556282981e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.537107702547135e-09</v>
+        <v>7.537107702547125e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.036279511133947e-09</v>
+        <v>8.036279511133943e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.712394684918583e-09</v>
+        <v>7.712394684918587e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.332882383696038e-09</v>
+        <v>7.332882383696037e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.137456866681198e-08</v>
+        <v>3.137456866681202e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.469466596613732e-08</v>
+        <v>3.469466596613728e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.585399810310547e-08</v>
+        <v>3.585399810310546e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.469466767899239e-08</v>
+        <v>3.469466767899231e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.469466767899239e-08</v>
+        <v>3.469466767899231e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.589079743183895e-08</v>
+        <v>3.589079743183888e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.619118510425035e-08</v>
+        <v>3.619118510425039e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.469459050026336e-08</v>
+        <v>3.469459050026337e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.270162440302066e-08</v>
+        <v>4.270162440302062e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.580156497631116e-08</v>
+        <v>3.580156497631119e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.305740867469741e-08</v>
+        <v>3.305740867469744e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6615,28 +6615,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.23053309771513e-08</v>
+        <v>1.230533097715128e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.973376993588975e-09</v>
+        <v>9.973376993588892e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.008710067593223e-08</v>
+        <v>1.008710067593222e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.78564369295213e-09</v>
+        <v>9.785643692952113e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.986086164380956e-09</v>
+        <v>9.986086164380946e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.250853285737162e-08</v>
+        <v>1.250853285737159e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.242435696752713e-08</v>
+        <v>1.242435696752714e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.239536024926518e-08</v>
+        <v>1.239536024926516e-08</v>
       </c>
       <c r="J6" t="n">
         <v>1.062652525260814e-08</v>
@@ -6655,28 +6655,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.368398474213952e-08</v>
+        <v>1.36839847421395e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.377408948012734e-08</v>
+        <v>1.377408948012733e-08</v>
       </c>
       <c r="D7" t="n">
         <v>1.387660332637365e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.377411210347154e-08</v>
+        <v>1.377411210347152e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.377411210347154e-08</v>
+        <v>1.377411210347152e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.388718662235986e-08</v>
+        <v>1.388718662235983e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.371191187453607e-08</v>
+        <v>1.371191187453605e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.37740140142534e-08</v>
+        <v>1.377401401425339e-08</v>
       </c>
       <c r="J7" t="n">
         <v>1.42731858228402e-08</v>
@@ -6685,7 +6685,7 @@
         <v>1.394930099662484e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.356978869540232e-08</v>
+        <v>1.356978869540231e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6698,34 +6698,34 @@
         <v>3.036951751518554e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.5383154697926e-08</v>
+        <v>4.538315469792606e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.857637142903944e-08</v>
+        <v>4.857637142903949e-08</v>
       </c>
       <c r="E8" t="n">
         <v>4.130217248165965e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.093282675249865e-08</v>
+        <v>3.093282675249869e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.549276977059827e-08</v>
+        <v>4.549276977059826e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.531749502277437e-08</v>
+        <v>4.531749502277439e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.53795971624918e-08</v>
+        <v>4.537959716249181e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.588170119072599e-08</v>
+        <v>4.5881701190726e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.035768617378058e-08</v>
+        <v>3.035768617378059e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.076061205695966e-08</v>
+        <v>6.076061205695973e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.352972941426669e-08</v>
+        <v>2.352972941426666e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.822225933314523e-08</v>
+        <v>2.822225933314516e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.832519019012989e-08</v>
+        <v>2.832519019012982e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.353335973553259e-08</v>
+        <v>3.353335973553255e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.822225791322732e-08</v>
+        <v>2.82222579132273e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.833535647537772e-08</v>
+        <v>2.833535647537764e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.816008172755397e-08</v>
+        <v>2.816008172755391e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.822218386727125e-08</v>
+        <v>2.822218386727124e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.87213556758581e-08</v>
+        <v>2.872135567585802e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.573080833841002e-08</v>
+        <v>2.573080833840998e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.801795854842019e-08</v>
+        <v>2.801795854842014e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6851,34 +6851,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.140601103956404e-08</v>
+        <v>1.140601103956408e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.019862677261399e-08</v>
+        <v>1.019862677261401e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.141641479535631e-08</v>
+        <v>1.141641479535636e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.047265828763116e-08</v>
+        <v>1.047265828763121e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>9.569445818204215e-09</v>
+        <v>9.569445818204225e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.140565064853729e-08</v>
+        <v>1.140565064853731e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.137877133052718e-08</v>
+        <v>1.137877133052719e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.140795373780701e-08</v>
+        <v>1.140795373780703e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.155057079244328e-08</v>
+        <v>1.155057079244331e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.094216518613415e-08</v>
+        <v>1.094216518613421e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.138628332200832e-08</v>
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.196538663539091e-08</v>
+        <v>1.196538663539093e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.000257838521666e-08</v>
+        <v>1.000257838521669e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.204055053165113e-08</v>
+        <v>1.204055053165114e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.043918934684005e-08</v>
+        <v>1.043918934684008e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.948376823106329e-09</v>
+        <v>8.948376823106368e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.196442676638058e-08</v>
+        <v>1.19644267663806e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.185471900750636e-08</v>
+        <v>1.185471900750639e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.198068545573216e-08</v>
+        <v>1.19806854557322e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.258517442374979e-08</v>
+        <v>1.258517442374984e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.117996240447345e-08</v>
+        <v>1.117996240447349e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.18474753824067e-08</v>
+        <v>1.184747538240671e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.724385407074077e-09</v>
+        <v>7.724385407074091e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.668326911628103e-09</v>
+        <v>7.668326911628122e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.841900614711968e-09</v>
+        <v>7.841900614711974e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.688304316226241e-09</v>
+        <v>7.688304316226245e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.688304316226241e-09</v>
+        <v>7.688304316226245e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.711198961486664e-09</v>
+        <v>7.711198961486678e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.558023457709077e-09</v>
+        <v>7.558023457709094e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.700763686374959e-09</v>
+        <v>7.700763686374977e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.505707411260634e-09</v>
+        <v>8.505707411260652e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.682980233223237e-09</v>
+        <v>7.682980233223256e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.531168009106367e-09</v>
+        <v>7.531168009106384e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.531018252067835e-08</v>
+        <v>3.531018252067839e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.639575081163179e-08</v>
+        <v>3.639575081163189e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.786113590533187e-08</v>
+        <v>3.786113590533181e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.639575251999826e-08</v>
+        <v>3.639575251999842e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.639575251999826e-08</v>
+        <v>3.639575251999842e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.606458112368002e-08</v>
+        <v>3.606458112368064e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.59745697032737e-08</v>
+        <v>3.597456970327375e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.639569869703766e-08</v>
+        <v>3.639569869703785e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.999259612737501e-08</v>
+        <v>4.999259612737525e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.475890686344416e-08</v>
+        <v>3.475890686344423e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.559537054926831e-08</v>
+        <v>3.559537054926833e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.016697964114836e-08</v>
+        <v>1.016697964114837e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.013583607848738e-08</v>
+        <v>1.013583607848742e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.028865356052974e-08</v>
+        <v>1.028865356052975e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.947309958469502e-09</v>
+        <v>9.947309958469557e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.014650690072745e-08</v>
+        <v>1.014650690072748e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.015379319556095e-08</v>
+        <v>1.015379319556096e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.251842978864046e-08</v>
+        <v>1.25184297886405e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.014335792044924e-08</v>
+        <v>1.014335792044925e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.109484667623021e-08</v>
+        <v>1.109484667623023e-08</v>
       </c>
       <c r="K6" t="n">
         <v>1.01252985023157e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>9.972764991518223e-09</v>
+        <v>9.972764991518234e-09</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.400255894351521e-08</v>
+        <v>1.400255894351525e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.39789893374102e-08</v>
+        <v>1.397898933741021e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.411965870120989e-08</v>
+        <v>1.411965870120991e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.397898382818466e-08</v>
+        <v>1.397898382818469e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.397898382818466e-08</v>
+        <v>1.397898382818469e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.398937249792781e-08</v>
+        <v>1.398937249792784e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.383619699415021e-08</v>
+        <v>1.383619699415025e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.397893722281611e-08</v>
+        <v>1.397893722281614e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.478388094770178e-08</v>
+        <v>1.478388094770182e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.396115376966437e-08</v>
+        <v>1.396115376966444e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.380934154554749e-08</v>
+        <v>1.380934154554755e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.069572298179913e-08</v>
+        <v>3.069572298179923e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.563775466149979e-08</v>
+        <v>4.563775466149987e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.887787266784159e-08</v>
+        <v>4.88778726678416e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.154526393138261e-08</v>
+        <v>4.154526393138263e-08</v>
       </c>
       <c r="F8" t="n">
         <v>3.114667527663946e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.564467428332418e-08</v>
+        <v>4.564467428332426e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.549149877954671e-08</v>
+        <v>4.549149877954672e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.563423900821249e-08</v>
+        <v>4.563423900821243e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.644212322411686e-08</v>
+        <v>4.644212322411696e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.037638841751676e-08</v>
+        <v>3.037638841751682e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.109384732351987e-08</v>
+        <v>6.109384732351995e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.310143102682225e-08</v>
+        <v>2.310143102682229e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.748994342615758e-08</v>
+        <v>2.748994342615763e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.76310299193118e-08</v>
+        <v>2.763102991931184e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.258139182257449e-08</v>
+        <v>3.258139182257453e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.748994200401941e-08</v>
+        <v>2.748994200401947e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.750032658667521e-08</v>
+        <v>2.750032658667529e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.734715108289762e-08</v>
+        <v>2.734715108289766e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.748989131156348e-08</v>
+        <v>2.748989131156359e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.82948350364492e-08</v>
+        <v>2.829483503644929e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.481201541364681e-08</v>
+        <v>2.481201541364686e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.732029563429491e-08</v>
+        <v>2.732029563429499e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.180710717557792e-08</v>
+        <v>1.180710717557789e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.044297831370451e-08</v>
+        <v>1.044297831370452e-08</v>
       </c>
       <c r="D2" t="n">
         <v>1.205809400305252e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.072171097754445e-08</v>
+        <v>1.07217109775444e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>9.811917106758682e-09</v>
+        <v>9.811917106758657e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.188869173343115e-08</v>
+        <v>1.188869173343113e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.249586364856522e-08</v>
+        <v>1.249586364856521e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.170547665568243e-08</v>
+        <v>1.170547665568241e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.181815470584377e-08</v>
+        <v>1.18181547058437e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.12949188703023e-08</v>
+        <v>1.129491887030231e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.262280725967882e-08</v>
+        <v>1.26228072596788e-08</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.297182819417731e-08</v>
+        <v>1.297182819417728e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.018812025604815e-08</v>
+        <v>1.018812025604817e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.475416457124448e-08</v>
+        <v>1.47541645712445e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.063001500830563e-08</v>
+        <v>1.063001500830568e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>9.12833708074027e-09</v>
+        <v>9.128337080740341e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.355448116988456e-08</v>
+        <v>1.35544811698846e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.793039440396304e-08</v>
+        <v>1.793039440396305e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.225152286916734e-08</v>
+        <v>1.225152286916731e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.287124121979866e-08</v>
+        <v>1.28712412197985e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.189392825022368e-08</v>
+        <v>1.189392825022354e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.879440814977104e-08</v>
+        <v>1.879440814977105e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.130396830796677e-09</v>
+        <v>9.130396830796663e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.863283674818212e-09</v>
+        <v>7.8632836748182e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.196540850676747e-08</v>
+        <v>1.196540850676746e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>7.888052768884969e-09</v>
+        <v>7.888052768884967e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.888052768884969e-09</v>
+        <v>7.888052768884967e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.00414457984781e-08</v>
+        <v>1.004144579847811e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.698255208776936e-08</v>
+        <v>1.698255208776939e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>7.927633397901885e-09</v>
+        <v>7.927633397901852e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.874052294475705e-09</v>
+        <v>8.874052294475687e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>8.64830507830631e-09</v>
+        <v>8.648305078306276e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.826060765638719e-08</v>
+        <v>1.826060765638717e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.889182487364587e-08</v>
+        <v>5.889182487364581e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.993318303933647e-08</v>
+        <v>3.993318303933559e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.075077570746473e-07</v>
+        <v>1.075077570746476e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>3.993318506655808e-08</v>
+        <v>3.993318506655778e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.993318506655808e-08</v>
+        <v>3.993318506655778e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.651692951704997e-08</v>
+        <v>7.651692951705055e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>2.093486419801539e-07</v>
+        <v>2.093486419801545e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>3.993264768917953e-08</v>
+        <v>3.993264768917926e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.720787421711359e-08</v>
+        <v>5.720787421711319e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.073277947911013e-08</v>
+        <v>5.073277947911015e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.489826848737425e-08</v>
+        <v>5.489826848737515e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7407,34 +7407,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.184800848855517e-08</v>
+        <v>1.184800848855516e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.058506153699538e-08</v>
+        <v>1.058506153699532e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.477550077017754e-08</v>
+        <v>1.477550077017756e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.038156234154937e-08</v>
+        <v>1.038156234154942e-08</v>
       </c>
       <c r="F6" t="n">
         <v>1.064447721302372e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.558713614279601e-08</v>
+        <v>1.558713614279602e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.267636127100825e-08</v>
+        <v>2.267636127100822e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.347332374221971e-08</v>
+        <v>1.347332374221975e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.444967249646203e-08</v>
+        <v>1.4449672496462e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.13448160239857e-08</v>
+        <v>1.134481602398572e-08</v>
       </c>
       <c r="L6" t="n">
         <v>2.104046120437001e-08</v>
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.592369188688987e-08</v>
+        <v>1.592369188688989e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.472146380415208e-08</v>
+        <v>1.472146380415207e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.875825806894517e-08</v>
+        <v>1.875825806894519e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.472024427382428e-08</v>
+        <v>1.47202442738243e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.472024427382428e-08</v>
+        <v>1.47202442738243e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.683474085457133e-08</v>
+        <v>1.683474085457132e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.37758471438626e-08</v>
+        <v>2.377584714386263e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.472092845399509e-08</v>
+        <v>1.472092845399506e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.566734735056887e-08</v>
+        <v>1.566734735056891e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.544160013439951e-08</v>
+        <v>1.544160013439953e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.505390271248032e-08</v>
+        <v>2.505390271248036e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.397630366056848e-08</v>
+        <v>3.39763036605685e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.896084286087425e-08</v>
+        <v>4.896084286087411e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.635139795029243e-08</v>
+        <v>5.635139795029228e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.453421831486578e-08</v>
+        <v>4.453421831486584e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.328662835584806e-08</v>
+        <v>3.328662835584808e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.107153880741016e-08</v>
+        <v>5.107153880741007e-08</v>
       </c>
       <c r="H8" t="n">
         <v>5.801264509670187e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.895772640683393e-08</v>
+        <v>4.89577264068339e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.990732596207855e-08</v>
+        <v>4.990732596207858e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.319358234061028e-08</v>
+        <v>3.319358234061036e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>7.619643643130977e-08</v>
+        <v>7.619643643130979e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7527,34 +7527,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.830130447620462e-08</v>
+        <v>2.830130447620467e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.257385059205347e-08</v>
+        <v>3.257385059205357e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.661109092367753e-08</v>
+        <v>3.661109092367763e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.88916191919142e-08</v>
+        <v>3.889161919191424e-08</v>
       </c>
       <c r="F9" t="n">
         <v>3.257384679009913e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.46871276424728e-08</v>
+        <v>3.468712764247286e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>4.162823393176416e-08</v>
+        <v>4.162823393176415e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.257331524189659e-08</v>
+        <v>3.257331524189654e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.351973413847035e-08</v>
+        <v>3.351973413847034e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.012188149150883e-08</v>
+        <v>3.012188149150882e-08</v>
       </c>
       <c r="L9" t="n">
         <v>4.290628950038186e-08</v>
@@ -7643,31 +7643,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.149645002364791e-08</v>
+        <v>1.14964500236479e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.026888752570476e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.180756994331137e-08</v>
+        <v>1.180756994331138e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.054589343385714e-08</v>
+        <v>1.054589343385716e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>9.637141959974935e-09</v>
+        <v>9.637141959974942e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>1.162209455831067e-08</v>
+        <v>1.162209455831066e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1568273159138e-08</v>
+        <v>1.156827315913798e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.151246881468818e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.161713160480077e-08</v>
+        <v>1.161713160480078e-08</v>
       </c>
       <c r="K2" t="n">
         <v>1.101575601277017e-08</v>
@@ -7686,34 +7686,34 @@
         <v>1.181797741691259e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.900775644087486e-09</v>
+        <v>9.900775644087502e-09</v>
       </c>
       <c r="D3" t="n">
         <v>1.402475709687073e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.034100384841757e-08</v>
+        <v>1.034100384841759e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>8.841047421186947e-09</v>
+        <v>8.841047421186949e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>1.27122650413921e-08</v>
+        <v>1.271226504139212e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.241794213067491e-08</v>
+        <v>1.241794213067492e-08</v>
       </c>
       <c r="I3" t="n">
         <v>1.19341340064103e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.240354300423151e-08</v>
+        <v>1.240354300423154e-08</v>
       </c>
       <c r="K3" t="n">
         <v>1.110422312982558e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.574699651280769e-08</v>
+        <v>1.574699651280771e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.369810592411831e-09</v>
+        <v>7.369810592411857e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.451596972472007e-09</v>
+        <v>7.45159697247202e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.088405320724498e-08</v>
+        <v>1.088405320724503e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>7.473086937348723e-09</v>
+        <v>7.47308693734874e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.47308693734872e-09</v>
+        <v>7.473086937348728e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>8.779119697624406e-09</v>
+        <v>8.779119697624422e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>8.331675467515296e-09</v>
+        <v>8.331675467515291e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.499863847779996e-09</v>
+        <v>7.499863847779991e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.162983659171162e-09</v>
+        <v>8.16298365917121e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.533405667416587e-09</v>
+        <v>7.53340566741661e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.354969061458194e-08</v>
+        <v>1.354969061458196e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.883267152183293e-08</v>
+        <v>2.883267152183289e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.293052883618645e-08</v>
+        <v>3.293052883618654e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.388884848236326e-08</v>
+        <v>8.388884848236329e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.293053069010782e-08</v>
+        <v>3.293053069010784e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.293053069010782e-08</v>
+        <v>3.293053069010784e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.265751153437108e-08</v>
+        <v>5.265751153437067e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.871637934686466e-08</v>
+        <v>4.871637934686469e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.293018577663619e-08</v>
+        <v>3.29301857766362e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.34328586498834e-08</v>
+        <v>4.343285864988323e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.186018846599808e-08</v>
+        <v>3.186018846599804e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.489593776416438e-07</v>
+        <v>1.489593776416434e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7803,34 +7803,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.236915872177619e-08</v>
+        <v>1.236915872177621e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.930793106632016e-09</v>
+        <v>9.93079310663197e-09</v>
       </c>
       <c r="D6" t="n">
         <v>1.343363622794431e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.742650738159649e-09</v>
+        <v>9.742650738159659e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.966976196776773e-09</v>
+        <v>9.966976196776783e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.377846782698876e-08</v>
+        <v>1.377846782698872e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.34298479399429e-08</v>
+        <v>1.342984793994279e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.249921197714435e-08</v>
+        <v>1.249921197714436e-08</v>
       </c>
       <c r="J6" t="n">
         <v>1.077713434851152e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.976350400983305e-09</v>
+        <v>9.976350400983306e-09</v>
       </c>
       <c r="L6" t="n">
         <v>1.604984795049287e-08</v>
@@ -7846,28 +7846,28 @@
         <v>1.367660725434791e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.380700356926634e-08</v>
+        <v>1.380700356926636e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.719043469385734e-08</v>
+        <v>1.719043469385735e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.38064057096502e-08</v>
+        <v>1.380640570965024e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.38064057096502e-08</v>
+        <v>1.380640570965024e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.508591635956049e-08</v>
+        <v>1.508591635956043e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.463847212945137e-08</v>
+        <v>1.463847212945139e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.380666050971608e-08</v>
+        <v>1.38066605097161e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.446978032110723e-08</v>
+        <v>1.446978032110725e-08</v>
       </c>
       <c r="K7" t="n">
         <v>1.384020232935268e-08</v>
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.043633254691139e-08</v>
+        <v>3.043633254691155e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.559623204909936e-08</v>
+        <v>4.559623204909962e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.209303122848969e-08</v>
+        <v>5.20930312284899e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.148617221129756e-08</v>
+        <v>4.148617221129774e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.104294045329394e-08</v>
+        <v>3.104294045329405e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.687223557884273e-08</v>
+        <v>4.687223557884288e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.642479134873333e-08</v>
+        <v>4.642479134873355e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.55929797289983e-08</v>
+        <v>4.559297972899846e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.625905269887632e-08</v>
+        <v>4.625905269887656e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>3.032080092485893e-08</v>
+        <v>3.032080092485901e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.733934035769681e-08</v>
+        <v>6.733934035769711e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.381614297635791e-08</v>
+        <v>2.381614297635792e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.865606871309675e-08</v>
+        <v>2.865606871309676e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.203991701716081e-08</v>
+        <v>3.20399170171608e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.409076521022657e-08</v>
+        <v>3.409076521022655e-08</v>
       </c>
       <c r="F9" t="n">
         <v>2.8656067156516e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.993498150339092e-08</v>
+        <v>2.993498150339089e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.948753727328178e-08</v>
+        <v>2.948753727328176e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.865572565354649e-08</v>
+        <v>2.865572565354652e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.931884546493765e-08</v>
+        <v>2.931884546493761e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.596054847336879e-08</v>
+        <v>2.596054847336876e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.470555242034842e-08</v>
+        <v>3.470555242034839e-08</v>
       </c>
     </row>
   </sheetData>
